--- a/scripts/ffn/performance.xlsx
+++ b/scripts/ffn/performance.xlsx
@@ -9,13 +9,18 @@
   <sheets>
     <sheet name="Models" sheetId="1" r:id="rId1"/>
     <sheet name="Ensemble" sheetId="2" r:id="rId2"/>
+    <sheet name="Ensemble optspreads" sheetId="3" r:id="rId3"/>
+    <sheet name="Ensemble opt-undspreads" sheetId="4" r:id="rId4"/>
+    <sheet name="Returns Long-Short 30-min" sheetId="5" r:id="rId5"/>
+    <sheet name="Returns Long-Short Daily" sheetId="6" r:id="rId6"/>
+    <sheet name="Returns Long-Short Weekly" sheetId="7" r:id="rId7"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="576" uniqueCount="472">
   <si>
     <t>Model</t>
   </si>
@@ -149,7 +154,1288 @@
     <t>H-L 10 portfolios, 0 turnover</t>
   </si>
   <si>
-    <t>[nan, nan]</t>
+    <t>[np.float64(0.000433810237941636), np.float64(2.136355203519665e-32)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.0003908864096079647), np.float64(0.8578662009050895)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-1.1007154165245756), np.float64(0.27134472797856407)]</t>
+  </si>
+  <si>
+    <t>delta_change_mean</t>
+  </si>
+  <si>
+    <t>delta_change_std</t>
+  </si>
+  <si>
+    <t>turnover_mean</t>
+  </si>
+  <si>
+    <t>turnover_std</t>
+  </si>
+  <si>
+    <t>H-L 3 portfolios, 0.05 turnover</t>
+  </si>
+  <si>
+    <t>H-L 4 portfolios, 0.05 turnover</t>
+  </si>
+  <si>
+    <t>H-L 5 portfolios, 0.05 turnover</t>
+  </si>
+  <si>
+    <t>H-L 10 portfolios, 0.05 turnover</t>
+  </si>
+  <si>
+    <t>H-L 20 portfolios, 0.05 turnover</t>
+  </si>
+  <si>
+    <t>H-L 40 portfolios, 0.05 turnover</t>
+  </si>
+  <si>
+    <t>H-L 100 portfolios, 0.05 turnover</t>
+  </si>
+  <si>
+    <t>H-L 200 portfolios, 0.05 turnover</t>
+  </si>
+  <si>
+    <t>H-L 500 portfolios, 0.05 turnover</t>
+  </si>
+  <si>
+    <t>H-L 1000 portfolios, 0.05 turnover</t>
+  </si>
+  <si>
+    <t>H-L 3 portfolios, 0.04 turnover</t>
+  </si>
+  <si>
+    <t>H-L 4 portfolios, 0.04 turnover</t>
+  </si>
+  <si>
+    <t>H-L 5 portfolios, 0.04 turnover</t>
+  </si>
+  <si>
+    <t>H-L 10 portfolios, 0.04 turnover</t>
+  </si>
+  <si>
+    <t>H-L 20 portfolios, 0.04 turnover</t>
+  </si>
+  <si>
+    <t>H-L 40 portfolios, 0.04 turnover</t>
+  </si>
+  <si>
+    <t>H-L 100 portfolios, 0.04 turnover</t>
+  </si>
+  <si>
+    <t>H-L 200 portfolios, 0.04 turnover</t>
+  </si>
+  <si>
+    <t>H-L 500 portfolios, 0.04 turnover</t>
+  </si>
+  <si>
+    <t>H-L 1000 portfolios, 0.04 turnover</t>
+  </si>
+  <si>
+    <t>H-L 3 portfolios, 0.03 turnover</t>
+  </si>
+  <si>
+    <t>H-L 4 portfolios, 0.03 turnover</t>
+  </si>
+  <si>
+    <t>H-L 5 portfolios, 0.03 turnover</t>
+  </si>
+  <si>
+    <t>H-L 10 portfolios, 0.03 turnover</t>
+  </si>
+  <si>
+    <t>H-L 20 portfolios, 0.03 turnover</t>
+  </si>
+  <si>
+    <t>H-L 40 portfolios, 0.03 turnover</t>
+  </si>
+  <si>
+    <t>H-L 100 portfolios, 0.03 turnover</t>
+  </si>
+  <si>
+    <t>H-L 200 portfolios, 0.03 turnover</t>
+  </si>
+  <si>
+    <t>H-L 500 portfolios, 0.03 turnover</t>
+  </si>
+  <si>
+    <t>H-L 1000 portfolios, 0.03 turnover</t>
+  </si>
+  <si>
+    <t>H-L 3 portfolios, 0.02 turnover</t>
+  </si>
+  <si>
+    <t>H-L 4 portfolios, 0.02 turnover</t>
+  </si>
+  <si>
+    <t>H-L 5 portfolios, 0.02 turnover</t>
+  </si>
+  <si>
+    <t>H-L 10 portfolios, 0.02 turnover</t>
+  </si>
+  <si>
+    <t>H-L 20 portfolios, 0.02 turnover</t>
+  </si>
+  <si>
+    <t>H-L 40 portfolios, 0.02 turnover</t>
+  </si>
+  <si>
+    <t>H-L 100 portfolios, 0.02 turnover</t>
+  </si>
+  <si>
+    <t>H-L 200 portfolios, 0.02 turnover</t>
+  </si>
+  <si>
+    <t>H-L 500 portfolios, 0.02 turnover</t>
+  </si>
+  <si>
+    <t>H-L 1000 portfolios, 0.02 turnover</t>
+  </si>
+  <si>
+    <t>H-L 3 portfolios, 0.01 turnover</t>
+  </si>
+  <si>
+    <t>H-L 4 portfolios, 0.01 turnover</t>
+  </si>
+  <si>
+    <t>H-L 5 portfolios, 0.01 turnover</t>
+  </si>
+  <si>
+    <t>H-L 10 portfolios, 0.01 turnover</t>
+  </si>
+  <si>
+    <t>H-L 20 portfolios, 0.01 turnover</t>
+  </si>
+  <si>
+    <t>H-L 40 portfolios, 0.01 turnover</t>
+  </si>
+  <si>
+    <t>H-L 100 portfolios, 0.01 turnover</t>
+  </si>
+  <si>
+    <t>H-L 200 portfolios, 0.01 turnover</t>
+  </si>
+  <si>
+    <t>H-L 500 portfolios, 0.01 turnover</t>
+  </si>
+  <si>
+    <t>H-L 1000 portfolios, 0.01 turnover</t>
+  </si>
+  <si>
+    <t>H-L 3 portfolios, 0 turnover</t>
+  </si>
+  <si>
+    <t>H-L 4 portfolios, 0 turnover</t>
+  </si>
+  <si>
+    <t>H-L 5 portfolios, 0 turnover</t>
+  </si>
+  <si>
+    <t>H-L 20 portfolios, 0 turnover</t>
+  </si>
+  <si>
+    <t>H-L 40 portfolios, 0 turnover</t>
+  </si>
+  <si>
+    <t>H-L 100 portfolios, 0 turnover</t>
+  </si>
+  <si>
+    <t>H-L 200 portfolios, 0 turnover</t>
+  </si>
+  <si>
+    <t>H-L 500 portfolios, 0 turnover</t>
+  </si>
+  <si>
+    <t>H-L 1000 portfolios, 0 turnover</t>
+  </si>
+  <si>
+    <t>inf</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.0029863860332970615), np.float64(0.055250427052330166)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.003517450417967046), np.float64(0.09028690578357539)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.0014866126299620214), np.float64(0.20228683702556502)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.0020137282895691475), np.float64(0.38666869038567536)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0020379832951972847), np.float64(0.016098730421171104)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.004289065282516425), np.float64(0.011409804524543344)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.010832107994880893), np.float64(0.010403064194005674)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.021346542048892712), np.float64(0.011572666763182098)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.05297419395207186), np.float64(0.014094043316403909)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.10193225792932553), np.float64(0.009290522274838045)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.00029701973305442747), np.float64(0.47158873293947173)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.00019158491554669517), np.float64(0.7209893025775425)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0007411643110324242), np.float64(0.24404549255596597)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0021450701432957527), np.float64(0.09127566155045969)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.004601201061435948), np.float64(0.06931905930747982)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.009460374575218849), np.float64(0.06028148354200394)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.02364467004281071), np.float64(0.0610906923306249)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.04647385230037348), np.float64(0.06043309687870293)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.11582420126809638), np.float64(0.06623134104423158)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.22191823322700596), np.float64(0.05511511390217236)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.000537214653794223), np.float64(1.1844755612720097e-21)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.0003380838248399593), np.float64(1.7498094862302912e-08)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.00020294034520086128), np.float64(0.0037038384176998358)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.00022143676208547593), np.float64(0.07530257640987763)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0007541347223479365), np.float64(0.0016515131823203035)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0018237701985619856), np.float64(1.4226756444316203e-05)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.004343266430129353), np.float64(3.3142826372763596e-05)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.008368687953096572), np.float64(5.705472309699326e-05)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.02145561082861879), np.float64(1.8876381698632256e-05)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0415856367977222), np.float64(2.883320783915815e-05)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.0001132247960378734), np.float64(0.3506226769142772)]</t>
+  </si>
+  <si>
+    <t>[np.float64(4.5842873552207864e-05), np.float64(0.7598834757379611)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.00012501295045108185), np.float64(0.46894482194641873)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.000602044640064541), np.float64(0.07732918699475674)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0014270513045035055), np.float64(0.033620321035413465)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0027595912178333885), np.float64(0.039602913879607196)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.006515634996619725), np.float64(0.05192975637160744)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.012600991267057174), np.float64(0.0602046374728022)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.03056183325880133), np.float64(0.06253907159490846)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.06471428041029778), np.float64(0.07796433169607002)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-8.669576886628979e-05), np.float64(0.15159347111180096)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-3.373199920912279e-06), np.float64(0.9572869875761426)]</t>
+  </si>
+  <si>
+    <t>[np.float64(4.499088220213623e-05), np.float64(0.5477873478951261)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.000236558727420744), np.float64(0.08599133565115806)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0006264939568828834), np.float64(2.853930793869528e-07)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.001018794850512001), np.float64(8.712097761956866e-06)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0019407085984127041), np.float64(0.00046107399652364593)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.003388156443277956), np.float64(0.0021786793194926274)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.007481694688347086), np.float64(0.005677152821737695)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.014564475291827287), np.float64(0.008904019799135406)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0002490698694815981), np.float64(4.5808486923175856e-23)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0002949839227006422), np.float64(8.167581735988578e-26)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.00032914355649402296), np.float64(6.575461326498763e-28)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.00043381023793381075), np.float64(2.1363554913116837e-32)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0005378897759371654), np.float64(3.388454958721246e-35)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0006343978838201762), np.float64(5.73621775072856e-34)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0007679217445818178), np.float64(6.277724002572346e-27)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0009145807453900796), np.float64(2.9657483975418194e-21)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0011588358161300975), np.float64(1.425848712138654e-14)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.001316152393464954), np.float64(3.676978749141694e-11)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.23130161350963263), np.float64(0.017267783017343736)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.323963777396353), np.float64(0.012311030551366361)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.2144277087754402), np.float64(0.0032483272721947273)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.44872635207088607), np.float64(0.001984786778568051)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.07198655097106646), np.float64(0.16784393621865848)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.16144446165311907), np.float64(0.12121813787773199)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.4411025495363798), np.float64(0.08751568599047001)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.948564575797443), np.float64(0.0636650548468569)]</t>
+  </si>
+  <si>
+    <t>[np.float64(2.4394003182310997), np.float64(0.05569099874522908)]</t>
+  </si>
+  <si>
+    <t>[np.float64(5.28532652276138), np.float64(0.019517527299654516)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-5.170943276083593e-05), np.float64(0.9983937506273854)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0037415941719644544), np.float64(0.9107831875802971)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0039877431048455595), np.float64(0.9198712946259177)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.009748813834512008), np.float64(0.9018340679023588)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.021837045339416647), np.float64(0.8890588803597257)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.06435255446370909), np.float64(0.8355002437436514)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.2674837649258842), np.float64(0.7288857126180909)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.59250784264433), np.float64(0.692010977830494)]</t>
+  </si>
+  <si>
+    <t>[np.float64(1.3283910374230636), np.float64(0.7228847928318437)]</t>
+  </si>
+  <si>
+    <t>[np.float64(3.1745999195798777), np.float64(0.6357799034065985)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0027855137609266362), np.float64(0.4138593180362105)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0034318359777966395), np.float64(0.35379414952189414)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.007400379593237517), np.float64(0.08952341373675587)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.013159706204243012), np.float64(0.08943545114824954)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.024980934566682655), np.float64(0.0908634236204916)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.04876790481919284), np.float64(0.05797216841005444)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.11671021255534567), np.float64(0.06737474974460333)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.2342027930680176), np.float64(0.062259489253331086)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.32547910010446224), np.float64(0.27086119599123926)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.672515845698298), np.float64(0.23121258998364191)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0016695613870738326), np.float64(0.8251276477928426)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.0007570809929404365), np.float64(0.9354719896163665)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.00021533628462946293), np.float64(0.984079814320768)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.005337173534263359), np.float64(0.8013171502597793)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.002101085122568585), np.float64(0.9595458398442691)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.0043706586887547316), np.float64(0.9577447529995351)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.0238893341917757), np.float64(0.9074040611674841)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.006552972822577503), np.float64(0.9871658074985586)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.027946811805371684), np.float64(0.9769853757631888)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.17181162300661132), np.float64(0.9346763947095201)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.00887249037417238), np.float64(0.018662363574560997)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.004799011713381993), np.float64(0.22192050217837356)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0055495322983366195), np.float64(0.2345700858963667)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.009775687620790868), np.float64(0.25280973287581077)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0002595187919333742), np.float64(0.9723220993088416)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.004960103728278161), np.float64(0.7232219055922452)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.010668732190636113), np.float64(0.7520625861459526)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.026516171120512765), np.float64(0.6938601982192094)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.04690741983825978), np.float64(0.7681660997219338)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.19788595940519843), np.float64(0.526430676072377)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.00044743038070723783), np.float64(0.7683676859395339)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.00037707852006919516), np.float64(0.8233621563932436)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.0003665849832401086), np.float64(0.8389520265247941)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.00039088635882694294), np.float64(0.8578662193163857)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.0007583749213656054), np.float64(0.7679606624774589)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.001172315723098539), np.float64(0.7026474461993765)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.0012192768344242225), np.float64(0.7727612395007982)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.0024828525734007455), np.float64(0.6624458585639679)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.007203850304138652), np.float64(0.4120995493264426)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.008423058801978398), np.float64(0.4525256023143103)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-2.389866237999027), np.float64(0.017080247516041553)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-2.035619643609742), np.float64(0.04211076632596732)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-1.9031025069101557), np.float64(0.05737841462769555)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-1.114929692515744), np.float64(0.2652084037672185)]</t>
+  </si>
+  <si>
+    <t>[np.float64(1.1607420106360204), np.float64(0.24608587621880607)]</t>
+  </si>
+  <si>
+    <t>[np.float64(2.0440419119183457), np.float64(0.041269564614228045)]</t>
+  </si>
+  <si>
+    <t>[np.float64(2.475974561758271), np.float64(0.013488923341736847)]</t>
+  </si>
+  <si>
+    <t>[np.float64(2.5302167471881964), np.float64(0.011586007645262134)]</t>
+  </si>
+  <si>
+    <t>[np.float64(2.51077582443436), np.float64(0.012238685763255982)]</t>
+  </si>
+  <si>
+    <t>[np.float64(2.671611870940747), np.float64(0.0076990761854082625)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-2.0033206963774637), np.float64(0.0454727236298333)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-1.1705757971772877), np.float64(0.24211065149630645)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.39156222051174855), np.float64(0.6954838103324833)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.8112474934229678), np.float64(0.417459824669194)]</t>
+  </si>
+  <si>
+    <t>[np.float64(1.4301052340676568), np.float64(0.15306912290865893)]</t>
+  </si>
+  <si>
+    <t>[np.float64(1.7230382265967361), np.float64(0.08525999638452526)]</t>
+  </si>
+  <si>
+    <t>[np.float64(1.8378717790567813), np.float64(0.06644423912586916)]</t>
+  </si>
+  <si>
+    <t>[np.float64(1.8706717638836992), np.float64(0.0617478907186954)]</t>
+  </si>
+  <si>
+    <t>[np.float64(1.84676225859124), np.float64(0.06514306373053169)]</t>
+  </si>
+  <si>
+    <t>[np.float64(1.9395149341841955), np.float64(0.05278258017810758)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-2.9333492224285664), np.float64(0.0034470510250512055)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-2.5739801536665476), np.float64(0.01022873905680402)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-2.2730996834262203), np.float64(0.023279031720721755)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-1.4001550211177631), np.float64(0.16184653003034413)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.32752822955135025), np.float64(0.7433523016857625)]</t>
+  </si>
+  <si>
+    <t>[np.float64(1.5415590792192988), np.float64(0.12356798902033089)]</t>
+  </si>
+  <si>
+    <t>[np.float64(3.2237624945772927), np.float64(0.0013154007569716535)]</t>
+  </si>
+  <si>
+    <t>[np.float64(3.7006590037996134), np.float64(0.0002294541992143181)]</t>
+  </si>
+  <si>
+    <t>[np.float64(4.1899300538028275), np.float64(3.0943752070460695e-05)]</t>
+  </si>
+  <si>
+    <t>[np.float64(4.183710986198905), np.float64(3.178460370196317e-05)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-2.1306824908511826), np.float64(0.03341336976687799)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-1.8134744209184044), np.float64(0.07012547523373558)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-1.6156440216704537), np.float64(0.10655736761808644)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.6113783960100092), np.float64(0.5411191719505982)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.5285699119505786), np.float64(0.5972473891674912)]</t>
+  </si>
+  <si>
+    <t>[np.float64(1.302137249395283), np.float64(0.1932364478202105)]</t>
+  </si>
+  <si>
+    <t>[np.float64(1.6653564821127744), np.float64(0.09622502861289896)]</t>
+  </si>
+  <si>
+    <t>[np.float64(1.749660141946447), np.float64(0.08055240969134166)]</t>
+  </si>
+  <si>
+    <t>[np.float64(1.8162426964037235), np.float64(0.06969952331630498)]</t>
+  </si>
+  <si>
+    <t>[np.float64(1.7379693341257592), np.float64(0.08259299606581583)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-2.0169184451258344), np.float64(0.044030692648249846)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-1.8380806256069162), np.float64(0.06641342899859314)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-1.7415445255450401), np.float64(0.08196455131767096)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-1.3782931821117916), np.float64(0.16849010507912587)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.6610513987884814), np.float64(0.5087657145790497)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.1331123498937922), np.float64(0.8941373067743089)]</t>
+  </si>
+  <si>
+    <t>[np.float64(1.285124694972015), np.float64(0.19911290754668956)]</t>
+  </si>
+  <si>
+    <t>[np.float64(1.9864935016988488), np.float64(0.047312249292774965)]</t>
+  </si>
+  <si>
+    <t>[np.float64(2.2990017105897356), np.float64(0.021756368767573354)]</t>
+  </si>
+  <si>
+    <t>[np.float64(2.3698779570312234), np.float64(0.018025358098205633)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-1.4295772242488007), np.float64(0.15322065869490964)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-1.3444708706301454), np.float64(0.17916932846447164)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-1.293368655811064), np.float64(0.19624914881152924)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-1.1007154150470781), np.float64(0.27134472862142467)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.9575687737896426), np.float64(0.33856351876899254)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.9126265914738796), np.float64(0.36170818152125517)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.7489009068120202), np.float64(0.4541324849531235)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.43203192104166166), np.float64(0.6658322088079515)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.1821370440938674), np.float64(0.8555203591610572)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.36282682992007026), np.float64(0.7168280924020395)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.0042969918357723055), np.float64(0.07394066370809807)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.00735345466619663), np.float64(0.10104454812440303)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.003704066475024531), np.float64(0.21229089159728837)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.003401075382946986), np.float64(0.3180781132354391)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0018692818945122147), np.float64(0.007798117791287835)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.004041786989103341), np.float64(0.008285435328212312)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.010767355133128603), np.float64(0.010327341697818147)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.021290084879093344), np.float64(0.010580229289942181)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.05247935425350169), np.float64(0.01392269720650999)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.1009786176413001), np.float64(0.008419855667524815)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.00042535626903131724), np.float64(0.16975189333238877)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-3.9104108911108834e-05), np.float64(0.9128768056345613)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.00045495069693896864), np.float64(0.24966231813280726)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0018008861364174323), np.float64(0.056548979917638235)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.004080621804798575), np.float64(0.054917384106117975)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.007659231327584837), np.float64(0.027880424277173257)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.022184172582200172), np.float64(0.05970867656792576)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.04428310679480938), np.float64(0.061916543329417734)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.10164020799154472), np.float64(0.04681672938551419)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.21178895461022887), np.float64(0.05670931467712975)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.0005199897081436296), np.float64(1.2270863236868474e-21)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.00034855388865982843), np.float64(1.3398654989894204e-08)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.00024108193681985965), np.float64(0.0008224476762961955)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.00015232867624260526), np.float64(0.24220595761370153)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0006374280321708888), np.float64(0.01083825200984139)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0018021239939575752), np.float64(1.566594183574699e-05)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.00429638004640253), np.float64(3.6057145866437144e-05)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.008261678217368148), np.float64(6.291331346517755e-05)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.021253607650856), np.float64(1.644067011005415e-05)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.041300225958429575), np.float64(2.7275628958840646e-05)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.00018155065359615015), np.float64(0.07233384822247854)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-4.165153456148231e-06), np.float64(0.9737295783699816)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.00011050738860862922), np.float64(0.46185524971902747)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0005490712410609793), np.float64(0.067506259847224)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0013735661863531368), np.float64(0.02621487680703952)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0026089102479863054), np.float64(0.03110196399657712)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0062563055294806245), np.float64(0.04564671585713236)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.012523177984153186), np.float64(0.06014668117969892)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.02854667866761269), np.float64(0.04990980606801858)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.06438879356734759), np.float64(0.07899093618793432)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.00013544141848212076), np.float64(0.031345669977474525)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-7.321964189206079e-05), np.float64(0.3687430667723206)]</t>
+  </si>
+  <si>
+    <t>[np.float64(3.209672262955456e-05), np.float64(0.6991976424305824)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0003298217932693203), np.float64(6.595922162017649e-07)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0005970130161208384), np.float64(2.2282097331709741e-07)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0009845619539208472), np.float64(3.068196841913492e-06)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0018459509633537128), np.float64(0.0002275506801210533)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0031952907426622975), np.float64(0.0011098982628278623)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.006936835619069287), np.float64(0.0035839575981636554)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.013363307645850609), np.float64(0.005088124634770773)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.00024355433544299727), np.float64(2.3377395950478936e-22)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0002905213759735466), np.float64(3.3932838349109885e-25)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0003255439501428689), np.float64(2.1536808247726947e-27)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0004333892542540111), np.float64(2.1961496669143943e-32)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0005365624918133783), np.float64(5.659715453614667e-35)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.000632025874638353), np.float64(8.397101617892438e-34)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0007636562438372992), np.float64(8.687839311027584e-27)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0008981169404214736), np.float64(1.2870931058906505e-20)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0011525436421423898), np.float64(2.1120976058356525e-14)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0013017396020348164), np.float64(6.278828837359763e-11)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.35340422653432824), np.float64(0.018429875591709888)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.7192168272308522), np.float64(0.010006324464169727)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.5259540229674201), np.float64(0.004523337346965701)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.6434864475323994), np.float64(0.0024371643111793678)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.05599815532348908), np.float64(0.19521089592182367)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.1437354808678705), np.float64(0.12561350146319955)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.45460151883427324), np.float64(0.07575256282367235)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.8841066874484207), np.float64(0.07887738205669312)]</t>
+  </si>
+  <si>
+    <t>[np.float64(2.414669161821136), np.float64(0.05636007780318799)]</t>
+  </si>
+  <si>
+    <t>[np.float64(4.6545697805362005), np.float64(0.03708628800245523)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.0031893506989811088), np.float64(0.8687702663067136)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.002565433966391423), np.float64(0.9082994639399797)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.003822530400708042), np.float64(0.8766729197485195)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.0005596377836552755), np.float64(0.9923996960098335)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.005767686846860901), np.float64(0.9649220395944261)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.010946378681250802), np.float64(0.9591348959961804)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.2573348947181331), np.float64(0.7204906602176244)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.562523879539552), np.float64(0.695193162161333)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.955348787015338), np.float64(0.7512782402775331)]</t>
+  </si>
+  <si>
+    <t>[np.float64(3.1831659060833144), np.float64(0.6204226823838851)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0024944354752827495), np.float64(0.4491704341187765)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.003296741351507689), np.float64(0.38317605916253533)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.007251348055398434), np.float64(0.1059211465069605)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.012501923750444836), np.float64(0.12339535960278435)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.024542464758492016), np.float64(0.11182913098218825)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.049328109867956674), np.float64(0.05339121553795216)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.12187327764399476), np.float64(0.05402546715561796)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.25070247119554656), np.float64(0.04400633340253639)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.3145435831847674), np.float64(0.27867201506488487)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.7170390563726151), np.float64(0.2005577943029872)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.00022239977440937972), np.float64(0.9718032133419354)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.00033721529485726586), np.float64(0.9659535717628486)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0001409409218550065), np.float64(0.9880323805385525)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.005095510795104379), np.float64(0.7852893153395738)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.0023584153885552236), np.float64(0.9507450867841563)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.0025667383678440532), np.float64(0.9724840625144939)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.01833365639489696), np.float64(0.9236779538393038)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.020482955806791856), np.float64(0.9595423039398718)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.018256757966880106), np.float64(0.9830123264551605)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.17763099895872753), np.float64(0.9321521654818063)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.006857999280727054), np.float64(0.07989431420050044)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.009713489375256911), np.float64(0.0558935996787181)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.007270931265350187), np.float64(0.16037506604294297)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.003453289082176602), np.float64(0.40008454651275627)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.001498670808325031), np.float64(0.8327908687782624)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.003942226176048748), np.float64(0.7611295399790237)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.00640026002804715), np.float64(0.8343223096412796)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.018172026884200443), np.float64(0.7608168398427946)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.026345921349457596), np.float64(0.8510735127263772)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.14312031278816612), np.float64(0.5924151124330418)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.0005546078035339267), np.float64(0.7137318333690449)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.0004957960093099087), np.float64(0.7687210203362217)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.0004277302365397221), np.float64(0.8123881820625675)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.0005030957271188268), np.float64(0.817515939569168)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.0009197271968702862), np.float64(0.7207830350592757)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.0012280020859428828), np.float64(0.689292614901583)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.0011195883353350802), np.float64(0.7892881868944079)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.0018509933688420075), np.float64(0.7431410435982803)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.007388302085531288), np.float64(0.3982514565761293)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.008198376280716476), np.float64(0.46053010214385176)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-2.0691159190534756), np.float64(0.03884916316380829)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-1.7151639246231083), np.float64(0.08669435632615762)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-1.4215400031358747), np.float64(0.15554143008990698)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-1.113826387640768), np.float64(0.26568124555168354)]</t>
+  </si>
+  <si>
+    <t>[np.float64(1.0931828674381685), np.float64(0.274635738581285)]</t>
+  </si>
+  <si>
+    <t>[np.float64(2.0686167804058164), np.float64(0.03889614008320044)]</t>
+  </si>
+  <si>
+    <t>[np.float64(2.4820062068666817), np.float64(0.013264453685887339)]</t>
+  </si>
+  <si>
+    <t>[np.float64(2.5562089401437875), np.float64(0.010761792397710837)]</t>
+  </si>
+  <si>
+    <t>[np.float64(2.519692303900614), np.float64(0.011935391728537336)]</t>
+  </si>
+  <si>
+    <t>[np.float64(2.7016099645569542), np.float64(0.007043487726707048)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-2.383582165677948), np.float64(0.017372572772258857)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-1.722977593828031), np.float64(0.08527096718051623)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.937898541839189), np.float64(0.3485737252611945)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.676693018556021), np.float64(0.4987922820897803)]</t>
+  </si>
+  <si>
+    <t>[np.float64(1.4267534130390933), np.float64(0.15403301727408486)]</t>
+  </si>
+  <si>
+    <t>[np.float64(1.9321224689645098), np.float64(0.053689835829487546)]</t>
+  </si>
+  <si>
+    <t>[np.float64(1.8433268913616434), np.float64(0.06564333245805193)]</t>
+  </si>
+  <si>
+    <t>[np.float64(1.8582443711870342), np.float64(0.06349381487040184)]</t>
+  </si>
+  <si>
+    <t>[np.float64(1.9936920755122634), np.float64(0.046517776420612895)]</t>
+  </si>
+  <si>
+    <t>[np.float64(1.9249700073060194), np.float64(0.0545800161634754)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-2.887960943573834), np.float64(0.003979900880958809)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-2.55413086548119), np.float64(0.01082571345614148)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-2.3130350248020286), np.float64(0.020968258045896124)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-1.501314799221408), np.float64(0.1336605228180827)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.5044527148307816), np.float64(0.6140793011549592)]</t>
+  </si>
+  <si>
+    <t>[np.float64(1.530137897430654), np.float64(0.12636967743018682)]</t>
+  </si>
+  <si>
+    <t>[np.float64(3.2274312271680996), np.float64(0.0012988606009339632)]</t>
+  </si>
+  <si>
+    <t>[np.float64(3.667894321042078), np.float64(0.0002603967599498271)]</t>
+  </si>
+  <si>
+    <t>[np.float64(4.212491391298942), np.float64(2.8067642322059735e-05)]</t>
+  </si>
+  <si>
+    <t>[np.float64(4.201042833124145), np.float64(2.9493709433001735e-05)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-2.282790216112952), np.float64(0.022698847340389808)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-1.917326557920498), np.float64(0.05554490241585829)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-1.6491774029682287), np.float64(0.09949571175374237)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.7354102488627805), np.float64(0.4623007380393652)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.492387252281739), np.float64(0.6225778953295262)]</t>
+  </si>
+  <si>
+    <t>[np.float64(1.3112748696636403), np.float64(0.19013331634490097)]</t>
+  </si>
+  <si>
+    <t>[np.float64(1.705958594251199), np.float64(0.08839585307720205)]</t>
+  </si>
+  <si>
+    <t>[np.float64(1.7558424392770324), np.float64(0.0794900086041064)]</t>
+  </si>
+  <si>
+    <t>[np.float64(1.912719528190924), np.float64(0.05613332818161418)]</t>
+  </si>
+  <si>
+    <t>[np.float64(1.7299465865554189), np.float64(0.08401747569365196)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-2.1362064302641506), np.float64(0.03295918726049869)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-2.00677879313547), np.float64(0.04510226541393788)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-1.7958908031465233), np.float64(0.0728812747058526)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-1.286543053806983), np.float64(0.19861803582229015)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.7484402686071573), np.float64(0.45441003879301217)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.046753827190213426), np.float64(0.9627208550068279)]</t>
+  </si>
+  <si>
+    <t>[np.float64(1.2318463165151152), np.float64(0.21836092171704946)]</t>
+  </si>
+  <si>
+    <t>[np.float64(2.013184731181292), np.float64(0.04442274533365733)]</t>
+  </si>
+  <si>
+    <t>[np.float64(2.4111730544230294), np.float64(0.016121022028928282)]</t>
+  </si>
+  <si>
+    <t>[np.float64(2.5145613544303407), np.float64(0.012109095071980349)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-1.4341164122708812), np.float64(0.15192166491281411)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-1.3460367211129733), np.float64(0.17866404094639132)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-1.296044733219902), np.float64(0.19532607305244362)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-1.0744128585423571), np.float64(0.2829548888325427)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.9487112667316275), np.float64(0.3430480162786125)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.9102041659285912), np.float64(0.3629832958357629)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.6968161563544906), np.float64(0.486116064652148)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.507322132308427), np.float64(0.612065721963775)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.020732375290880258), np.float64(0.9834642049542762)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.1486284927784864), np.float64(0.881883464986484)]</t>
+  </si>
+  <si>
+    <t>Returns</t>
   </si>
 </sst>
 </file>
@@ -1506,10 +2792,6169 @@
         <v>44</v>
       </c>
       <c r="V12" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="W12" t="s">
-        <v>44</v>
+        <v>46</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:P61"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:16">
+      <c r="B1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1" t="s">
+        <v>47</v>
+      </c>
+      <c r="G1" t="s">
+        <v>48</v>
+      </c>
+      <c r="H1" t="s">
+        <v>49</v>
+      </c>
+      <c r="I1" t="s">
+        <v>50</v>
+      </c>
+      <c r="J1" t="s">
+        <v>36</v>
+      </c>
+      <c r="K1" t="s">
+        <v>37</v>
+      </c>
+      <c r="L1" t="s">
+        <v>38</v>
+      </c>
+      <c r="M1" t="s">
+        <v>39</v>
+      </c>
+      <c r="N1" t="s">
+        <v>40</v>
+      </c>
+      <c r="O1" t="s">
+        <v>41</v>
+      </c>
+      <c r="P1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C2">
+        <v>0.0006489562854946995</v>
+      </c>
+      <c r="D2">
+        <v>-0.00272751459851861</v>
+      </c>
+      <c r="E2">
+        <v>0.04451280832290649</v>
+      </c>
+      <c r="F2">
+        <v>0.0008142940350808203</v>
+      </c>
+      <c r="G2">
+        <v>0.0008870551246218383</v>
+      </c>
+      <c r="H2">
+        <v>1.000498667071587</v>
+      </c>
+      <c r="I2">
+        <v>0.04898464745335985</v>
+      </c>
+      <c r="J2">
+        <v>-0.06127482652664185</v>
+      </c>
+      <c r="K2">
+        <v>-0.9998699426651001</v>
+      </c>
+      <c r="L2">
+        <v>2.54775071144104</v>
+      </c>
+      <c r="M2">
+        <v>-3.507147550582886</v>
+      </c>
+      <c r="N2" t="s">
+        <v>111</v>
+      </c>
+      <c r="O2" t="s">
+        <v>171</v>
+      </c>
+      <c r="P2" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16">
+      <c r="A3">
+        <v>0</v>
+      </c>
+      <c r="B3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C3">
+        <v>0.0008627227457982943</v>
+      </c>
+      <c r="D3">
+        <v>-0.003152419114485383</v>
+      </c>
+      <c r="E3">
+        <v>0.05936579778790474</v>
+      </c>
+      <c r="F3">
+        <v>0.000937557895667851</v>
+      </c>
+      <c r="G3">
+        <v>0.0009736670763231814</v>
+      </c>
+      <c r="H3">
+        <v>1.000711352520691</v>
+      </c>
+      <c r="I3">
+        <v>0.04895578998244713</v>
+      </c>
+      <c r="J3">
+        <v>-0.05310160294175148</v>
+      </c>
+      <c r="K3">
+        <v>-0.9999678134918213</v>
+      </c>
+      <c r="L3">
+        <v>3.397881746292114</v>
+      </c>
+      <c r="M3">
+        <v>-3.039341926574707</v>
+      </c>
+      <c r="N3" t="s">
+        <v>112</v>
+      </c>
+      <c r="O3" t="s">
+        <v>172</v>
+      </c>
+      <c r="P3" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16">
+      <c r="A4">
+        <v>0</v>
+      </c>
+      <c r="B4" t="s">
+        <v>53</v>
+      </c>
+      <c r="C4">
+        <v>0.001074498078101334</v>
+      </c>
+      <c r="D4">
+        <v>-0.001247276784852147</v>
+      </c>
+      <c r="E4">
+        <v>0.03339485079050064</v>
+      </c>
+      <c r="F4">
+        <v>0.001039808266796172</v>
+      </c>
+      <c r="G4">
+        <v>0.001065933261997998</v>
+      </c>
+      <c r="H4">
+        <v>1.0008189660606</v>
+      </c>
+      <c r="I4">
+        <v>0.04890893210529241</v>
+      </c>
+      <c r="J4">
+        <v>-0.03734937310218811</v>
+      </c>
+      <c r="K4">
+        <v>-0.9832383394241333</v>
+      </c>
+      <c r="L4">
+        <v>1.911399364471436</v>
+      </c>
+      <c r="M4">
+        <v>-2.137741804122925</v>
+      </c>
+      <c r="N4" t="s">
+        <v>113</v>
+      </c>
+      <c r="O4" t="s">
+        <v>173</v>
+      </c>
+      <c r="P4" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16">
+      <c r="A5">
+        <v>0</v>
+      </c>
+      <c r="B5" t="s">
+        <v>54</v>
+      </c>
+      <c r="C5">
+        <v>0.002110896305672595</v>
+      </c>
+      <c r="D5">
+        <v>-0.001530286390334368</v>
+      </c>
+      <c r="E5">
+        <v>0.0666949674487114</v>
+      </c>
+      <c r="F5">
+        <v>0.001366736250929534</v>
+      </c>
+      <c r="G5">
+        <v>0.001289737643674016</v>
+      </c>
+      <c r="H5">
+        <v>1.000991456181977</v>
+      </c>
+      <c r="I5">
+        <v>0.04897115398303527</v>
+      </c>
+      <c r="J5">
+        <v>-0.02294455654919147</v>
+      </c>
+      <c r="K5">
+        <v>-0.9933760762214661</v>
+      </c>
+      <c r="L5">
+        <v>3.817376613616943</v>
+      </c>
+      <c r="M5">
+        <v>-1.313262701034546</v>
+      </c>
+      <c r="N5" t="s">
+        <v>114</v>
+      </c>
+      <c r="O5" t="s">
+        <v>174</v>
+      </c>
+      <c r="P5" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16">
+      <c r="A6">
+        <v>0</v>
+      </c>
+      <c r="B6" t="s">
+        <v>55</v>
+      </c>
+      <c r="C6">
+        <v>0.004144393646722697</v>
+      </c>
+      <c r="D6">
+        <v>0.00210663746111095</v>
+      </c>
+      <c r="E6">
+        <v>0.02414033561944962</v>
+      </c>
+      <c r="F6">
+        <v>0.001641415758058429</v>
+      </c>
+      <c r="G6">
+        <v>0.001516166841611266</v>
+      </c>
+      <c r="H6">
+        <v>1.001060903539771</v>
+      </c>
+      <c r="I6">
+        <v>0.04912687428620994</v>
+      </c>
+      <c r="J6">
+        <v>0.08726628869771957</v>
+      </c>
+      <c r="K6">
+        <v>985.5167846679688</v>
+      </c>
+      <c r="L6">
+        <v>1.381704688072205</v>
+      </c>
+      <c r="M6">
+        <v>4.994803905487061</v>
+      </c>
+      <c r="N6" t="s">
+        <v>115</v>
+      </c>
+      <c r="O6" t="s">
+        <v>175</v>
+      </c>
+      <c r="P6" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16">
+      <c r="A7">
+        <v>0</v>
+      </c>
+      <c r="B7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C7">
+        <v>0.008180201075460802</v>
+      </c>
+      <c r="D7">
+        <v>0.004424530081450939</v>
+      </c>
+      <c r="E7">
+        <v>0.04835550487041473</v>
+      </c>
+      <c r="F7">
+        <v>0.00189140229485929</v>
+      </c>
+      <c r="G7">
+        <v>0.001797955832444131</v>
+      </c>
+      <c r="H7">
+        <v>1.001120178079407</v>
+      </c>
+      <c r="I7">
+        <v>0.04883684095389589</v>
+      </c>
+      <c r="J7">
+        <v>0.09150002896785736</v>
+      </c>
+      <c r="K7">
+        <v>1910594</v>
+      </c>
+      <c r="L7">
+        <v>2.767692565917969</v>
+      </c>
+      <c r="M7">
+        <v>5.237127780914307</v>
+      </c>
+      <c r="N7" t="s">
+        <v>116</v>
+      </c>
+      <c r="O7" t="s">
+        <v>176</v>
+      </c>
+      <c r="P7" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16">
+      <c r="A8">
+        <v>0</v>
+      </c>
+      <c r="B8" t="s">
+        <v>57</v>
+      </c>
+      <c r="C8">
+        <v>0.02017702605310936</v>
+      </c>
+      <c r="D8">
+        <v>0.01112701464444399</v>
+      </c>
+      <c r="E8">
+        <v>0.120678074657917</v>
+      </c>
+      <c r="F8">
+        <v>0.002234698738902807</v>
+      </c>
+      <c r="G8">
+        <v>0.002263986272737384</v>
+      </c>
+      <c r="H8">
+        <v>1.001499285212445</v>
+      </c>
+      <c r="I8">
+        <v>0.04955486610177292</v>
+      </c>
+      <c r="J8">
+        <v>0.09220410883426666</v>
+      </c>
+      <c r="K8">
+        <v>5539756729434112</v>
+      </c>
+      <c r="L8">
+        <v>6.907172679901123</v>
+      </c>
+      <c r="M8">
+        <v>5.277426719665527</v>
+      </c>
+      <c r="N8" t="s">
+        <v>117</v>
+      </c>
+      <c r="O8" t="s">
+        <v>177</v>
+      </c>
+      <c r="P8" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16">
+      <c r="A9">
+        <v>0</v>
+      </c>
+      <c r="B9" t="s">
+        <v>58</v>
+      </c>
+      <c r="C9">
+        <v>0.04012992265103704</v>
+      </c>
+      <c r="D9">
+        <v>0.02207440137863159</v>
+      </c>
+      <c r="E9">
+        <v>0.2413547337055206</v>
+      </c>
+      <c r="F9">
+        <v>0.002449276391416788</v>
+      </c>
+      <c r="G9">
+        <v>0.002570094540715218</v>
+      </c>
+      <c r="H9">
+        <v>1.00177247848752</v>
+      </c>
+      <c r="I9">
+        <v>0.05019940399832536</v>
+      </c>
+      <c r="J9">
+        <v>0.09146040678024292</v>
+      </c>
+      <c r="K9">
+        <v>1.160886129857693E+31</v>
+      </c>
+      <c r="L9">
+        <v>13.81426429748535</v>
+      </c>
+      <c r="M9">
+        <v>5.234859943389893</v>
+      </c>
+      <c r="N9" t="s">
+        <v>118</v>
+      </c>
+      <c r="O9" t="s">
+        <v>178</v>
+      </c>
+      <c r="P9" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16">
+      <c r="A10">
+        <v>0</v>
+      </c>
+      <c r="B10" t="s">
+        <v>59</v>
+      </c>
+      <c r="C10">
+        <v>0.1009122827015687</v>
+      </c>
+      <c r="D10">
+        <v>0.05475205183029175</v>
+      </c>
+      <c r="E10">
+        <v>0.6162889003753662</v>
+      </c>
+      <c r="F10">
+        <v>0.002690139692276716</v>
+      </c>
+      <c r="G10">
+        <v>0.003015485359355807</v>
+      </c>
+      <c r="H10">
+        <v>1.002390026334335</v>
+      </c>
+      <c r="I10">
+        <v>0.05598150961590734</v>
+      </c>
+      <c r="J10">
+        <v>0.08884153515100479</v>
+      </c>
+      <c r="K10" t="s">
+        <v>110</v>
+      </c>
+      <c r="L10">
+        <v>35.27412796020508</v>
+      </c>
+      <c r="M10">
+        <v>5.084965229034424</v>
+      </c>
+      <c r="N10" t="s">
+        <v>119</v>
+      </c>
+      <c r="O10" t="s">
+        <v>179</v>
+      </c>
+      <c r="P10" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16">
+      <c r="A11">
+        <v>0</v>
+      </c>
+      <c r="B11" t="s">
+        <v>60</v>
+      </c>
+      <c r="C11">
+        <v>0.1944929280247392</v>
+      </c>
+      <c r="D11">
+        <v>0.1051542013883591</v>
+      </c>
+      <c r="E11">
+        <v>1.12047290802002</v>
+      </c>
+      <c r="F11">
+        <v>0.002925543813034892</v>
+      </c>
+      <c r="G11">
+        <v>0.00344734382815659</v>
+      </c>
+      <c r="H11">
+        <v>1.003549571603427</v>
+      </c>
+      <c r="I11">
+        <v>0.06545946019335863</v>
+      </c>
+      <c r="J11">
+        <v>0.09384805709123611</v>
+      </c>
+      <c r="K11" t="s">
+        <v>110</v>
+      </c>
+      <c r="L11">
+        <v>64.13178253173828</v>
+      </c>
+      <c r="M11">
+        <v>5.371520519256592</v>
+      </c>
+      <c r="N11" t="s">
+        <v>120</v>
+      </c>
+      <c r="O11" t="s">
+        <v>180</v>
+      </c>
+      <c r="P11" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16">
+      <c r="A12">
+        <v>0</v>
+      </c>
+      <c r="B12" t="s">
+        <v>61</v>
+      </c>
+      <c r="C12">
+        <v>0.001271853898710877</v>
+      </c>
+      <c r="D12">
+        <v>-0.0002970764471683651</v>
+      </c>
+      <c r="E12">
+        <v>0.01176009513437748</v>
+      </c>
+      <c r="F12">
+        <v>0.0008421452948823571</v>
+      </c>
+      <c r="G12">
+        <v>0.0009055301197804511</v>
+      </c>
+      <c r="H12">
+        <v>1.000445228954681</v>
+      </c>
+      <c r="I12">
+        <v>0.0490134375316143</v>
+      </c>
+      <c r="J12">
+        <v>-0.02526139840483665</v>
+      </c>
+      <c r="K12">
+        <v>-0.6221826672554016</v>
+      </c>
+      <c r="L12">
+        <v>0.6731049418449402</v>
+      </c>
+      <c r="M12">
+        <v>-1.445870280265808</v>
+      </c>
+      <c r="N12" t="s">
+        <v>121</v>
+      </c>
+      <c r="O12" t="s">
+        <v>181</v>
+      </c>
+      <c r="P12" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16">
+      <c r="A13">
+        <v>0</v>
+      </c>
+      <c r="B13" t="s">
+        <v>62</v>
+      </c>
+      <c r="C13">
+        <v>0.001692371177052601</v>
+      </c>
+      <c r="D13">
+        <v>0.0001957038330147043</v>
+      </c>
+      <c r="E13">
+        <v>0.01529214717447758</v>
+      </c>
+      <c r="F13">
+        <v>0.000973308167885989</v>
+      </c>
+      <c r="G13">
+        <v>0.0009888614295050502</v>
+      </c>
+      <c r="H13">
+        <v>1.000623263643984</v>
+      </c>
+      <c r="I13">
+        <v>0.04901757486652551</v>
+      </c>
+      <c r="J13">
+        <v>0.01279766857624054</v>
+      </c>
+      <c r="K13">
+        <v>0.8987331390380859</v>
+      </c>
+      <c r="L13">
+        <v>0.8752667307853699</v>
+      </c>
+      <c r="M13">
+        <v>0.7324918508529663</v>
+      </c>
+      <c r="N13" t="s">
+        <v>122</v>
+      </c>
+      <c r="O13" t="s">
+        <v>182</v>
+      </c>
+      <c r="P13" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16">
+      <c r="A14">
+        <v>0</v>
+      </c>
+      <c r="B14" t="s">
+        <v>63</v>
+      </c>
+      <c r="C14">
+        <v>0.002110234043637722</v>
+      </c>
+      <c r="D14">
+        <v>0.0007454555016011</v>
+      </c>
+      <c r="E14">
+        <v>0.01813148893415928</v>
+      </c>
+      <c r="F14">
+        <v>0.001083908136934042</v>
+      </c>
+      <c r="G14">
+        <v>0.001088045770302415</v>
+      </c>
+      <c r="H14">
+        <v>1.000719428335878</v>
+      </c>
+      <c r="I14">
+        <v>0.04903055153958815</v>
+      </c>
+      <c r="J14">
+        <v>0.04111386090517044</v>
+      </c>
+      <c r="K14">
+        <v>10.48534774780273</v>
+      </c>
+      <c r="L14">
+        <v>1.037780284881592</v>
+      </c>
+      <c r="M14">
+        <v>2.353207349777222</v>
+      </c>
+      <c r="N14" t="s">
+        <v>123</v>
+      </c>
+      <c r="O14" t="s">
+        <v>183</v>
+      </c>
+      <c r="P14" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16">
+      <c r="A15">
+        <v>0</v>
+      </c>
+      <c r="B15" t="s">
+        <v>64</v>
+      </c>
+      <c r="C15">
+        <v>0.004180124447797706</v>
+      </c>
+      <c r="D15">
+        <v>0.002155152149498463</v>
+      </c>
+      <c r="E15">
+        <v>0.03618983551859856</v>
+      </c>
+      <c r="F15">
+        <v>0.001404242007993162</v>
+      </c>
+      <c r="G15">
+        <v>0.001330580329522491</v>
+      </c>
+      <c r="H15">
+        <v>1.000898860137178</v>
+      </c>
+      <c r="I15">
+        <v>0.04902106792906804</v>
+      </c>
+      <c r="J15">
+        <v>0.05955130979418755</v>
+      </c>
+      <c r="K15">
+        <v>1155.077270507812</v>
+      </c>
+      <c r="L15">
+        <v>2.071374177932739</v>
+      </c>
+      <c r="M15">
+        <v>3.408499717712402</v>
+      </c>
+      <c r="N15" t="s">
+        <v>124</v>
+      </c>
+      <c r="O15" t="s">
+        <v>184</v>
+      </c>
+      <c r="P15" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16">
+      <c r="A16">
+        <v>0</v>
+      </c>
+      <c r="B16" t="s">
+        <v>65</v>
+      </c>
+      <c r="C16">
+        <v>0.008275241257172574</v>
+      </c>
+      <c r="D16">
+        <v>0.004621425177901983</v>
+      </c>
+      <c r="E16">
+        <v>0.07219464331865311</v>
+      </c>
+      <c r="F16">
+        <v>0.001685747061856091</v>
+      </c>
+      <c r="G16">
+        <v>0.001563900616019964</v>
+      </c>
+      <c r="H16">
+        <v>1.00097351463223</v>
+      </c>
+      <c r="I16">
+        <v>0.04916243438416142</v>
+      </c>
+      <c r="J16">
+        <v>0.06401340663433075</v>
+      </c>
+      <c r="K16">
+        <v>3630156.25</v>
+      </c>
+      <c r="L16">
+        <v>4.132157802581787</v>
+      </c>
+      <c r="M16">
+        <v>3.663893699645996</v>
+      </c>
+      <c r="N16" t="s">
+        <v>125</v>
+      </c>
+      <c r="O16" t="s">
+        <v>185</v>
+      </c>
+      <c r="P16" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16">
+      <c r="A17">
+        <v>0</v>
+      </c>
+      <c r="B17" t="s">
+        <v>66</v>
+      </c>
+      <c r="C17">
+        <v>0.01637871267090393</v>
+      </c>
+      <c r="D17">
+        <v>0.009512928314507008</v>
+      </c>
+      <c r="E17">
+        <v>0.1435531824827194</v>
+      </c>
+      <c r="F17">
+        <v>0.001942820148542523</v>
+      </c>
+      <c r="G17">
+        <v>0.00184637971688062</v>
+      </c>
+      <c r="H17">
+        <v>1.001080919839276</v>
+      </c>
+      <c r="I17">
+        <v>0.04887937638917519</v>
+      </c>
+      <c r="J17">
+        <v>0.06626762449741364</v>
+      </c>
+      <c r="K17">
+        <v>29545920987136</v>
+      </c>
+      <c r="L17">
+        <v>8.216460227966309</v>
+      </c>
+      <c r="M17">
+        <v>3.792917013168335</v>
+      </c>
+      <c r="N17" t="s">
+        <v>126</v>
+      </c>
+      <c r="O17" t="s">
+        <v>186</v>
+      </c>
+      <c r="P17" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16">
+      <c r="A18">
+        <v>0</v>
+      </c>
+      <c r="B18" t="s">
+        <v>67</v>
+      </c>
+      <c r="C18">
+        <v>0.0407412072111796</v>
+      </c>
+      <c r="D18">
+        <v>0.02382531017065048</v>
+      </c>
+      <c r="E18">
+        <v>0.3600844442844391</v>
+      </c>
+      <c r="F18">
+        <v>0.002265958115458488</v>
+      </c>
+      <c r="G18">
+        <v>0.002284314716234803</v>
+      </c>
+      <c r="H18">
+        <v>1.00135507732144</v>
+      </c>
+      <c r="I18">
+        <v>0.04957500159494027</v>
+      </c>
+      <c r="J18">
+        <v>0.06616589426994324</v>
+      </c>
+      <c r="K18">
+        <v>3.161488410528183E+33</v>
+      </c>
+      <c r="L18">
+        <v>20.60992050170898</v>
+      </c>
+      <c r="M18">
+        <v>3.787094354629517</v>
+      </c>
+      <c r="N18" t="s">
+        <v>127</v>
+      </c>
+      <c r="O18" t="s">
+        <v>187</v>
+      </c>
+      <c r="P18" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16">
+      <c r="A19">
+        <v>0</v>
+      </c>
+      <c r="B19" t="s">
+        <v>68</v>
+      </c>
+      <c r="C19">
+        <v>0.08025253826334208</v>
+      </c>
+      <c r="D19">
+        <v>0.04692748188972473</v>
+      </c>
+      <c r="E19">
+        <v>0.7058046460151672</v>
+      </c>
+      <c r="F19">
+        <v>0.002467099810019135</v>
+      </c>
+      <c r="G19">
+        <v>0.002597420010715723</v>
+      </c>
+      <c r="H19">
+        <v>1.00171644153203</v>
+      </c>
+      <c r="I19">
+        <v>0.05012967222080539</v>
+      </c>
+      <c r="J19">
+        <v>0.06648791581392288</v>
+      </c>
+      <c r="K19" t="s">
+        <v>110</v>
+      </c>
+      <c r="L19">
+        <v>40.39768218994141</v>
+      </c>
+      <c r="M19">
+        <v>3.805525779724121</v>
+      </c>
+      <c r="N19" t="s">
+        <v>128</v>
+      </c>
+      <c r="O19" t="s">
+        <v>188</v>
+      </c>
+      <c r="P19" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16">
+      <c r="A20">
+        <v>0</v>
+      </c>
+      <c r="B20" t="s">
+        <v>69</v>
+      </c>
+      <c r="C20">
+        <v>0.2025295094596681</v>
+      </c>
+      <c r="D20">
+        <v>0.1168944090604782</v>
+      </c>
+      <c r="E20">
+        <v>1.797990083694458</v>
+      </c>
+      <c r="F20">
+        <v>0.002730359556153417</v>
+      </c>
+      <c r="G20">
+        <v>0.003136329585686326</v>
+      </c>
+      <c r="H20">
+        <v>1.002390026334335</v>
+      </c>
+      <c r="I20">
+        <v>0.05598150961590734</v>
+      </c>
+      <c r="J20">
+        <v>0.06501393765211105</v>
+      </c>
+      <c r="K20" t="s">
+        <v>110</v>
+      </c>
+      <c r="L20">
+        <v>102.9103927612305</v>
+      </c>
+      <c r="M20">
+        <v>3.721160650253296</v>
+      </c>
+      <c r="N20" t="s">
+        <v>129</v>
+      </c>
+      <c r="O20" t="s">
+        <v>189</v>
+      </c>
+      <c r="P20" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16">
+      <c r="A21">
+        <v>0</v>
+      </c>
+      <c r="B21" t="s">
+        <v>70</v>
+      </c>
+      <c r="C21">
+        <v>0.3874753291197571</v>
+      </c>
+      <c r="D21">
+        <v>0.2245352268218994</v>
+      </c>
+      <c r="E21">
+        <v>3.299152135848999</v>
+      </c>
+      <c r="F21">
+        <v>0.002912175608798862</v>
+      </c>
+      <c r="G21">
+        <v>0.003422800684347749</v>
+      </c>
+      <c r="H21">
+        <v>1.003549571603427</v>
+      </c>
+      <c r="I21">
+        <v>0.06545946019335863</v>
+      </c>
+      <c r="J21">
+        <v>0.06805846095085144</v>
+      </c>
+      <c r="K21" t="s">
+        <v>110</v>
+      </c>
+      <c r="L21">
+        <v>188.8314361572266</v>
+      </c>
+      <c r="M21">
+        <v>3.895417928695679</v>
+      </c>
+      <c r="N21" t="s">
+        <v>130</v>
+      </c>
+      <c r="O21" t="s">
+        <v>190</v>
+      </c>
+      <c r="P21" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16">
+      <c r="A22">
+        <v>0</v>
+      </c>
+      <c r="B22" t="s">
+        <v>71</v>
+      </c>
+      <c r="C22">
+        <v>0.0002916228310618378</v>
+      </c>
+      <c r="D22">
+        <v>-0.0005341224605217576</v>
+      </c>
+      <c r="E22">
+        <v>0.001557938172481954</v>
+      </c>
+      <c r="F22">
+        <v>0.0008586779003962874</v>
+      </c>
+      <c r="G22">
+        <v>0.0009144709329120815</v>
+      </c>
+      <c r="H22">
+        <v>1.000385146103818</v>
+      </c>
+      <c r="I22">
+        <v>0.04904638919282042</v>
+      </c>
+      <c r="J22">
+        <v>-0.3428393304347992</v>
+      </c>
+      <c r="K22">
+        <v>-0.8262670040130615</v>
+      </c>
+      <c r="L22">
+        <v>0.08917069435119629</v>
+      </c>
+      <c r="M22">
+        <v>-19.62287139892578</v>
+      </c>
+      <c r="N22" t="s">
+        <v>131</v>
+      </c>
+      <c r="O22" t="s">
+        <v>191</v>
+      </c>
+      <c r="P22" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16">
+      <c r="A23">
+        <v>0</v>
+      </c>
+      <c r="B23" t="s">
+        <v>72</v>
+      </c>
+      <c r="C23">
+        <v>0.0003842219568673803</v>
+      </c>
+      <c r="D23">
+        <v>-0.0003342698037158698</v>
+      </c>
+      <c r="E23">
+        <v>0.001694523263722658</v>
+      </c>
+      <c r="F23">
+        <v>0.001009350758977234</v>
+      </c>
+      <c r="G23">
+        <v>0.001008119899779558</v>
+      </c>
+      <c r="H23">
+        <v>1.000587048283798</v>
+      </c>
+      <c r="I23">
+        <v>0.04903511434975312</v>
+      </c>
+      <c r="J23">
+        <v>-0.1972648054361343</v>
+      </c>
+      <c r="K23">
+        <v>-0.6655367016792297</v>
+      </c>
+      <c r="L23">
+        <v>0.09698832780122757</v>
+      </c>
+      <c r="M23">
+        <v>-11.29071807861328</v>
+      </c>
+      <c r="N23" t="s">
+        <v>132</v>
+      </c>
+      <c r="O23" t="s">
+        <v>192</v>
+      </c>
+      <c r="P23" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="24" spans="1:16">
+      <c r="A24">
+        <v>0</v>
+      </c>
+      <c r="B24" t="s">
+        <v>73</v>
+      </c>
+      <c r="C24">
+        <v>0.00047377278169768</v>
+      </c>
+      <c r="D24">
+        <v>-0.0001949756406247616</v>
+      </c>
+      <c r="E24">
+        <v>0.001991864992305636</v>
+      </c>
+      <c r="F24">
+        <v>0.001118695479817688</v>
+      </c>
+      <c r="G24">
+        <v>0.001105327974073589</v>
+      </c>
+      <c r="H24">
+        <v>1.000661138279478</v>
+      </c>
+      <c r="I24">
+        <v>0.04902979652171693</v>
+      </c>
+      <c r="J24">
+        <v>-0.09788597375154495</v>
+      </c>
+      <c r="K24">
+        <v>-0.4720604419708252</v>
+      </c>
+      <c r="L24">
+        <v>0.1140070855617523</v>
+      </c>
+      <c r="M24">
+        <v>-5.602635860443115</v>
+      </c>
+      <c r="N24" t="s">
+        <v>133</v>
+      </c>
+      <c r="O24" t="s">
+        <v>193</v>
+      </c>
+      <c r="P24" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="25" spans="1:16">
+      <c r="A25">
+        <v>0</v>
+      </c>
+      <c r="B25" t="s">
+        <v>74</v>
+      </c>
+      <c r="C25">
+        <v>0.0008979150210120929</v>
+      </c>
+      <c r="D25">
+        <v>0.0002349815185880288</v>
+      </c>
+      <c r="E25">
+        <v>0.003553028916940093</v>
+      </c>
+      <c r="F25">
+        <v>0.001442242646589875</v>
+      </c>
+      <c r="G25">
+        <v>0.001345796277746558</v>
+      </c>
+      <c r="H25">
+        <v>1.000779403822832</v>
+      </c>
+      <c r="I25">
+        <v>0.04907581461688444</v>
+      </c>
+      <c r="J25">
+        <v>0.06613554805517197</v>
+      </c>
+      <c r="K25">
+        <v>1.158996343612671</v>
+      </c>
+      <c r="L25">
+        <v>0.2033624053001404</v>
+      </c>
+      <c r="M25">
+        <v>3.785357475280762</v>
+      </c>
+      <c r="N25" t="s">
+        <v>134</v>
+      </c>
+      <c r="O25" t="s">
+        <v>194</v>
+      </c>
+      <c r="P25" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="26" spans="1:16">
+      <c r="A26">
+        <v>0</v>
+      </c>
+      <c r="B26" t="s">
+        <v>75</v>
+      </c>
+      <c r="C26">
+        <v>0.00170312132670721</v>
+      </c>
+      <c r="D26">
+        <v>0.0007784951594658196</v>
+      </c>
+      <c r="E26">
+        <v>0.006827003788203001</v>
+      </c>
+      <c r="F26">
+        <v>0.001706059207208455</v>
+      </c>
+      <c r="G26">
+        <v>0.001588835963048041</v>
+      </c>
+      <c r="H26">
+        <v>1.000824731935867</v>
+      </c>
+      <c r="I26">
+        <v>0.04920461453639326</v>
+      </c>
+      <c r="J26">
+        <v>0.1140317469835281</v>
+      </c>
+      <c r="K26">
+        <v>11.79643249511719</v>
+      </c>
+      <c r="L26">
+        <v>0.3907527923583984</v>
+      </c>
+      <c r="M26">
+        <v>6.526761054992676</v>
+      </c>
+      <c r="N26" t="s">
+        <v>135</v>
+      </c>
+      <c r="O26" t="s">
+        <v>195</v>
+      </c>
+      <c r="P26" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="27" spans="1:16">
+      <c r="A27">
+        <v>0</v>
+      </c>
+      <c r="B27" t="s">
+        <v>76</v>
+      </c>
+      <c r="C27">
+        <v>0.00326725944428376</v>
+      </c>
+      <c r="D27">
+        <v>0.00186333036981523</v>
+      </c>
+      <c r="E27">
+        <v>0.01194890309125185</v>
+      </c>
+      <c r="F27">
+        <v>0.001967997988685966</v>
+      </c>
+      <c r="G27">
+        <v>0.001923320232890546</v>
+      </c>
+      <c r="H27">
+        <v>1.00088371389221</v>
+      </c>
+      <c r="I27">
+        <v>0.04895669209326105</v>
+      </c>
+      <c r="J27">
+        <v>0.1559415459632874</v>
+      </c>
+      <c r="K27">
+        <v>444.2733764648438</v>
+      </c>
+      <c r="L27">
+        <v>0.6839116215705872</v>
+      </c>
+      <c r="M27">
+        <v>8.925524711608887</v>
+      </c>
+      <c r="N27" t="s">
+        <v>136</v>
+      </c>
+      <c r="O27" t="s">
+        <v>196</v>
+      </c>
+      <c r="P27" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="28" spans="1:16">
+      <c r="A28">
+        <v>0</v>
+      </c>
+      <c r="B28" t="s">
+        <v>77</v>
+      </c>
+      <c r="C28">
+        <v>0.007904496522116375</v>
+      </c>
+      <c r="D28">
+        <v>0.00442524254322052</v>
+      </c>
+      <c r="E28">
+        <v>0.02977568283677101</v>
+      </c>
+      <c r="F28">
+        <v>0.002293302211910486</v>
+      </c>
+      <c r="G28">
+        <v>0.002343410160392523</v>
+      </c>
+      <c r="H28">
+        <v>1.001327293621854</v>
+      </c>
+      <c r="I28">
+        <v>0.04964785490252448</v>
+      </c>
+      <c r="J28">
+        <v>0.1486193537712097</v>
+      </c>
+      <c r="K28">
+        <v>1915056.375</v>
+      </c>
+      <c r="L28">
+        <v>1.704251408576965</v>
+      </c>
+      <c r="M28">
+        <v>8.506429672241211</v>
+      </c>
+      <c r="N28" t="s">
+        <v>137</v>
+      </c>
+      <c r="O28" t="s">
+        <v>197</v>
+      </c>
+      <c r="P28" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="29" spans="1:16">
+      <c r="A29">
+        <v>0</v>
+      </c>
+      <c r="B29" t="s">
+        <v>78</v>
+      </c>
+      <c r="C29">
+        <v>0.0155263827937298</v>
+      </c>
+      <c r="D29">
+        <v>0.008538034744560719</v>
+      </c>
+      <c r="E29">
+        <v>0.0591905266046524</v>
+      </c>
+      <c r="F29">
+        <v>0.002463834593072534</v>
+      </c>
+      <c r="G29">
+        <v>0.002646224340423942</v>
+      </c>
+      <c r="H29">
+        <v>1.001806783666435</v>
+      </c>
+      <c r="I29">
+        <v>0.05020058130583997</v>
+      </c>
+      <c r="J29">
+        <v>0.1442466378211975</v>
+      </c>
+      <c r="K29">
+        <v>1247025823744</v>
+      </c>
+      <c r="L29">
+        <v>3.387849807739258</v>
+      </c>
+      <c r="M29">
+        <v>8.25615119934082</v>
+      </c>
+      <c r="N29" t="s">
+        <v>138</v>
+      </c>
+      <c r="O29" t="s">
+        <v>198</v>
+      </c>
+      <c r="P29" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="30" spans="1:16">
+      <c r="A30">
+        <v>0</v>
+      </c>
+      <c r="B30" t="s">
+        <v>79</v>
+      </c>
+      <c r="C30">
+        <v>0.03838099555085277</v>
+      </c>
+      <c r="D30">
+        <v>0.02171331085264683</v>
+      </c>
+      <c r="E30">
+        <v>0.1424635052680969</v>
+      </c>
+      <c r="F30">
+        <v>0.002693106420338154</v>
+      </c>
+      <c r="G30">
+        <v>0.003153375815600157</v>
+      </c>
+      <c r="H30">
+        <v>1.002390026334335</v>
+      </c>
+      <c r="I30">
+        <v>0.05581022428338915</v>
+      </c>
+      <c r="J30">
+        <v>0.1524131447076797</v>
+      </c>
+      <c r="K30">
+        <v>3.646675773371835E+30</v>
+      </c>
+      <c r="L30">
+        <v>8.154090881347656</v>
+      </c>
+      <c r="M30">
+        <v>8.72357177734375</v>
+      </c>
+      <c r="N30" t="s">
+        <v>139</v>
+      </c>
+      <c r="O30" t="s">
+        <v>199</v>
+      </c>
+      <c r="P30" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="31" spans="1:16">
+      <c r="A31">
+        <v>0</v>
+      </c>
+      <c r="B31" t="s">
+        <v>80</v>
+      </c>
+      <c r="C31">
+        <v>0.07550170717279617</v>
+      </c>
+      <c r="D31">
+        <v>0.04218887910246849</v>
+      </c>
+      <c r="E31">
+        <v>0.2824690043926239</v>
+      </c>
+      <c r="F31">
+        <v>0.002915629185736179</v>
+      </c>
+      <c r="G31">
+        <v>0.003386245807632804</v>
+      </c>
+      <c r="H31">
+        <v>1.003427172582619</v>
+      </c>
+      <c r="I31">
+        <v>0.06555952123015193</v>
+      </c>
+      <c r="J31">
+        <v>0.1493575572967529</v>
+      </c>
+      <c r="K31" t="s">
+        <v>110</v>
+      </c>
+      <c r="L31">
+        <v>16.16749572753906</v>
+      </c>
+      <c r="M31">
+        <v>8.548681259155273</v>
+      </c>
+      <c r="N31" t="s">
+        <v>140</v>
+      </c>
+      <c r="O31" t="s">
+        <v>200</v>
+      </c>
+      <c r="P31" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="32" spans="1:16">
+      <c r="A32">
+        <v>0</v>
+      </c>
+      <c r="B32" t="s">
+        <v>81</v>
+      </c>
+      <c r="C32">
+        <v>0.0004151987165389204</v>
+      </c>
+      <c r="D32">
+        <v>-0.0001113754115067422</v>
+      </c>
+      <c r="E32">
+        <v>0.003457163227722049</v>
+      </c>
+      <c r="F32">
+        <v>0.000906384433619678</v>
+      </c>
+      <c r="G32">
+        <v>0.0009456852567382157</v>
+      </c>
+      <c r="H32">
+        <v>1.00025426614191</v>
+      </c>
+      <c r="I32">
+        <v>0.04916120659383433</v>
+      </c>
+      <c r="J32">
+        <v>-0.03221583738923073</v>
+      </c>
+      <c r="K32">
+        <v>-0.3057827353477478</v>
+      </c>
+      <c r="L32">
+        <v>0.1978754103183746</v>
+      </c>
+      <c r="M32">
+        <v>-1.843917012214661</v>
+      </c>
+      <c r="N32" t="s">
+        <v>141</v>
+      </c>
+      <c r="O32" t="s">
+        <v>201</v>
+      </c>
+      <c r="P32" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="33" spans="1:16">
+      <c r="A33">
+        <v>0</v>
+      </c>
+      <c r="B33" t="s">
+        <v>82</v>
+      </c>
+      <c r="C33">
+        <v>0.0005467353562597846</v>
+      </c>
+      <c r="D33">
+        <v>4.501263174461201E-05</v>
+      </c>
+      <c r="E33">
+        <v>0.004275826271623373</v>
+      </c>
+      <c r="F33">
+        <v>0.001054043415933847</v>
+      </c>
+      <c r="G33">
+        <v>0.001044702949002385</v>
+      </c>
+      <c r="H33">
+        <v>1.00040973996972</v>
+      </c>
+      <c r="I33">
+        <v>0.0491212297935223</v>
+      </c>
+      <c r="J33">
+        <v>0.01052723545581102</v>
+      </c>
+      <c r="K33">
+        <v>0.1590687036514282</v>
+      </c>
+      <c r="L33">
+        <v>0.2447326928377151</v>
+      </c>
+      <c r="M33">
+        <v>0.6025405526161194</v>
+      </c>
+      <c r="N33" t="s">
+        <v>142</v>
+      </c>
+      <c r="O33" t="s">
+        <v>202</v>
+      </c>
+      <c r="P33" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="34" spans="1:16">
+      <c r="A34">
+        <v>0</v>
+      </c>
+      <c r="B34" t="s">
+        <v>83</v>
+      </c>
+      <c r="C34">
+        <v>0.0006746913795326198</v>
+      </c>
+      <c r="D34">
+        <v>0.0001252431247849017</v>
+      </c>
+      <c r="E34">
+        <v>0.004920781590044498</v>
+      </c>
+      <c r="F34">
+        <v>0.001181162660941482</v>
+      </c>
+      <c r="G34">
+        <v>0.001145208836533129</v>
+      </c>
+      <c r="H34">
+        <v>1.000494473160648</v>
+      </c>
+      <c r="I34">
+        <v>0.04913234547926285</v>
+      </c>
+      <c r="J34">
+        <v>0.02545187622308731</v>
+      </c>
+      <c r="K34">
+        <v>0.507452130317688</v>
+      </c>
+      <c r="L34">
+        <v>0.2816475927829742</v>
+      </c>
+      <c r="M34">
+        <v>1.456772565841675</v>
+      </c>
+      <c r="N34" t="s">
+        <v>143</v>
+      </c>
+      <c r="O34" t="s">
+        <v>203</v>
+      </c>
+      <c r="P34" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="35" spans="1:16">
+      <c r="A35">
+        <v>0</v>
+      </c>
+      <c r="B35" t="s">
+        <v>84</v>
+      </c>
+      <c r="C35">
+        <v>0.001290105695415123</v>
+      </c>
+      <c r="D35">
+        <v>0.0006074167904444039</v>
+      </c>
+      <c r="E35">
+        <v>0.009711002930998802</v>
+      </c>
+      <c r="F35">
+        <v>0.001483182772062719</v>
+      </c>
+      <c r="G35">
+        <v>0.001383733469992876</v>
+      </c>
+      <c r="H35">
+        <v>1.000576151783436</v>
+      </c>
+      <c r="I35">
+        <v>0.04925848257086345</v>
+      </c>
+      <c r="J35">
+        <v>0.06254933774471283</v>
+      </c>
+      <c r="K35">
+        <v>6.309277534484863</v>
+      </c>
+      <c r="L35">
+        <v>0.5558223724365234</v>
+      </c>
+      <c r="M35">
+        <v>3.580095767974854</v>
+      </c>
+      <c r="N35" t="s">
+        <v>144</v>
+      </c>
+      <c r="O35" t="s">
+        <v>204</v>
+      </c>
+      <c r="P35" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="36" spans="1:16">
+      <c r="A36">
+        <v>0</v>
+      </c>
+      <c r="B36" t="s">
+        <v>85</v>
+      </c>
+      <c r="C36">
+        <v>0.002478677329872715</v>
+      </c>
+      <c r="D36">
+        <v>0.001425030874088407</v>
+      </c>
+      <c r="E36">
+        <v>0.01913256570696831</v>
+      </c>
+      <c r="F36">
+        <v>0.001748466165736318</v>
+      </c>
+      <c r="G36">
+        <v>0.001646545249968767</v>
+      </c>
+      <c r="H36">
+        <v>1.000656477049321</v>
+      </c>
+      <c r="I36">
+        <v>0.04938793676852724</v>
+      </c>
+      <c r="J36">
+        <v>0.07448195666074753</v>
+      </c>
+      <c r="K36">
+        <v>105.1728134155273</v>
+      </c>
+      <c r="L36">
+        <v>1.095078229904175</v>
+      </c>
+      <c r="M36">
+        <v>4.263075351715088</v>
+      </c>
+      <c r="N36" t="s">
+        <v>145</v>
+      </c>
+      <c r="O36" t="s">
+        <v>205</v>
+      </c>
+      <c r="P36" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="37" spans="1:16">
+      <c r="A37">
+        <v>0</v>
+      </c>
+      <c r="B37" t="s">
+        <v>86</v>
+      </c>
+      <c r="C37">
+        <v>0.004805983686776916</v>
+      </c>
+      <c r="D37">
+        <v>0.002755812834948301</v>
+      </c>
+      <c r="E37">
+        <v>0.03821425512433052</v>
+      </c>
+      <c r="F37">
+        <v>0.002015324775129557</v>
+      </c>
+      <c r="G37">
+        <v>0.002001747721806169</v>
+      </c>
+      <c r="H37">
+        <v>1.000725728001895</v>
+      </c>
+      <c r="I37">
+        <v>0.04911782304405179</v>
+      </c>
+      <c r="J37">
+        <v>0.07211478799581528</v>
+      </c>
+      <c r="K37">
+        <v>8228.306640625</v>
+      </c>
+      <c r="L37">
+        <v>2.187244415283203</v>
+      </c>
+      <c r="M37">
+        <v>4.12758731842041</v>
+      </c>
+      <c r="N37" t="s">
+        <v>146</v>
+      </c>
+      <c r="O37" t="s">
+        <v>206</v>
+      </c>
+      <c r="P37" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="38" spans="1:16">
+      <c r="A38">
+        <v>0</v>
+      </c>
+      <c r="B38" t="s">
+        <v>87</v>
+      </c>
+      <c r="C38">
+        <v>0.0117290258181497</v>
+      </c>
+      <c r="D38">
+        <v>0.006495381239801645</v>
+      </c>
+      <c r="E38">
+        <v>0.09554632753133774</v>
+      </c>
+      <c r="F38">
+        <v>0.002343357307836413</v>
+      </c>
+      <c r="G38">
+        <v>0.002424548147246242</v>
+      </c>
+      <c r="H38">
+        <v>1.001299101307605</v>
+      </c>
+      <c r="I38">
+        <v>0.04971851649373414</v>
+      </c>
+      <c r="J38">
+        <v>0.06798148155212402</v>
+      </c>
+      <c r="K38">
+        <v>1626960256</v>
+      </c>
+      <c r="L38">
+        <v>5.468723297119141</v>
+      </c>
+      <c r="M38">
+        <v>3.891011953353882</v>
+      </c>
+      <c r="N38" t="s">
+        <v>147</v>
+      </c>
+      <c r="O38" t="s">
+        <v>207</v>
+      </c>
+      <c r="P38" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="39" spans="1:16">
+      <c r="A39">
+        <v>0</v>
+      </c>
+      <c r="B39" t="s">
+        <v>88</v>
+      </c>
+      <c r="C39">
+        <v>0.02321277969874092</v>
+      </c>
+      <c r="D39">
+        <v>0.01260670740157366</v>
+      </c>
+      <c r="E39">
+        <v>0.1911198198795319</v>
+      </c>
+      <c r="F39">
+        <v>0.002456719055771828</v>
+      </c>
+      <c r="G39">
+        <v>0.002719229320064187</v>
+      </c>
+      <c r="H39">
+        <v>1.001778965707161</v>
+      </c>
+      <c r="I39">
+        <v>0.05019527102009144</v>
+      </c>
+      <c r="J39">
+        <v>0.06596232205629349</v>
+      </c>
+      <c r="K39">
+        <v>6.66969388406014E+17</v>
+      </c>
+      <c r="L39">
+        <v>10.93900108337402</v>
+      </c>
+      <c r="M39">
+        <v>3.775442600250244</v>
+      </c>
+      <c r="N39" t="s">
+        <v>148</v>
+      </c>
+      <c r="O39" t="s">
+        <v>208</v>
+      </c>
+      <c r="P39" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="40" spans="1:16">
+      <c r="A40">
+        <v>0</v>
+      </c>
+      <c r="B40" t="s">
+        <v>89</v>
+      </c>
+      <c r="C40">
+        <v>0.05699422617512208</v>
+      </c>
+      <c r="D40">
+        <v>0.03058591671288013</v>
+      </c>
+      <c r="E40">
+        <v>0.4677845239639282</v>
+      </c>
+      <c r="F40">
+        <v>0.002696954645216465</v>
+      </c>
+      <c r="G40">
+        <v>0.003227959387004375</v>
+      </c>
+      <c r="H40">
+        <v>1.002458025790339</v>
+      </c>
+      <c r="I40">
+        <v>0.05577336899009723</v>
+      </c>
+      <c r="J40">
+        <v>0.0653846263885498</v>
+      </c>
+      <c r="K40" t="s">
+        <v>110</v>
+      </c>
+      <c r="L40">
+        <v>26.77427864074707</v>
+      </c>
+      <c r="M40">
+        <v>3.742377519607544</v>
+      </c>
+      <c r="N40" t="s">
+        <v>149</v>
+      </c>
+      <c r="O40" t="s">
+        <v>209</v>
+      </c>
+      <c r="P40" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="41" spans="1:16">
+      <c r="A41">
+        <v>0</v>
+      </c>
+      <c r="B41" t="s">
+        <v>90</v>
+      </c>
+      <c r="C41">
+        <v>0.1217249606192397</v>
+      </c>
+      <c r="D41">
+        <v>0.06455230712890625</v>
+      </c>
+      <c r="E41">
+        <v>1.046587467193604</v>
+      </c>
+      <c r="F41">
+        <v>0.002937576966360211</v>
+      </c>
+      <c r="G41">
+        <v>0.003484579036012292</v>
+      </c>
+      <c r="H41">
+        <v>1.00327417380661</v>
+      </c>
+      <c r="I41">
+        <v>0.06542116701726271</v>
+      </c>
+      <c r="J41">
+        <v>0.06167884543538094</v>
+      </c>
+      <c r="K41" t="s">
+        <v>110</v>
+      </c>
+      <c r="L41">
+        <v>59.90284729003906</v>
+      </c>
+      <c r="M41">
+        <v>3.530272006988525</v>
+      </c>
+      <c r="N41" t="s">
+        <v>150</v>
+      </c>
+      <c r="O41" t="s">
+        <v>210</v>
+      </c>
+      <c r="P41" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="42" spans="1:16">
+      <c r="A42">
+        <v>0</v>
+      </c>
+      <c r="B42" t="s">
+        <v>91</v>
+      </c>
+      <c r="C42">
+        <v>0.000163128305210527</v>
+      </c>
+      <c r="D42">
+        <v>-7.738864951534197E-05</v>
+      </c>
+      <c r="E42">
+        <v>0.001728695002384484</v>
+      </c>
+      <c r="F42">
+        <v>0.00100701954215765</v>
+      </c>
+      <c r="G42">
+        <v>0.001016075257211924</v>
+      </c>
+      <c r="H42">
+        <v>1.000012370534692</v>
+      </c>
+      <c r="I42">
+        <v>0.04925347627764366</v>
+      </c>
+      <c r="J42">
+        <v>-0.04476709291338921</v>
+      </c>
+      <c r="K42">
+        <v>-0.2238919734954834</v>
+      </c>
+      <c r="L42">
+        <v>0.09894419461488724</v>
+      </c>
+      <c r="M42">
+        <v>-2.562304973602295</v>
+      </c>
+      <c r="N42" t="s">
+        <v>151</v>
+      </c>
+      <c r="O42" t="s">
+        <v>211</v>
+      </c>
+      <c r="P42" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="43" spans="1:16">
+      <c r="A43">
+        <v>0</v>
+      </c>
+      <c r="B43" t="s">
+        <v>92</v>
+      </c>
+      <c r="C43">
+        <v>0.0002068902309460867</v>
+      </c>
+      <c r="D43">
+        <v>1.580766365805175E-06</v>
+      </c>
+      <c r="E43">
+        <v>0.001797576202079654</v>
+      </c>
+      <c r="F43">
+        <v>0.001158248749561608</v>
+      </c>
+      <c r="G43">
+        <v>0.001114469836466014</v>
+      </c>
+      <c r="H43">
+        <v>1.00013882965927</v>
+      </c>
+      <c r="I43">
+        <v>0.04927650801171669</v>
+      </c>
+      <c r="J43">
+        <v>0.0008793876622803509</v>
+      </c>
+      <c r="K43">
+        <v>0.005089759826660156</v>
+      </c>
+      <c r="L43">
+        <v>0.1028866991400719</v>
+      </c>
+      <c r="M43">
+        <v>0.0503329411149025</v>
+      </c>
+      <c r="N43" t="s">
+        <v>152</v>
+      </c>
+      <c r="O43" t="s">
+        <v>212</v>
+      </c>
+      <c r="P43" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="44" spans="1:16">
+      <c r="A44">
+        <v>0</v>
+      </c>
+      <c r="B44" t="s">
+        <v>93</v>
+      </c>
+      <c r="C44">
+        <v>0.0002467428584240391</v>
+      </c>
+      <c r="D44">
+        <v>5.070186671218835E-05</v>
+      </c>
+      <c r="E44">
+        <v>0.00213600741699338</v>
+      </c>
+      <c r="F44">
+        <v>0.001256683375686407</v>
+      </c>
+      <c r="G44">
+        <v>0.001175142591819167</v>
+      </c>
+      <c r="H44">
+        <v>1.000199516912835</v>
+      </c>
+      <c r="I44">
+        <v>0.04930695096472746</v>
+      </c>
+      <c r="J44">
+        <v>0.02373674698174</v>
+      </c>
+      <c r="K44">
+        <v>0.1805387735366821</v>
+      </c>
+      <c r="L44">
+        <v>0.1222572699189186</v>
+      </c>
+      <c r="M44">
+        <v>1.358604788780212</v>
+      </c>
+      <c r="N44" t="s">
+        <v>153</v>
+      </c>
+      <c r="O44" t="s">
+        <v>213</v>
+      </c>
+      <c r="P44" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="45" spans="1:16">
+      <c r="A45">
+        <v>0</v>
+      </c>
+      <c r="B45" t="s">
+        <v>94</v>
+      </c>
+      <c r="C45">
+        <v>0.000418227391027618</v>
+      </c>
+      <c r="D45">
+        <v>0.0002466987352818251</v>
+      </c>
+      <c r="E45">
+        <v>0.003928408958017826</v>
+      </c>
+      <c r="F45">
+        <v>0.001553717302158475</v>
+      </c>
+      <c r="G45">
+        <v>0.001425911206752062</v>
+      </c>
+      <c r="H45">
+        <v>1.000221416247028</v>
+      </c>
+      <c r="I45">
+        <v>0.04950464593513523</v>
+      </c>
+      <c r="J45">
+        <v>0.0627986416220665</v>
+      </c>
+      <c r="K45">
+        <v>1.243206262588501</v>
+      </c>
+      <c r="L45">
+        <v>0.2248477935791016</v>
+      </c>
+      <c r="M45">
+        <v>3.594365119934082</v>
+      </c>
+      <c r="N45" t="s">
+        <v>154</v>
+      </c>
+      <c r="O45" t="s">
+        <v>214</v>
+      </c>
+      <c r="P45" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="46" spans="1:16">
+      <c r="A46">
+        <v>0</v>
+      </c>
+      <c r="B46" t="s">
+        <v>95</v>
+      </c>
+      <c r="C46">
+        <v>0.0007129880150008291</v>
+      </c>
+      <c r="D46">
+        <v>0.0006267557619139552</v>
+      </c>
+      <c r="E46">
+        <v>0.003452827921137214</v>
+      </c>
+      <c r="F46">
+        <v>0.001786551787517965</v>
+      </c>
+      <c r="G46">
+        <v>0.001727149821817875</v>
+      </c>
+      <c r="H46">
+        <v>1.000273062920105</v>
+      </c>
+      <c r="I46">
+        <v>0.0495703527426862</v>
+      </c>
+      <c r="J46">
+        <v>0.1815195530653</v>
+      </c>
+      <c r="K46">
+        <v>6.789381980895996</v>
+      </c>
+      <c r="L46">
+        <v>0.1976272761821747</v>
+      </c>
+      <c r="M46">
+        <v>10.38951683044434</v>
+      </c>
+      <c r="N46" t="s">
+        <v>155</v>
+      </c>
+      <c r="O46" t="s">
+        <v>215</v>
+      </c>
+      <c r="P46" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="47" spans="1:16">
+      <c r="A47">
+        <v>0</v>
+      </c>
+      <c r="B47" t="s">
+        <v>96</v>
+      </c>
+      <c r="C47">
+        <v>0.00125770756149036</v>
+      </c>
+      <c r="D47">
+        <v>0.001014170004054904</v>
+      </c>
+      <c r="E47">
+        <v>0.006496627815067768</v>
+      </c>
+      <c r="F47">
+        <v>0.002075225347653031</v>
+      </c>
+      <c r="G47">
+        <v>0.002079477766528726</v>
+      </c>
+      <c r="H47">
+        <v>1.000584189796434</v>
+      </c>
+      <c r="I47">
+        <v>0.04930031668064337</v>
+      </c>
+      <c r="J47">
+        <v>0.1561071425676346</v>
+      </c>
+      <c r="K47">
+        <v>26.67562866210938</v>
+      </c>
+      <c r="L47">
+        <v>0.3718432784080505</v>
+      </c>
+      <c r="M47">
+        <v>8.935003280639648</v>
+      </c>
+      <c r="N47" t="s">
+        <v>156</v>
+      </c>
+      <c r="O47" t="s">
+        <v>216</v>
+      </c>
+      <c r="P47" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="48" spans="1:16">
+      <c r="A48">
+        <v>0</v>
+      </c>
+      <c r="B48" t="s">
+        <v>97</v>
+      </c>
+      <c r="C48">
+        <v>0.00279924356822104</v>
+      </c>
+      <c r="D48">
+        <v>0.001931043574586511</v>
+      </c>
+      <c r="E48">
+        <v>0.01575051993131638</v>
+      </c>
+      <c r="F48">
+        <v>0.002351341070607305</v>
+      </c>
+      <c r="G48">
+        <v>0.002508192323148251</v>
+      </c>
+      <c r="H48">
+        <v>1.001397817285241</v>
+      </c>
+      <c r="I48">
+        <v>0.04972508138690804</v>
+      </c>
+      <c r="J48">
+        <v>0.1226018965244293</v>
+      </c>
+      <c r="K48">
+        <v>554.62255859375</v>
+      </c>
+      <c r="L48">
+        <v>0.9015023112297058</v>
+      </c>
+      <c r="M48">
+        <v>7.017285346984863</v>
+      </c>
+      <c r="N48" t="s">
+        <v>157</v>
+      </c>
+      <c r="O48" t="s">
+        <v>217</v>
+      </c>
+      <c r="P48" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="49" spans="1:16">
+      <c r="A49">
+        <v>0</v>
+      </c>
+      <c r="B49" t="s">
+        <v>98</v>
+      </c>
+      <c r="C49">
+        <v>0.005345552601125421</v>
+      </c>
+      <c r="D49">
+        <v>0.003364598611369729</v>
+      </c>
+      <c r="E49">
+        <v>0.03145559132099152</v>
+      </c>
+      <c r="F49">
+        <v>0.002486592624336481</v>
+      </c>
+      <c r="G49">
+        <v>0.002830783370882273</v>
+      </c>
+      <c r="H49">
+        <v>1.001786599807579</v>
+      </c>
+      <c r="I49">
+        <v>0.05030394547247187</v>
+      </c>
+      <c r="J49">
+        <v>0.1069634482264519</v>
+      </c>
+      <c r="K49">
+        <v>60101.53125</v>
+      </c>
+      <c r="L49">
+        <v>1.800403237342834</v>
+      </c>
+      <c r="M49">
+        <v>6.12219762802124</v>
+      </c>
+      <c r="N49" t="s">
+        <v>158</v>
+      </c>
+      <c r="O49" t="s">
+        <v>218</v>
+      </c>
+      <c r="P49" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="50" spans="1:16">
+      <c r="A50">
+        <v>0</v>
+      </c>
+      <c r="B50" t="s">
+        <v>99</v>
+      </c>
+      <c r="C50">
+        <v>0.01275981076882689</v>
+      </c>
+      <c r="D50">
+        <v>0.007430895697325468</v>
+      </c>
+      <c r="E50">
+        <v>0.07695961743593216</v>
+      </c>
+      <c r="F50">
+        <v>0.00271061179228127</v>
+      </c>
+      <c r="G50">
+        <v>0.003261131467297673</v>
+      </c>
+      <c r="H50">
+        <v>1.002390026334335</v>
+      </c>
+      <c r="I50">
+        <v>0.05581022428338915</v>
+      </c>
+      <c r="J50">
+        <v>0.09655577689409256</v>
+      </c>
+      <c r="K50">
+        <v>34137503744</v>
+      </c>
+      <c r="L50">
+        <v>4.404887676239014</v>
+      </c>
+      <c r="M50">
+        <v>5.526500225067139</v>
+      </c>
+      <c r="N50" t="s">
+        <v>159</v>
+      </c>
+      <c r="O50" t="s">
+        <v>219</v>
+      </c>
+      <c r="P50" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="51" spans="1:16">
+      <c r="A51">
+        <v>0</v>
+      </c>
+      <c r="B51" t="s">
+        <v>100</v>
+      </c>
+      <c r="C51">
+        <v>0.02582372839762866</v>
+      </c>
+      <c r="D51">
+        <v>0.01434710435569286</v>
+      </c>
+      <c r="E51">
+        <v>0.1585066467523575</v>
+      </c>
+      <c r="F51">
+        <v>0.002945988206192851</v>
+      </c>
+      <c r="G51">
+        <v>0.003574476111680269</v>
+      </c>
+      <c r="H51">
+        <v>1.003427172582619</v>
+      </c>
+      <c r="I51">
+        <v>0.06555952123015193</v>
+      </c>
+      <c r="J51">
+        <v>0.09051421284675598</v>
+      </c>
+      <c r="K51">
+        <v>1.850299332936797E+20</v>
+      </c>
+      <c r="L51">
+        <v>9.072341918945312</v>
+      </c>
+      <c r="M51">
+        <v>5.180703163146973</v>
+      </c>
+      <c r="N51" t="s">
+        <v>160</v>
+      </c>
+      <c r="O51" t="s">
+        <v>220</v>
+      </c>
+      <c r="P51" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="52" spans="1:16">
+      <c r="A52">
+        <v>0</v>
+      </c>
+      <c r="B52" t="s">
+        <v>101</v>
+      </c>
+      <c r="C52">
+        <v>0.0001358196412379829</v>
+      </c>
+      <c r="D52">
+        <v>0.0002485990116838366</v>
+      </c>
+      <c r="E52">
+        <v>0.0006966633372940123</v>
+      </c>
+      <c r="F52">
+        <v>0.001195036456920207</v>
+      </c>
+      <c r="G52">
+        <v>0.001170410891063511</v>
+      </c>
+      <c r="H52">
+        <v>0.9993355654272075</v>
+      </c>
+      <c r="I52">
+        <v>0.04970018436395925</v>
+      </c>
+      <c r="J52">
+        <v>0.3568423986434937</v>
+      </c>
+      <c r="K52">
+        <v>1.25726318359375</v>
+      </c>
+      <c r="L52">
+        <v>0.03987446799874306</v>
+      </c>
+      <c r="M52">
+        <v>20.42435646057129</v>
+      </c>
+      <c r="N52" t="s">
+        <v>161</v>
+      </c>
+      <c r="O52" t="s">
+        <v>221</v>
+      </c>
+      <c r="P52" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="53" spans="1:16">
+      <c r="A53">
+        <v>0</v>
+      </c>
+      <c r="B53" t="s">
+        <v>102</v>
+      </c>
+      <c r="C53">
+        <v>0.000161675460081585</v>
+      </c>
+      <c r="D53">
+        <v>0.0002945880987681448</v>
+      </c>
+      <c r="E53">
+        <v>0.0007737397099845111</v>
+      </c>
+      <c r="F53">
+        <v>0.001255546347238123</v>
+      </c>
+      <c r="G53">
+        <v>0.001215652446262538</v>
+      </c>
+      <c r="H53">
+        <v>0.9992692137412479</v>
+      </c>
+      <c r="I53">
+        <v>0.04983916698022196</v>
+      </c>
+      <c r="J53">
+        <v>0.3807328045368195</v>
+      </c>
+      <c r="K53">
+        <v>1.624411344528198</v>
+      </c>
+      <c r="L53">
+        <v>0.04428603872656822</v>
+      </c>
+      <c r="M53">
+        <v>21.79175567626953</v>
+      </c>
+      <c r="N53" t="s">
+        <v>162</v>
+      </c>
+      <c r="O53" t="s">
+        <v>222</v>
+      </c>
+      <c r="P53" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="54" spans="1:16">
+      <c r="A54">
+        <v>0</v>
+      </c>
+      <c r="B54" t="s">
+        <v>103</v>
+      </c>
+      <c r="C54">
+        <v>0.0001813595801389748</v>
+      </c>
+      <c r="D54">
+        <v>0.0003287568397354335</v>
+      </c>
+      <c r="E54">
+        <v>0.0008257005247287452</v>
+      </c>
+      <c r="F54">
+        <v>0.001301071722991765</v>
+      </c>
+      <c r="G54">
+        <v>0.001226006424985826</v>
+      </c>
+      <c r="H54">
+        <v>0.9992162523452683</v>
+      </c>
+      <c r="I54">
+        <v>0.04999607866341085</v>
+      </c>
+      <c r="J54">
+        <v>0.3981550633907318</v>
+      </c>
+      <c r="K54">
+        <v>1.93557596206665</v>
+      </c>
+      <c r="L54">
+        <v>0.04726008325815201</v>
+      </c>
+      <c r="M54">
+        <v>22.78894233703613</v>
+      </c>
+      <c r="N54" t="s">
+        <v>163</v>
+      </c>
+      <c r="O54" t="s">
+        <v>223</v>
+      </c>
+      <c r="P54" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="55" spans="1:16">
+      <c r="A55">
+        <v>0</v>
+      </c>
+      <c r="B55" t="s">
+        <v>43</v>
+      </c>
+      <c r="C55">
+        <v>0.0002414943916754144</v>
+      </c>
+      <c r="D55">
+        <v>0.0004333991091698408</v>
+      </c>
+      <c r="E55">
+        <v>0.0009991895640268922</v>
+      </c>
+      <c r="F55">
+        <v>0.001439976971596479</v>
+      </c>
+      <c r="G55">
+        <v>0.001435801852494478</v>
+      </c>
+      <c r="H55">
+        <v>0.9992745048699395</v>
+      </c>
+      <c r="I55">
+        <v>0.05022997637096376</v>
+      </c>
+      <c r="J55">
+        <v>0.4337506294250488</v>
+      </c>
+      <c r="K55">
+        <v>3.135705947875977</v>
+      </c>
+      <c r="L55">
+        <v>0.05718996375799179</v>
+      </c>
+      <c r="M55">
+        <v>24.82630348205566</v>
+      </c>
+      <c r="N55" t="s">
+        <v>164</v>
+      </c>
+      <c r="O55" t="s">
+        <v>224</v>
+      </c>
+      <c r="P55" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="56" spans="1:16">
+      <c r="A56">
+        <v>0</v>
+      </c>
+      <c r="B56" t="s">
+        <v>104</v>
+      </c>
+      <c r="C56">
+        <v>0.0002990741814790491</v>
+      </c>
+      <c r="D56">
+        <v>0.000537072541192174</v>
+      </c>
+      <c r="E56">
+        <v>0.0011811638250947</v>
+      </c>
+      <c r="F56">
+        <v>0.001678191474638879</v>
+      </c>
+      <c r="G56">
+        <v>0.001778496196493506</v>
+      </c>
+      <c r="H56">
+        <v>1.000145350294837</v>
+      </c>
+      <c r="I56">
+        <v>0.04956531302650627</v>
+      </c>
+      <c r="J56">
+        <v>0.4546977579593658</v>
+      </c>
+      <c r="K56">
+        <v>4.80583667755127</v>
+      </c>
+      <c r="L56">
+        <v>0.06760551035404205</v>
+      </c>
+      <c r="M56">
+        <v>26.02523994445801</v>
+      </c>
+      <c r="N56" t="s">
+        <v>165</v>
+      </c>
+      <c r="O56" t="s">
+        <v>225</v>
+      </c>
+      <c r="P56" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="57" spans="1:16">
+      <c r="A57">
+        <v>0</v>
+      </c>
+      <c r="B57" t="s">
+        <v>105</v>
+      </c>
+      <c r="C57">
+        <v>0.0003520870224145781</v>
+      </c>
+      <c r="D57">
+        <v>0.0006330463802441955</v>
+      </c>
+      <c r="E57">
+        <v>0.001421531196683645</v>
+      </c>
+      <c r="F57">
+        <v>0.00185447046533227</v>
+      </c>
+      <c r="G57">
+        <v>0.002132507972419262</v>
+      </c>
+      <c r="H57">
+        <v>1.000772346920553</v>
+      </c>
+      <c r="I57">
+        <v>0.04908126999962909</v>
+      </c>
+      <c r="J57">
+        <v>0.44532710313797</v>
+      </c>
+      <c r="K57">
+        <v>6.949080944061279</v>
+      </c>
+      <c r="L57">
+        <v>0.0813632607460022</v>
+      </c>
+      <c r="M57">
+        <v>25.48889923095703</v>
+      </c>
+      <c r="N57" t="s">
+        <v>166</v>
+      </c>
+      <c r="O57" t="s">
+        <v>226</v>
+      </c>
+      <c r="P57" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="58" spans="1:16">
+      <c r="A58">
+        <v>0</v>
+      </c>
+      <c r="B58" t="s">
+        <v>106</v>
+      </c>
+      <c r="C58">
+        <v>0.0004147644817084658</v>
+      </c>
+      <c r="D58">
+        <v>0.0007664625300094485</v>
+      </c>
+      <c r="E58">
+        <v>0.001965186791494489</v>
+      </c>
+      <c r="F58">
+        <v>0.002124054590240121</v>
+      </c>
+      <c r="G58">
+        <v>0.002591048134490848</v>
+      </c>
+      <c r="H58">
+        <v>1.001305166126638</v>
+      </c>
+      <c r="I58">
+        <v>0.04976511731612621</v>
+      </c>
+      <c r="J58">
+        <v>0.3900201916694641</v>
+      </c>
+      <c r="K58">
+        <v>11.30669784545898</v>
+      </c>
+      <c r="L58">
+        <v>0.1124801188707352</v>
+      </c>
+      <c r="M58">
+        <v>22.32333183288574</v>
+      </c>
+      <c r="N58" t="s">
+        <v>167</v>
+      </c>
+      <c r="O58" t="s">
+        <v>227</v>
+      </c>
+      <c r="P58" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="59" spans="1:16">
+      <c r="A59">
+        <v>0</v>
+      </c>
+      <c r="B59" t="s">
+        <v>107</v>
+      </c>
+      <c r="C59">
+        <v>0.0004578765216544392</v>
+      </c>
+      <c r="D59">
+        <v>0.0009116887231357396</v>
+      </c>
+      <c r="E59">
+        <v>0.002679570810869336</v>
+      </c>
+      <c r="F59">
+        <v>0.002270683413371444</v>
+      </c>
+      <c r="G59">
+        <v>0.0028814144898206</v>
+      </c>
+      <c r="H59">
+        <v>1.001415876124365</v>
+      </c>
+      <c r="I59">
+        <v>0.05051290192149779</v>
+      </c>
+      <c r="J59">
+        <v>0.3402368426322937</v>
+      </c>
+      <c r="K59">
+        <v>18.79461479187012</v>
+      </c>
+      <c r="L59">
+        <v>0.1533688604831696</v>
+      </c>
+      <c r="M59">
+        <v>19.47391510009766</v>
+      </c>
+      <c r="N59" t="s">
+        <v>168</v>
+      </c>
+      <c r="O59" t="s">
+        <v>228</v>
+      </c>
+      <c r="P59" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="60" spans="1:16">
+      <c r="A60">
+        <v>0</v>
+      </c>
+      <c r="B60" t="s">
+        <v>108</v>
+      </c>
+      <c r="C60">
+        <v>0.0005112206185981177</v>
+      </c>
+      <c r="D60">
+        <v>0.00114975287579</v>
+      </c>
+      <c r="E60">
+        <v>0.004215768538415432</v>
+      </c>
+      <c r="F60">
+        <v>0.002419894561171532</v>
+      </c>
+      <c r="G60">
+        <v>0.003251965856179595</v>
+      </c>
+      <c r="H60">
+        <v>1.001628675282286</v>
+      </c>
+      <c r="I60">
+        <v>0.05720951072135684</v>
+      </c>
+      <c r="J60">
+        <v>0.2727267444133759</v>
+      </c>
+      <c r="K60">
+        <v>42.14189529418945</v>
+      </c>
+      <c r="L60">
+        <v>0.2412952035665512</v>
+      </c>
+      <c r="M60">
+        <v>15.60988330841064</v>
+      </c>
+      <c r="N60" t="s">
+        <v>169</v>
+      </c>
+      <c r="O60" t="s">
+        <v>229</v>
+      </c>
+      <c r="P60" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="61" spans="1:16">
+      <c r="A61">
+        <v>0</v>
+      </c>
+      <c r="B61" t="s">
+        <v>109</v>
+      </c>
+      <c r="C61">
+        <v>0.0005477455078690072</v>
+      </c>
+      <c r="D61">
+        <v>0.001303202821873128</v>
+      </c>
+      <c r="E61">
+        <v>0.005588145460933447</v>
+      </c>
+      <c r="F61">
+        <v>0.002502876333892345</v>
+      </c>
+      <c r="G61">
+        <v>0.003532109782099724</v>
+      </c>
+      <c r="H61">
+        <v>1.002600979192166</v>
+      </c>
+      <c r="I61">
+        <v>0.06659987593070682</v>
+      </c>
+      <c r="J61">
+        <v>0.2332084625959396</v>
+      </c>
+      <c r="K61">
+        <v>70.27107238769531</v>
+      </c>
+      <c r="L61">
+        <v>0.319845050573349</v>
+      </c>
+      <c r="M61">
+        <v>13.34800148010254</v>
+      </c>
+      <c r="N61" t="s">
+        <v>170</v>
+      </c>
+      <c r="O61" t="s">
+        <v>230</v>
+      </c>
+      <c r="P61" t="s">
+        <v>290</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:P61"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:16">
+      <c r="B1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1" t="s">
+        <v>47</v>
+      </c>
+      <c r="G1" t="s">
+        <v>48</v>
+      </c>
+      <c r="H1" t="s">
+        <v>49</v>
+      </c>
+      <c r="I1" t="s">
+        <v>50</v>
+      </c>
+      <c r="J1" t="s">
+        <v>36</v>
+      </c>
+      <c r="K1" t="s">
+        <v>37</v>
+      </c>
+      <c r="L1" t="s">
+        <v>38</v>
+      </c>
+      <c r="M1" t="s">
+        <v>39</v>
+      </c>
+      <c r="N1" t="s">
+        <v>40</v>
+      </c>
+      <c r="O1" t="s">
+        <v>41</v>
+      </c>
+      <c r="P1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C2">
+        <v>0.0005968378769909851</v>
+      </c>
+      <c r="D2">
+        <v>-0.003906970843672752</v>
+      </c>
+      <c r="E2">
+        <v>0.06871426105499268</v>
+      </c>
+      <c r="F2">
+        <v>0.0008329615229740739</v>
+      </c>
+      <c r="G2">
+        <v>0.0008923794375732541</v>
+      </c>
+      <c r="H2">
+        <v>1.00049883938557</v>
+      </c>
+      <c r="I2">
+        <v>0.04898512794940538</v>
+      </c>
+      <c r="J2">
+        <v>-0.05685822293162346</v>
+      </c>
+      <c r="K2">
+        <v>-0.9999973177909851</v>
+      </c>
+      <c r="L2">
+        <v>3.932953596115112</v>
+      </c>
+      <c r="M2">
+        <v>-3.254357099533081</v>
+      </c>
+      <c r="N2" t="s">
+        <v>291</v>
+      </c>
+      <c r="O2" t="s">
+        <v>351</v>
+      </c>
+      <c r="P2" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16">
+      <c r="A3">
+        <v>0</v>
+      </c>
+      <c r="B3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C3">
+        <v>0.0007933526912793172</v>
+      </c>
+      <c r="D3">
+        <v>-0.006556747481226921</v>
+      </c>
+      <c r="E3">
+        <v>0.1282479763031006</v>
+      </c>
+      <c r="F3">
+        <v>0.0009462435264140368</v>
+      </c>
+      <c r="G3">
+        <v>0.0009752179612405598</v>
+      </c>
+      <c r="H3">
+        <v>1.000708131932882</v>
+      </c>
+      <c r="I3">
+        <v>0.04895746086183403</v>
+      </c>
+      <c r="J3">
+        <v>-0.05112554505467415</v>
+      </c>
+      <c r="K3">
+        <v>-1</v>
+      </c>
+      <c r="L3">
+        <v>7.340445995330811</v>
+      </c>
+      <c r="M3">
+        <v>-2.926239728927612</v>
+      </c>
+      <c r="N3" t="s">
+        <v>292</v>
+      </c>
+      <c r="O3" t="s">
+        <v>352</v>
+      </c>
+      <c r="P3" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16">
+      <c r="A4">
+        <v>0</v>
+      </c>
+      <c r="B4" t="s">
+        <v>53</v>
+      </c>
+      <c r="C4">
+        <v>0.0009879255411609767</v>
+      </c>
+      <c r="D4">
+        <v>-0.003128546290099621</v>
+      </c>
+      <c r="E4">
+        <v>0.08503894507884979</v>
+      </c>
+      <c r="F4">
+        <v>0.001047390047460794</v>
+      </c>
+      <c r="G4">
+        <v>0.001068350276909769</v>
+      </c>
+      <c r="H4">
+        <v>1.000810734866418</v>
+      </c>
+      <c r="I4">
+        <v>0.04893453707834217</v>
+      </c>
+      <c r="J4">
+        <v>-0.03678957000374794</v>
+      </c>
+      <c r="K4">
+        <v>-0.9999651908874512</v>
+      </c>
+      <c r="L4">
+        <v>4.867319107055664</v>
+      </c>
+      <c r="M4">
+        <v>-2.105700731277466</v>
+      </c>
+      <c r="N4" t="s">
+        <v>293</v>
+      </c>
+      <c r="O4" t="s">
+        <v>353</v>
+      </c>
+      <c r="P4" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16">
+      <c r="A5">
+        <v>0</v>
+      </c>
+      <c r="B5" t="s">
+        <v>54</v>
+      </c>
+      <c r="C5">
+        <v>0.001939136873801407</v>
+      </c>
+      <c r="D5">
+        <v>-0.002703542122617364</v>
+      </c>
+      <c r="E5">
+        <v>0.09763555973768234</v>
+      </c>
+      <c r="F5">
+        <v>0.001374062267132103</v>
+      </c>
+      <c r="G5">
+        <v>0.001294519985094666</v>
+      </c>
+      <c r="H5">
+        <v>1.000985067314885</v>
+      </c>
+      <c r="I5">
+        <v>0.04893295624779516</v>
+      </c>
+      <c r="J5">
+        <v>-0.02769013866782188</v>
+      </c>
+      <c r="K5">
+        <v>-0.9998592734336853</v>
+      </c>
+      <c r="L5">
+        <v>5.588303089141846</v>
+      </c>
+      <c r="M5">
+        <v>-1.584882497787476</v>
+      </c>
+      <c r="N5" t="s">
+        <v>294</v>
+      </c>
+      <c r="O5" t="s">
+        <v>354</v>
+      </c>
+      <c r="P5" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16">
+      <c r="A6">
+        <v>0</v>
+      </c>
+      <c r="B6" t="s">
+        <v>55</v>
+      </c>
+      <c r="C6">
+        <v>0.003802787533307643</v>
+      </c>
+      <c r="D6">
+        <v>0.00192308216355741</v>
+      </c>
+      <c r="E6">
+        <v>0.02001701667904854</v>
+      </c>
+      <c r="F6">
+        <v>0.001645300537347794</v>
+      </c>
+      <c r="G6">
+        <v>0.001519371406175196</v>
+      </c>
+      <c r="H6">
+        <v>1.001070959375685</v>
+      </c>
+      <c r="I6">
+        <v>0.04910987749698358</v>
+      </c>
+      <c r="J6">
+        <v>0.09607236832380295</v>
+      </c>
+      <c r="K6">
+        <v>540.3002319335938</v>
+      </c>
+      <c r="L6">
+        <v>1.145701050758362</v>
+      </c>
+      <c r="M6">
+        <v>5.498831748962402</v>
+      </c>
+      <c r="N6" t="s">
+        <v>295</v>
+      </c>
+      <c r="O6" t="s">
+        <v>355</v>
+      </c>
+      <c r="P6" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16">
+      <c r="A7">
+        <v>0</v>
+      </c>
+      <c r="B7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C7">
+        <v>0.007496727263131745</v>
+      </c>
+      <c r="D7">
+        <v>0.004164630081504583</v>
+      </c>
+      <c r="E7">
+        <v>0.04365257173776627</v>
+      </c>
+      <c r="F7">
+        <v>0.001901817508041859</v>
+      </c>
+      <c r="G7">
+        <v>0.001795641961507499</v>
+      </c>
+      <c r="H7">
+        <v>1.001143254036422</v>
+      </c>
+      <c r="I7">
+        <v>0.04884497006886806</v>
+      </c>
+      <c r="J7">
+        <v>0.0954040065407753</v>
+      </c>
+      <c r="K7">
+        <v>818166.5</v>
+      </c>
+      <c r="L7">
+        <v>2.49851393699646</v>
+      </c>
+      <c r="M7">
+        <v>5.460577011108398</v>
+      </c>
+      <c r="N7" t="s">
+        <v>296</v>
+      </c>
+      <c r="O7" t="s">
+        <v>356</v>
+      </c>
+      <c r="P7" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16">
+      <c r="A8">
+        <v>0</v>
+      </c>
+      <c r="B8" t="s">
+        <v>57</v>
+      </c>
+      <c r="C8">
+        <v>0.01847337151457263</v>
+      </c>
+      <c r="D8">
+        <v>0.01106492150574923</v>
+      </c>
+      <c r="E8">
+        <v>0.1198592409491539</v>
+      </c>
+      <c r="F8">
+        <v>0.002261060290038586</v>
+      </c>
+      <c r="G8">
+        <v>0.002273147692903876</v>
+      </c>
+      <c r="H8">
+        <v>1.001483180078128</v>
+      </c>
+      <c r="I8">
+        <v>0.04954464652670695</v>
+      </c>
+      <c r="J8">
+        <v>0.09231596440076828</v>
+      </c>
+      <c r="K8">
+        <v>4529980390244352</v>
+      </c>
+      <c r="L8">
+        <v>6.860305786132812</v>
+      </c>
+      <c r="M8">
+        <v>5.283828735351562</v>
+      </c>
+      <c r="N8" t="s">
+        <v>297</v>
+      </c>
+      <c r="O8" t="s">
+        <v>357</v>
+      </c>
+      <c r="P8" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16">
+      <c r="A9">
+        <v>0</v>
+      </c>
+      <c r="B9" t="s">
+        <v>58</v>
+      </c>
+      <c r="C9">
+        <v>0.03672633897143723</v>
+      </c>
+      <c r="D9">
+        <v>0.02190644294023514</v>
+      </c>
+      <c r="E9">
+        <v>0.2377467006444931</v>
+      </c>
+      <c r="F9">
+        <v>0.002488412195816636</v>
+      </c>
+      <c r="G9">
+        <v>0.002632650779560208</v>
+      </c>
+      <c r="H9">
+        <v>1.001715517904244</v>
+      </c>
+      <c r="I9">
+        <v>0.05025363923385218</v>
+      </c>
+      <c r="J9">
+        <v>0.09214194118976593</v>
+      </c>
+      <c r="K9">
+        <v>6.77576688203714E+30</v>
+      </c>
+      <c r="L9">
+        <v>13.60775375366211</v>
+      </c>
+      <c r="M9">
+        <v>5.273868560791016</v>
+      </c>
+      <c r="N9" t="s">
+        <v>298</v>
+      </c>
+      <c r="O9" t="s">
+        <v>358</v>
+      </c>
+      <c r="P9" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16">
+      <c r="A10">
+        <v>0</v>
+      </c>
+      <c r="B10" t="s">
+        <v>59</v>
+      </c>
+      <c r="C10">
+        <v>0.09222659394525165</v>
+      </c>
+      <c r="D10">
+        <v>0.05439530313014984</v>
+      </c>
+      <c r="E10">
+        <v>0.6093196272850037</v>
+      </c>
+      <c r="F10">
+        <v>0.002725073136389256</v>
+      </c>
+      <c r="G10">
+        <v>0.003032611683011055</v>
+      </c>
+      <c r="H10">
+        <v>1.002390026334335</v>
+      </c>
+      <c r="I10">
+        <v>0.05598150961590734</v>
+      </c>
+      <c r="J10">
+        <v>0.08927220106124878</v>
+      </c>
+      <c r="K10" t="s">
+        <v>110</v>
+      </c>
+      <c r="L10">
+        <v>34.8752326965332</v>
+      </c>
+      <c r="M10">
+        <v>5.109614849090576</v>
+      </c>
+      <c r="N10" t="s">
+        <v>299</v>
+      </c>
+      <c r="O10" t="s">
+        <v>359</v>
+      </c>
+      <c r="P10" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16">
+      <c r="A11">
+        <v>0</v>
+      </c>
+      <c r="B11" t="s">
+        <v>60</v>
+      </c>
+      <c r="C11">
+        <v>0.1787624510060036</v>
+      </c>
+      <c r="D11">
+        <v>0.1039649769663811</v>
+      </c>
+      <c r="E11">
+        <v>1.094953536987305</v>
+      </c>
+      <c r="F11">
+        <v>0.002951268572360277</v>
+      </c>
+      <c r="G11">
+        <v>0.003463260363787413</v>
+      </c>
+      <c r="H11">
+        <v>1.003549571603427</v>
+      </c>
+      <c r="I11">
+        <v>0.06545946019335863</v>
+      </c>
+      <c r="J11">
+        <v>0.09494921565055847</v>
+      </c>
+      <c r="K11" t="s">
+        <v>110</v>
+      </c>
+      <c r="L11">
+        <v>62.67114639282227</v>
+      </c>
+      <c r="M11">
+        <v>5.43454647064209</v>
+      </c>
+      <c r="N11" t="s">
+        <v>300</v>
+      </c>
+      <c r="O11" t="s">
+        <v>360</v>
+      </c>
+      <c r="P11" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16">
+      <c r="A12">
+        <v>0</v>
+      </c>
+      <c r="B12" t="s">
+        <v>61</v>
+      </c>
+      <c r="C12">
+        <v>0.0008941828648590997</v>
+      </c>
+      <c r="D12">
+        <v>-0.0004288601630833</v>
+      </c>
+      <c r="E12">
+        <v>0.008826624602079391</v>
+      </c>
+      <c r="F12">
+        <v>0.0008399088401347399</v>
+      </c>
+      <c r="G12">
+        <v>0.0009085889905691147</v>
+      </c>
+      <c r="H12">
+        <v>1.000444815174435</v>
+      </c>
+      <c r="I12">
+        <v>0.04902869977434892</v>
+      </c>
+      <c r="J12">
+        <v>-0.04858710616827011</v>
+      </c>
+      <c r="K12">
+        <v>-0.7546898126602173</v>
+      </c>
+      <c r="L12">
+        <v>0.5052037835121155</v>
+      </c>
+      <c r="M12">
+        <v>-2.780948638916016</v>
+      </c>
+      <c r="N12" t="s">
+        <v>301</v>
+      </c>
+      <c r="O12" t="s">
+        <v>361</v>
+      </c>
+      <c r="P12" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16">
+      <c r="A13">
+        <v>0</v>
+      </c>
+      <c r="B13" t="s">
+        <v>62</v>
+      </c>
+      <c r="C13">
+        <v>0.001189064369279581</v>
+      </c>
+      <c r="D13">
+        <v>-4.193589484202676E-05</v>
+      </c>
+      <c r="E13">
+        <v>0.01018855441361666</v>
+      </c>
+      <c r="F13">
+        <v>0.0009688055724836886</v>
+      </c>
+      <c r="G13">
+        <v>0.0009867355693131685</v>
+      </c>
+      <c r="H13">
+        <v>1.000635168358134</v>
+      </c>
+      <c r="I13">
+        <v>0.04902880105479978</v>
+      </c>
+      <c r="J13">
+        <v>-0.004115981049835682</v>
+      </c>
+      <c r="K13">
+        <v>-0.1284388899803162</v>
+      </c>
+      <c r="L13">
+        <v>0.5831556916236877</v>
+      </c>
+      <c r="M13">
+        <v>-0.2355837374925613</v>
+      </c>
+      <c r="N13" t="s">
+        <v>302</v>
+      </c>
+      <c r="O13" t="s">
+        <v>362</v>
+      </c>
+      <c r="P13" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16">
+      <c r="A14">
+        <v>0</v>
+      </c>
+      <c r="B14" t="s">
+        <v>63</v>
+      </c>
+      <c r="C14">
+        <v>0.001481412230255795</v>
+      </c>
+      <c r="D14">
+        <v>0.0004507676349021494</v>
+      </c>
+      <c r="E14">
+        <v>0.01126209460198879</v>
+      </c>
+      <c r="F14">
+        <v>0.001082261558622122</v>
+      </c>
+      <c r="G14">
+        <v>0.001089607132598758</v>
+      </c>
+      <c r="H14">
+        <v>1.000730206693903</v>
+      </c>
+      <c r="I14">
+        <v>0.04903001620156933</v>
+      </c>
+      <c r="J14">
+        <v>0.04002520442008972</v>
+      </c>
+      <c r="K14">
+        <v>3.376546382904053</v>
+      </c>
+      <c r="L14">
+        <v>0.6446012258529663</v>
+      </c>
+      <c r="M14">
+        <v>2.290896654129028</v>
+      </c>
+      <c r="N14" t="s">
+        <v>303</v>
+      </c>
+      <c r="O14" t="s">
+        <v>363</v>
+      </c>
+      <c r="P14" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16">
+      <c r="A15">
+        <v>0</v>
+      </c>
+      <c r="B15" t="s">
+        <v>64</v>
+      </c>
+      <c r="C15">
+        <v>0.002922616752972795</v>
+      </c>
+      <c r="D15">
+        <v>0.001800293102860451</v>
+      </c>
+      <c r="E15">
+        <v>0.02689874172210693</v>
+      </c>
+      <c r="F15">
+        <v>0.001402011257596314</v>
+      </c>
+      <c r="G15">
+        <v>0.001328514539636672</v>
+      </c>
+      <c r="H15">
+        <v>1.000903480109434</v>
+      </c>
+      <c r="I15">
+        <v>0.04901933286817315</v>
+      </c>
+      <c r="J15">
+        <v>0.06692852824926376</v>
+      </c>
+      <c r="K15">
+        <v>361.3012390136719</v>
+      </c>
+      <c r="L15">
+        <v>1.539585828781128</v>
+      </c>
+      <c r="M15">
+        <v>3.830744743347168</v>
+      </c>
+      <c r="N15" t="s">
+        <v>304</v>
+      </c>
+      <c r="O15" t="s">
+        <v>364</v>
+      </c>
+      <c r="P15" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16">
+      <c r="A16">
+        <v>0</v>
+      </c>
+      <c r="B16" t="s">
+        <v>65</v>
+      </c>
+      <c r="C16">
+        <v>0.005762707155667767</v>
+      </c>
+      <c r="D16">
+        <v>0.004086158704012632</v>
+      </c>
+      <c r="E16">
+        <v>0.06056955456733704</v>
+      </c>
+      <c r="F16">
+        <v>0.001676679705269635</v>
+      </c>
+      <c r="G16">
+        <v>0.001554322778247297</v>
+      </c>
+      <c r="H16">
+        <v>1.000961221902555</v>
+      </c>
+      <c r="I16">
+        <v>0.04915397140838638</v>
+      </c>
+      <c r="J16">
+        <v>0.067462258040905</v>
+      </c>
+      <c r="K16">
+        <v>633432.0625</v>
+      </c>
+      <c r="L16">
+        <v>3.466780185699463</v>
+      </c>
+      <c r="M16">
+        <v>3.86129355430603</v>
+      </c>
+      <c r="N16" t="s">
+        <v>305</v>
+      </c>
+      <c r="O16" t="s">
+        <v>365</v>
+      </c>
+      <c r="P16" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16">
+      <c r="A17">
+        <v>0</v>
+      </c>
+      <c r="B17" t="s">
+        <v>66</v>
+      </c>
+      <c r="C17">
+        <v>0.01137647206287789</v>
+      </c>
+      <c r="D17">
+        <v>0.007668835576623678</v>
+      </c>
+      <c r="E17">
+        <v>0.09923607110977173</v>
+      </c>
+      <c r="F17">
+        <v>0.00193705887068063</v>
+      </c>
+      <c r="G17">
+        <v>0.001843196689151227</v>
+      </c>
+      <c r="H17">
+        <v>1.001033846640303</v>
+      </c>
+      <c r="I17">
+        <v>0.04888776222034857</v>
+      </c>
+      <c r="J17">
+        <v>0.07727871090173721</v>
+      </c>
+      <c r="K17">
+        <v>73999081472</v>
+      </c>
+      <c r="L17">
+        <v>5.679910659790039</v>
+      </c>
+      <c r="M17">
+        <v>4.42315149307251</v>
+      </c>
+      <c r="N17" t="s">
+        <v>306</v>
+      </c>
+      <c r="O17" t="s">
+        <v>366</v>
+      </c>
+      <c r="P17" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16">
+      <c r="A18">
+        <v>0</v>
+      </c>
+      <c r="B18" t="s">
+        <v>67</v>
+      </c>
+      <c r="C18">
+        <v>0.02819875027253365</v>
+      </c>
+      <c r="D18">
+        <v>0.02236281894147396</v>
+      </c>
+      <c r="E18">
+        <v>0.3360125422477722</v>
+      </c>
+      <c r="F18">
+        <v>0.002276191720739007</v>
+      </c>
+      <c r="G18">
+        <v>0.002292354591190815</v>
+      </c>
+      <c r="H18">
+        <v>1.001308708692968</v>
+      </c>
+      <c r="I18">
+        <v>0.04954445651151065</v>
+      </c>
+      <c r="J18">
+        <v>0.06655352562665939</v>
+      </c>
+      <c r="K18">
+        <v>2.925136981308162E+31</v>
+      </c>
+      <c r="L18">
+        <v>19.23213195800781</v>
+      </c>
+      <c r="M18">
+        <v>3.809280872344971</v>
+      </c>
+      <c r="N18" t="s">
+        <v>307</v>
+      </c>
+      <c r="O18" t="s">
+        <v>367</v>
+      </c>
+      <c r="P18" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16">
+      <c r="A19">
+        <v>0</v>
+      </c>
+      <c r="B19" t="s">
+        <v>68</v>
+      </c>
+      <c r="C19">
+        <v>0.05565907284467175</v>
+      </c>
+      <c r="D19">
+        <v>0.04471840709447861</v>
+      </c>
+      <c r="E19">
+        <v>0.6763868927955627</v>
+      </c>
+      <c r="F19">
+        <v>0.00248401565477252</v>
+      </c>
+      <c r="G19">
+        <v>0.002607102273032069</v>
+      </c>
+      <c r="H19">
+        <v>1.001779251555865</v>
+      </c>
+      <c r="I19">
+        <v>0.05021123610794206</v>
+      </c>
+      <c r="J19">
+        <v>0.06611365079879761</v>
+      </c>
+      <c r="K19" t="s">
+        <v>110</v>
+      </c>
+      <c r="L19">
+        <v>38.71391677856445</v>
+      </c>
+      <c r="M19">
+        <v>3.784104108810425</v>
+      </c>
+      <c r="N19" t="s">
+        <v>308</v>
+      </c>
+      <c r="O19" t="s">
+        <v>368</v>
+      </c>
+      <c r="P19" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16">
+      <c r="A20">
+        <v>0</v>
+      </c>
+      <c r="B20" t="s">
+        <v>69</v>
+      </c>
+      <c r="C20">
+        <v>0.1399167486104504</v>
+      </c>
+      <c r="D20">
+        <v>0.1023992002010345</v>
+      </c>
+      <c r="E20">
+        <v>1.457669973373413</v>
+      </c>
+      <c r="F20">
+        <v>0.002744531957432628</v>
+      </c>
+      <c r="G20">
+        <v>0.003133517922833562</v>
+      </c>
+      <c r="H20">
+        <v>1.002390026334335</v>
+      </c>
+      <c r="I20">
+        <v>0.05598150961590734</v>
+      </c>
+      <c r="J20">
+        <v>0.0702485516667366</v>
+      </c>
+      <c r="K20" t="s">
+        <v>110</v>
+      </c>
+      <c r="L20">
+        <v>83.43170928955078</v>
+      </c>
+      <c r="M20">
+        <v>4.02077054977417</v>
+      </c>
+      <c r="N20" t="s">
+        <v>309</v>
+      </c>
+      <c r="O20" t="s">
+        <v>369</v>
+      </c>
+      <c r="P20" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16">
+      <c r="A21">
+        <v>0</v>
+      </c>
+      <c r="B21" t="s">
+        <v>70</v>
+      </c>
+      <c r="C21">
+        <v>0.2724031597663126</v>
+      </c>
+      <c r="D21">
+        <v>0.214059978723526</v>
+      </c>
+      <c r="E21">
+        <v>3.170099258422852</v>
+      </c>
+      <c r="F21">
+        <v>0.002954148687422276</v>
+      </c>
+      <c r="G21">
+        <v>0.003394182771444321</v>
+      </c>
+      <c r="H21">
+        <v>1.003549571603427</v>
+      </c>
+      <c r="I21">
+        <v>0.06545946019335863</v>
+      </c>
+      <c r="J21">
+        <v>0.06752469390630722</v>
+      </c>
+      <c r="K21" t="s">
+        <v>110</v>
+      </c>
+      <c r="L21">
+        <v>181.4449157714844</v>
+      </c>
+      <c r="M21">
+        <v>3.864866971969604</v>
+      </c>
+      <c r="N21" t="s">
+        <v>310</v>
+      </c>
+      <c r="O21" t="s">
+        <v>370</v>
+      </c>
+      <c r="P21" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16">
+      <c r="A22">
+        <v>0</v>
+      </c>
+      <c r="B22" t="s">
+        <v>71</v>
+      </c>
+      <c r="C22">
+        <v>0.0002859314177757262</v>
+      </c>
+      <c r="D22">
+        <v>-0.0005172359524294734</v>
+      </c>
+      <c r="E22">
+        <v>0.001508558518253267</v>
+      </c>
+      <c r="F22">
+        <v>0.0008605393813923001</v>
+      </c>
+      <c r="G22">
+        <v>0.0009140089969150722</v>
+      </c>
+      <c r="H22">
+        <v>1.000369077854179</v>
+      </c>
+      <c r="I22">
+        <v>0.04906577860839411</v>
+      </c>
+      <c r="J22">
+        <v>-0.3428676724433899</v>
+      </c>
+      <c r="K22">
+        <v>-0.8163909316062927</v>
+      </c>
+      <c r="L22">
+        <v>0.08634438365697861</v>
+      </c>
+      <c r="M22">
+        <v>-19.6244945526123</v>
+      </c>
+      <c r="N22" t="s">
+        <v>311</v>
+      </c>
+      <c r="O22" t="s">
+        <v>371</v>
+      </c>
+      <c r="P22" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16">
+      <c r="A23">
+        <v>0</v>
+      </c>
+      <c r="B23" t="s">
+        <v>72</v>
+      </c>
+      <c r="C23">
+        <v>0.0003768525164605031</v>
+      </c>
+      <c r="D23">
+        <v>-0.0003449551004450768</v>
+      </c>
+      <c r="E23">
+        <v>0.001732680480927229</v>
+      </c>
+      <c r="F23">
+        <v>0.001004663063213229</v>
+      </c>
+      <c r="G23">
+        <v>0.001023926888592541</v>
+      </c>
+      <c r="H23">
+        <v>1.000560801496074</v>
+      </c>
+      <c r="I23">
+        <v>0.04907087505080421</v>
+      </c>
+      <c r="J23">
+        <v>-0.1990875452756882</v>
+      </c>
+      <c r="K23">
+        <v>-0.6770288944244385</v>
+      </c>
+      <c r="L23">
+        <v>0.09917230904102325</v>
+      </c>
+      <c r="M23">
+        <v>-11.39504432678223</v>
+      </c>
+      <c r="N23" t="s">
+        <v>312</v>
+      </c>
+      <c r="O23" t="s">
+        <v>372</v>
+      </c>
+      <c r="P23" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="24" spans="1:16">
+      <c r="A24">
+        <v>0</v>
+      </c>
+      <c r="B24" t="s">
+        <v>73</v>
+      </c>
+      <c r="C24">
+        <v>0.0004648283441714175</v>
+      </c>
+      <c r="D24">
+        <v>-0.0002333813899895176</v>
+      </c>
+      <c r="E24">
+        <v>0.002051062416285276</v>
+      </c>
+      <c r="F24">
+        <v>0.001118156360462308</v>
+      </c>
+      <c r="G24">
+        <v>0.001123031717725098</v>
+      </c>
+      <c r="H24">
+        <v>1.000648504478539</v>
+      </c>
+      <c r="I24">
+        <v>0.04905248314377132</v>
+      </c>
+      <c r="J24">
+        <v>-0.1137856096029282</v>
+      </c>
+      <c r="K24">
+        <v>-0.5344570875167847</v>
+      </c>
+      <c r="L24">
+        <v>0.1173953264951706</v>
+      </c>
+      <c r="M24">
+        <v>-6.512672901153564</v>
+      </c>
+      <c r="N24" t="s">
+        <v>313</v>
+      </c>
+      <c r="O24" t="s">
+        <v>373</v>
+      </c>
+      <c r="P24" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="25" spans="1:16">
+      <c r="A25">
+        <v>0</v>
+      </c>
+      <c r="B25" t="s">
+        <v>74</v>
+      </c>
+      <c r="C25">
+        <v>0.0008816263863101903</v>
+      </c>
+      <c r="D25">
+        <v>0.0001650650083320215</v>
+      </c>
+      <c r="E25">
+        <v>0.003718232735991478</v>
+      </c>
+      <c r="F25">
+        <v>0.001444206456653774</v>
+      </c>
+      <c r="G25">
+        <v>0.001365351257845759</v>
+      </c>
+      <c r="H25">
+        <v>1.00080813529151</v>
+      </c>
+      <c r="I25">
+        <v>0.04910762696561873</v>
+      </c>
+      <c r="J25">
+        <v>0.04439340531826019</v>
+      </c>
+      <c r="K25">
+        <v>0.71744704246521</v>
+      </c>
+      <c r="L25">
+        <v>0.2128180712461472</v>
+      </c>
+      <c r="M25">
+        <v>2.540916442871094</v>
+      </c>
+      <c r="N25" t="s">
+        <v>314</v>
+      </c>
+      <c r="O25" t="s">
+        <v>374</v>
+      </c>
+      <c r="P25" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="26" spans="1:16">
+      <c r="A26">
+        <v>0</v>
+      </c>
+      <c r="B26" t="s">
+        <v>75</v>
+      </c>
+      <c r="C26">
+        <v>0.001672854291544685</v>
+      </c>
+      <c r="D26">
+        <v>0.0006611456628888845</v>
+      </c>
+      <c r="E26">
+        <v>0.007132874801754951</v>
+      </c>
+      <c r="F26">
+        <v>0.001721086795441806</v>
+      </c>
+      <c r="G26">
+        <v>0.001620043418370187</v>
+      </c>
+      <c r="H26">
+        <v>1.000856393682047</v>
+      </c>
+      <c r="I26">
+        <v>0.04920940611285433</v>
+      </c>
+      <c r="J26">
+        <v>0.09268993139266968</v>
+      </c>
+      <c r="K26">
+        <v>7.716011047363281</v>
+      </c>
+      <c r="L26">
+        <v>0.4082597196102142</v>
+      </c>
+      <c r="M26">
+        <v>5.305233478546143</v>
+      </c>
+      <c r="N26" t="s">
+        <v>315</v>
+      </c>
+      <c r="O26" t="s">
+        <v>375</v>
+      </c>
+      <c r="P26" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="27" spans="1:16">
+      <c r="A27">
+        <v>0</v>
+      </c>
+      <c r="B27" t="s">
+        <v>76</v>
+      </c>
+      <c r="C27">
+        <v>0.003209630870436986</v>
+      </c>
+      <c r="D27">
+        <v>0.001841589575633407</v>
+      </c>
+      <c r="E27">
+        <v>0.01186717953532934</v>
+      </c>
+      <c r="F27">
+        <v>0.001973158912733197</v>
+      </c>
+      <c r="G27">
+        <v>0.001937946770340204</v>
+      </c>
+      <c r="H27">
+        <v>1.000909302984622</v>
+      </c>
+      <c r="I27">
+        <v>0.04897143790601073</v>
+      </c>
+      <c r="J27">
+        <v>0.155183419585228</v>
+      </c>
+      <c r="K27">
+        <v>413.6163635253906</v>
+      </c>
+      <c r="L27">
+        <v>0.6792340278625488</v>
+      </c>
+      <c r="M27">
+        <v>8.882132530212402</v>
+      </c>
+      <c r="N27" t="s">
+        <v>316</v>
+      </c>
+      <c r="O27" t="s">
+        <v>376</v>
+      </c>
+      <c r="P27" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="28" spans="1:16">
+      <c r="A28">
+        <v>0</v>
+      </c>
+      <c r="B28" t="s">
+        <v>77</v>
+      </c>
+      <c r="C28">
+        <v>0.007765530741508959</v>
+      </c>
+      <c r="D28">
+        <v>0.004378229845315218</v>
+      </c>
+      <c r="E28">
+        <v>0.02960263378918171</v>
+      </c>
+      <c r="F28">
+        <v>0.002309937262907624</v>
+      </c>
+      <c r="G28">
+        <v>0.002341942163184285</v>
+      </c>
+      <c r="H28">
+        <v>1.001284580885936</v>
+      </c>
+      <c r="I28">
+        <v>0.04964286393453234</v>
+      </c>
+      <c r="J28">
+        <v>0.1479000151157379</v>
+      </c>
+      <c r="K28">
+        <v>1642408.5</v>
+      </c>
+      <c r="L28">
+        <v>1.694346785545349</v>
+      </c>
+      <c r="M28">
+        <v>8.46525764465332</v>
+      </c>
+      <c r="N28" t="s">
+        <v>317</v>
+      </c>
+      <c r="O28" t="s">
+        <v>377</v>
+      </c>
+      <c r="P28" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="29" spans="1:16">
+      <c r="A29">
+        <v>0</v>
+      </c>
+      <c r="B29" t="s">
+        <v>78</v>
+      </c>
+      <c r="C29">
+        <v>0.0152539699883258</v>
+      </c>
+      <c r="D29">
+        <v>0.008454234339296818</v>
+      </c>
+      <c r="E29">
+        <v>0.05878772214055061</v>
+      </c>
+      <c r="F29">
+        <v>0.00251486012712121</v>
+      </c>
+      <c r="G29">
+        <v>0.002662759041413665</v>
+      </c>
+      <c r="H29">
+        <v>1.001778965707161</v>
+      </c>
+      <c r="I29">
+        <v>0.05020788020867947</v>
+      </c>
+      <c r="J29">
+        <v>0.1438095271587372</v>
+      </c>
+      <c r="K29">
+        <v>949833957376</v>
+      </c>
+      <c r="L29">
+        <v>3.364794731140137</v>
+      </c>
+      <c r="M29">
+        <v>8.231132507324219</v>
+      </c>
+      <c r="N29" t="s">
+        <v>318</v>
+      </c>
+      <c r="O29" t="s">
+        <v>378</v>
+      </c>
+      <c r="P29" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="30" spans="1:16">
+      <c r="A30">
+        <v>0</v>
+      </c>
+      <c r="B30" t="s">
+        <v>79</v>
+      </c>
+      <c r="C30">
+        <v>0.03771405180667901</v>
+      </c>
+      <c r="D30">
+        <v>0.02151268906891346</v>
+      </c>
+      <c r="E30">
+        <v>0.1400909274816513</v>
+      </c>
+      <c r="F30">
+        <v>0.002763934200629592</v>
+      </c>
+      <c r="G30">
+        <v>0.003213431686162949</v>
+      </c>
+      <c r="H30">
+        <v>1.002390026334335</v>
+      </c>
+      <c r="I30">
+        <v>0.05581022428338915</v>
+      </c>
+      <c r="J30">
+        <v>0.1535623222589493</v>
+      </c>
+      <c r="K30">
+        <v>1.917153854834016E+30</v>
+      </c>
+      <c r="L30">
+        <v>8.018293380737305</v>
+      </c>
+      <c r="M30">
+        <v>8.789346694946289</v>
+      </c>
+      <c r="N30" t="s">
+        <v>319</v>
+      </c>
+      <c r="O30" t="s">
+        <v>379</v>
+      </c>
+      <c r="P30" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="31" spans="1:16">
+      <c r="A31">
+        <v>0</v>
+      </c>
+      <c r="B31" t="s">
+        <v>80</v>
+      </c>
+      <c r="C31">
+        <v>0.07419103931220386</v>
+      </c>
+      <c r="D31">
+        <v>0.04192589223384857</v>
+      </c>
+      <c r="E31">
+        <v>0.27972811460495</v>
+      </c>
+      <c r="F31">
+        <v>0.002951104659587145</v>
+      </c>
+      <c r="G31">
+        <v>0.003436560276895761</v>
+      </c>
+      <c r="H31">
+        <v>1.003427172582619</v>
+      </c>
+      <c r="I31">
+        <v>0.06555952123015193</v>
+      </c>
+      <c r="J31">
+        <v>0.1498808711767197</v>
+      </c>
+      <c r="K31" t="s">
+        <v>110</v>
+      </c>
+      <c r="L31">
+        <v>16.01061630249023</v>
+      </c>
+      <c r="M31">
+        <v>8.578634262084961</v>
+      </c>
+      <c r="N31" t="s">
+        <v>320</v>
+      </c>
+      <c r="O31" t="s">
+        <v>380</v>
+      </c>
+      <c r="P31" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="32" spans="1:16">
+      <c r="A32">
+        <v>0</v>
+      </c>
+      <c r="B32" t="s">
+        <v>81</v>
+      </c>
+      <c r="C32">
+        <v>0.0003351072633730087</v>
+      </c>
+      <c r="D32">
+        <v>-0.0001817990851122886</v>
+      </c>
+      <c r="E32">
+        <v>0.002876998391002417</v>
+      </c>
+      <c r="F32">
+        <v>0.0009098531445488334</v>
+      </c>
+      <c r="G32">
+        <v>0.0009545031352899969</v>
+      </c>
+      <c r="H32">
+        <v>1.000261297454019</v>
+      </c>
+      <c r="I32">
+        <v>0.0491449456388782</v>
+      </c>
+      <c r="J32">
+        <v>-0.06319054216146469</v>
+      </c>
+      <c r="K32">
+        <v>-0.4487748146057129</v>
+      </c>
+      <c r="L32">
+        <v>0.1646688878536224</v>
+      </c>
+      <c r="M32">
+        <v>-3.616796016693115</v>
+      </c>
+      <c r="N32" t="s">
+        <v>321</v>
+      </c>
+      <c r="O32" t="s">
+        <v>381</v>
+      </c>
+      <c r="P32" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="33" spans="1:16">
+      <c r="A33">
+        <v>0</v>
+      </c>
+      <c r="B33" t="s">
+        <v>82</v>
+      </c>
+      <c r="C33">
+        <v>0.0004403014470678849</v>
+      </c>
+      <c r="D33">
+        <v>-4.534115305432351E-06</v>
+      </c>
+      <c r="E33">
+        <v>0.003605677746236324</v>
+      </c>
+      <c r="F33">
+        <v>0.001062995637767017</v>
+      </c>
+      <c r="G33">
+        <v>0.00105878512840718</v>
+      </c>
+      <c r="H33">
+        <v>1.000448543632522</v>
+      </c>
+      <c r="I33">
+        <v>0.04907647773420009</v>
+      </c>
+      <c r="J33">
+        <v>-0.001257493160665035</v>
+      </c>
+      <c r="K33">
+        <v>-0.01473057270050049</v>
+      </c>
+      <c r="L33">
+        <v>0.2063758373260498</v>
+      </c>
+      <c r="M33">
+        <v>-0.07197432219982147</v>
+      </c>
+      <c r="N33" t="s">
+        <v>322</v>
+      </c>
+      <c r="O33" t="s">
+        <v>382</v>
+      </c>
+      <c r="P33" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="34" spans="1:16">
+      <c r="A34">
+        <v>0</v>
+      </c>
+      <c r="B34" t="s">
+        <v>83</v>
+      </c>
+      <c r="C34">
+        <v>0.000542053180132204</v>
+      </c>
+      <c r="D34">
+        <v>0.000110657223558519</v>
+      </c>
+      <c r="E34">
+        <v>0.004281311761587858</v>
+      </c>
+      <c r="F34">
+        <v>0.00118694722186774</v>
+      </c>
+      <c r="G34">
+        <v>0.001153446966782212</v>
+      </c>
+      <c r="H34">
+        <v>1.000515182301191</v>
+      </c>
+      <c r="I34">
+        <v>0.04911721285939042</v>
+      </c>
+      <c r="J34">
+        <v>0.02584657073020935</v>
+      </c>
+      <c r="K34">
+        <v>0.4367612600326538</v>
+      </c>
+      <c r="L34">
+        <v>0.2450466603040695</v>
+      </c>
+      <c r="M34">
+        <v>1.479363441467285</v>
+      </c>
+      <c r="N34" t="s">
+        <v>323</v>
+      </c>
+      <c r="O34" t="s">
+        <v>383</v>
+      </c>
+      <c r="P34" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="35" spans="1:16">
+      <c r="A35">
+        <v>0</v>
+      </c>
+      <c r="B35" t="s">
+        <v>84</v>
+      </c>
+      <c r="C35">
+        <v>0.001026715951757813</v>
+      </c>
+      <c r="D35">
+        <v>0.0005542653962038457</v>
+      </c>
+      <c r="E35">
+        <v>0.008555739186704159</v>
+      </c>
+      <c r="F35">
+        <v>0.001493633259087801</v>
+      </c>
+      <c r="G35">
+        <v>0.001396391657181084</v>
+      </c>
+      <c r="H35">
+        <v>1.000587340777664</v>
+      </c>
+      <c r="I35">
+        <v>0.04923041825282931</v>
+      </c>
+      <c r="J35">
+        <v>0.06478288024663925</v>
+      </c>
+      <c r="K35">
+        <v>5.143899440765381</v>
+      </c>
+      <c r="L35">
+        <v>0.4896993041038513</v>
+      </c>
+      <c r="M35">
+        <v>3.707935571670532</v>
+      </c>
+      <c r="N35" t="s">
+        <v>324</v>
+      </c>
+      <c r="O35" t="s">
+        <v>384</v>
+      </c>
+      <c r="P35" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="36" spans="1:16">
+      <c r="A36">
+        <v>0</v>
+      </c>
+      <c r="B36" t="s">
+        <v>85</v>
+      </c>
+      <c r="C36">
+        <v>0.001953445901313399</v>
+      </c>
+      <c r="D36">
+        <v>0.001371302641928196</v>
+      </c>
+      <c r="E36">
+        <v>0.01759788766503334</v>
+      </c>
+      <c r="F36">
+        <v>0.001765078864991665</v>
+      </c>
+      <c r="G36">
+        <v>0.001654477789998055</v>
+      </c>
+      <c r="H36">
+        <v>1.000657424691578</v>
+      </c>
+      <c r="I36">
+        <v>0.04940889885862011</v>
+      </c>
+      <c r="J36">
+        <v>0.07792427390813828</v>
+      </c>
+      <c r="K36">
+        <v>88.04885101318359</v>
+      </c>
+      <c r="L36">
+        <v>1.007238864898682</v>
+      </c>
+      <c r="M36">
+        <v>4.460101127624512</v>
+      </c>
+      <c r="N36" t="s">
+        <v>325</v>
+      </c>
+      <c r="O36" t="s">
+        <v>385</v>
+      </c>
+      <c r="P36" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="37" spans="1:16">
+      <c r="A37">
+        <v>0</v>
+      </c>
+      <c r="B37" t="s">
+        <v>86</v>
+      </c>
+      <c r="C37">
+        <v>0.00375888070172166</v>
+      </c>
+      <c r="D37">
+        <v>0.002606706460937858</v>
+      </c>
+      <c r="E37">
+        <v>0.03448329493403435</v>
+      </c>
+      <c r="F37">
+        <v>0.002029479248449206</v>
+      </c>
+      <c r="G37">
+        <v>0.002012345939874649</v>
+      </c>
+      <c r="H37">
+        <v>1.000728884425843</v>
+      </c>
+      <c r="I37">
+        <v>0.04911341500339021</v>
+      </c>
+      <c r="J37">
+        <v>0.07559331506490707</v>
+      </c>
+      <c r="K37">
+        <v>5056.3623046875</v>
+      </c>
+      <c r="L37">
+        <v>1.973698019981384</v>
+      </c>
+      <c r="M37">
+        <v>4.326685428619385</v>
+      </c>
+      <c r="N37" t="s">
+        <v>326</v>
+      </c>
+      <c r="O37" t="s">
+        <v>386</v>
+      </c>
+      <c r="P37" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="38" spans="1:16">
+      <c r="A38">
+        <v>0</v>
+      </c>
+      <c r="B38" t="s">
+        <v>87</v>
+      </c>
+      <c r="C38">
+        <v>0.00911686123132811</v>
+      </c>
+      <c r="D38">
+        <v>0.006241131108254194</v>
+      </c>
+      <c r="E38">
+        <v>0.08922205120325089</v>
+      </c>
+      <c r="F38">
+        <v>0.002382248174399137</v>
+      </c>
+      <c r="G38">
+        <v>0.00245385430753231</v>
+      </c>
+      <c r="H38">
+        <v>1.001253823366736</v>
+      </c>
+      <c r="I38">
+        <v>0.04974047858626677</v>
+      </c>
+      <c r="J38">
+        <v>0.06995054334402084</v>
+      </c>
+      <c r="K38">
+        <v>711048128</v>
+      </c>
+      <c r="L38">
+        <v>5.106744766235352</v>
+      </c>
+      <c r="M38">
+        <v>4.003714084625244</v>
+      </c>
+      <c r="N38" t="s">
+        <v>327</v>
+      </c>
+      <c r="O38" t="s">
+        <v>387</v>
+      </c>
+      <c r="P38" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="39" spans="1:16">
+      <c r="A39">
+        <v>0</v>
+      </c>
+      <c r="B39" t="s">
+        <v>88</v>
+      </c>
+      <c r="C39">
+        <v>0.01799058025176466</v>
+      </c>
+      <c r="D39">
+        <v>0.01254036370664835</v>
+      </c>
+      <c r="E39">
+        <v>0.1899181604385376</v>
+      </c>
+      <c r="F39">
+        <v>0.00251706107519567</v>
+      </c>
+      <c r="G39">
+        <v>0.002736472990363836</v>
+      </c>
+      <c r="H39">
+        <v>1.001778965707161</v>
+      </c>
+      <c r="I39">
+        <v>0.05019527102009144</v>
+      </c>
+      <c r="J39">
+        <v>0.066030353307724</v>
+      </c>
+      <c r="K39">
+        <v>5.38033164510036E+17</v>
+      </c>
+      <c r="L39">
+        <v>10.8702220916748</v>
+      </c>
+      <c r="M39">
+        <v>3.779336452484131</v>
+      </c>
+      <c r="N39" t="s">
+        <v>328</v>
+      </c>
+      <c r="O39" t="s">
+        <v>388</v>
+      </c>
+      <c r="P39" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="40" spans="1:16">
+      <c r="A40">
+        <v>0</v>
+      </c>
+      <c r="B40" t="s">
+        <v>89</v>
+      </c>
+      <c r="C40">
+        <v>0.04421756449894186</v>
+      </c>
+      <c r="D40">
+        <v>0.02856089547276497</v>
+      </c>
+      <c r="E40">
+        <v>0.4150916635990143</v>
+      </c>
+      <c r="F40">
+        <v>0.002773036481812596</v>
+      </c>
+      <c r="G40">
+        <v>0.003276653820648789</v>
+      </c>
+      <c r="H40">
+        <v>1.002458025790339</v>
+      </c>
+      <c r="I40">
+        <v>0.05577336899009723</v>
+      </c>
+      <c r="J40">
+        <v>0.0688062384724617</v>
+      </c>
+      <c r="K40" t="s">
+        <v>110</v>
+      </c>
+      <c r="L40">
+        <v>23.75833129882812</v>
+      </c>
+      <c r="M40">
+        <v>3.938218116760254</v>
+      </c>
+      <c r="N40" t="s">
+        <v>329</v>
+      </c>
+      <c r="O40" t="s">
+        <v>389</v>
+      </c>
+      <c r="P40" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="41" spans="1:16">
+      <c r="A41">
+        <v>0</v>
+      </c>
+      <c r="B41" t="s">
+        <v>90</v>
+      </c>
+      <c r="C41">
+        <v>0.09318434450989825</v>
+      </c>
+      <c r="D41">
+        <v>0.06420988589525223</v>
+      </c>
+      <c r="E41">
+        <v>1.044713258743286</v>
+      </c>
+      <c r="F41">
+        <v>0.002966710599139333</v>
+      </c>
+      <c r="G41">
+        <v>0.003514169482514262</v>
+      </c>
+      <c r="H41">
+        <v>1.003427172582619</v>
+      </c>
+      <c r="I41">
+        <v>0.06555952123015193</v>
+      </c>
+      <c r="J41">
+        <v>0.06146173179149628</v>
+      </c>
+      <c r="K41" t="s">
+        <v>110</v>
+      </c>
+      <c r="L41">
+        <v>59.79557418823242</v>
+      </c>
+      <c r="M41">
+        <v>3.517845153808594</v>
+      </c>
+      <c r="N41" t="s">
+        <v>330</v>
+      </c>
+      <c r="O41" t="s">
+        <v>390</v>
+      </c>
+      <c r="P41" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="42" spans="1:16">
+      <c r="A42">
+        <v>0</v>
+      </c>
+      <c r="B42" t="s">
+        <v>91</v>
+      </c>
+      <c r="C42">
+        <v>0.0001578803450840063</v>
+      </c>
+      <c r="D42">
+        <v>-0.0001281119621125981</v>
+      </c>
+      <c r="E42">
+        <v>0.001794692478142679</v>
+      </c>
+      <c r="F42">
+        <v>0.001013688743114471</v>
+      </c>
+      <c r="G42">
+        <v>0.001018646406009793</v>
+      </c>
+      <c r="H42">
+        <v>1.000040517405601</v>
+      </c>
+      <c r="I42">
+        <v>0.04925923818372269</v>
+      </c>
+      <c r="J42">
+        <v>-0.07138379663228989</v>
+      </c>
+      <c r="K42">
+        <v>-0.3427237868309021</v>
+      </c>
+      <c r="L42">
+        <v>0.1027216464281082</v>
+      </c>
+      <c r="M42">
+        <v>-4.085748195648193</v>
+      </c>
+      <c r="N42" t="s">
+        <v>331</v>
+      </c>
+      <c r="O42" t="s">
+        <v>391</v>
+      </c>
+      <c r="P42" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="43" spans="1:16">
+      <c r="A43">
+        <v>0</v>
+      </c>
+      <c r="B43" t="s">
+        <v>92</v>
+      </c>
+      <c r="C43">
+        <v>0.0002003990442669997</v>
+      </c>
+      <c r="D43">
+        <v>-6.290154851740226E-05</v>
+      </c>
+      <c r="E43">
+        <v>0.002327232388779521</v>
+      </c>
+      <c r="F43">
+        <v>0.001162579748779535</v>
+      </c>
+      <c r="G43">
+        <v>0.001115540857426822</v>
+      </c>
+      <c r="H43">
+        <v>1.000163049716517</v>
+      </c>
+      <c r="I43">
+        <v>0.04930519215449514</v>
+      </c>
+      <c r="J43">
+        <v>-0.02702847681939602</v>
+      </c>
+      <c r="K43">
+        <v>-0.1861757636070251</v>
+      </c>
+      <c r="L43">
+        <v>0.1332022845745087</v>
+      </c>
+      <c r="M43">
+        <v>-1.547011375427246</v>
+      </c>
+      <c r="N43" t="s">
+        <v>332</v>
+      </c>
+      <c r="O43" t="s">
+        <v>392</v>
+      </c>
+      <c r="P43" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="44" spans="1:16">
+      <c r="A44">
+        <v>0</v>
+      </c>
+      <c r="B44" t="s">
+        <v>93</v>
+      </c>
+      <c r="C44">
+        <v>0.0002391076468513996</v>
+      </c>
+      <c r="D44">
+        <v>3.972735066781752E-05</v>
+      </c>
+      <c r="E44">
+        <v>0.002371215261518955</v>
+      </c>
+      <c r="F44">
+        <v>0.0012661621440202</v>
+      </c>
+      <c r="G44">
+        <v>0.001187456771731377</v>
+      </c>
+      <c r="H44">
+        <v>1.000244341332051</v>
+      </c>
+      <c r="I44">
+        <v>0.04929959315862163</v>
+      </c>
+      <c r="J44">
+        <v>0.01675400510430336</v>
+      </c>
+      <c r="K44">
+        <v>0.1388782262802124</v>
+      </c>
+      <c r="L44">
+        <v>0.1357197016477585</v>
+      </c>
+      <c r="M44">
+        <v>0.9589381217956543</v>
+      </c>
+      <c r="N44" t="s">
+        <v>333</v>
+      </c>
+      <c r="O44" t="s">
+        <v>393</v>
+      </c>
+      <c r="P44" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="45" spans="1:16">
+      <c r="A45">
+        <v>0</v>
+      </c>
+      <c r="B45" t="s">
+        <v>94</v>
+      </c>
+      <c r="C45">
+        <v>0.0004053901947026114</v>
+      </c>
+      <c r="D45">
+        <v>0.0003334699431434274</v>
+      </c>
+      <c r="E45">
+        <v>0.001877551199868321</v>
+      </c>
+      <c r="F45">
+        <v>0.001557462383061647</v>
+      </c>
+      <c r="G45">
+        <v>0.00142798840533942</v>
+      </c>
+      <c r="H45">
+        <v>1.000230052094138</v>
+      </c>
+      <c r="I45">
+        <v>0.04951580987079373</v>
+      </c>
+      <c r="J45">
+        <v>0.1776089817285538</v>
+      </c>
+      <c r="K45">
+        <v>1.980613946914673</v>
+      </c>
+      <c r="L45">
+        <v>0.1074641793966293</v>
+      </c>
+      <c r="M45">
+        <v>10.16569042205811</v>
+      </c>
+      <c r="N45" t="s">
+        <v>334</v>
+      </c>
+      <c r="O45" t="s">
+        <v>394</v>
+      </c>
+      <c r="P45" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="46" spans="1:16">
+      <c r="A46">
+        <v>0</v>
+      </c>
+      <c r="B46" t="s">
+        <v>95</v>
+      </c>
+      <c r="C46">
+        <v>0.0006904958197966759</v>
+      </c>
+      <c r="D46">
+        <v>0.0005985526950098574</v>
+      </c>
+      <c r="E46">
+        <v>0.003260192461311817</v>
+      </c>
+      <c r="F46">
+        <v>0.001799647812731564</v>
+      </c>
+      <c r="G46">
+        <v>0.001726460992358625</v>
+      </c>
+      <c r="H46">
+        <v>1.000249759940935</v>
+      </c>
+      <c r="I46">
+        <v>0.04958567558812052</v>
+      </c>
+      <c r="J46">
+        <v>0.183594286441803</v>
+      </c>
+      <c r="K46">
+        <v>6.101191997528076</v>
+      </c>
+      <c r="L46">
+        <v>0.1866015195846558</v>
+      </c>
+      <c r="M46">
+        <v>10.50826740264893</v>
+      </c>
+      <c r="N46" t="s">
+        <v>335</v>
+      </c>
+      <c r="O46" t="s">
+        <v>395</v>
+      </c>
+      <c r="P46" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="47" spans="1:16">
+      <c r="A47">
+        <v>0</v>
+      </c>
+      <c r="B47" t="s">
+        <v>96</v>
+      </c>
+      <c r="C47">
+        <v>0.001216440048301901</v>
+      </c>
+      <c r="D47">
+        <v>0.0009808067698031664</v>
+      </c>
+      <c r="E47">
+        <v>0.005978900007903576</v>
+      </c>
+      <c r="F47">
+        <v>0.002091237809509039</v>
+      </c>
+      <c r="G47">
+        <v>0.002098752651363611</v>
+      </c>
+      <c r="H47">
+        <v>1.000575568840191</v>
+      </c>
+      <c r="I47">
+        <v>0.04931734219433251</v>
+      </c>
+      <c r="J47">
+        <v>0.1640446782112122</v>
+      </c>
+      <c r="K47">
+        <v>23.82131958007812</v>
+      </c>
+      <c r="L47">
+        <v>0.3422104120254517</v>
+      </c>
+      <c r="M47">
+        <v>9.389318466186523</v>
+      </c>
+      <c r="N47" t="s">
+        <v>336</v>
+      </c>
+      <c r="O47" t="s">
+        <v>396</v>
+      </c>
+      <c r="P47" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="48" spans="1:16">
+      <c r="A48">
+        <v>0</v>
+      </c>
+      <c r="B48" t="s">
+        <v>97</v>
+      </c>
+      <c r="C48">
+        <v>0.002703794838778151</v>
+      </c>
+      <c r="D48">
+        <v>0.001840155688114464</v>
+      </c>
+      <c r="E48">
+        <v>0.01422779355198145</v>
+      </c>
+      <c r="F48">
+        <v>0.002406618092209101</v>
+      </c>
+      <c r="G48">
+        <v>0.002537856344133615</v>
+      </c>
+      <c r="H48">
+        <v>1.001324769815501</v>
+      </c>
+      <c r="I48">
+        <v>0.04983477923756022</v>
+      </c>
+      <c r="J48">
+        <v>0.1293352842330933</v>
+      </c>
+      <c r="K48">
+        <v>411.6814270019531</v>
+      </c>
+      <c r="L48">
+        <v>0.814346969127655</v>
+      </c>
+      <c r="M48">
+        <v>7.402679920196533</v>
+      </c>
+      <c r="N48" t="s">
+        <v>337</v>
+      </c>
+      <c r="O48" t="s">
+        <v>397</v>
+      </c>
+      <c r="P48" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="49" spans="1:16">
+      <c r="A49">
+        <v>0</v>
+      </c>
+      <c r="B49" t="s">
+        <v>98</v>
+      </c>
+      <c r="C49">
+        <v>0.005159438902871213</v>
+      </c>
+      <c r="D49">
+        <v>0.003179037244990468</v>
+      </c>
+      <c r="E49">
+        <v>0.02786662802100182</v>
+      </c>
+      <c r="F49">
+        <v>0.002557514701038599</v>
+      </c>
+      <c r="G49">
+        <v>0.002871550153940916</v>
+      </c>
+      <c r="H49">
+        <v>1.001723789783743</v>
+      </c>
+      <c r="I49">
+        <v>0.05025961951380982</v>
+      </c>
+      <c r="J49">
+        <v>0.1140804439783096</v>
+      </c>
+      <c r="K49">
+        <v>32797.06640625</v>
+      </c>
+      <c r="L49">
+        <v>1.59498405456543</v>
+      </c>
+      <c r="M49">
+        <v>6.529548168182373</v>
+      </c>
+      <c r="N49" t="s">
+        <v>338</v>
+      </c>
+      <c r="O49" t="s">
+        <v>398</v>
+      </c>
+      <c r="P49" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="50" spans="1:16">
+      <c r="A50">
+        <v>0</v>
+      </c>
+      <c r="B50" t="s">
+        <v>99</v>
+      </c>
+      <c r="C50">
+        <v>0.01231259841700836</v>
+      </c>
+      <c r="D50">
+        <v>0.006910129450261593</v>
+      </c>
+      <c r="E50">
+        <v>0.06775671988725662</v>
+      </c>
+      <c r="F50">
+        <v>0.002757431007921696</v>
+      </c>
+      <c r="G50">
+        <v>0.003301830962300301</v>
+      </c>
+      <c r="H50">
+        <v>1.002390026334335</v>
+      </c>
+      <c r="I50">
+        <v>0.05581022428338915</v>
+      </c>
+      <c r="J50">
+        <v>0.1019844114780426</v>
+      </c>
+      <c r="K50">
+        <v>6273409536</v>
+      </c>
+      <c r="L50">
+        <v>3.87814736366272</v>
+      </c>
+      <c r="M50">
+        <v>5.837215423583984</v>
+      </c>
+      <c r="N50" t="s">
+        <v>339</v>
+      </c>
+      <c r="O50" t="s">
+        <v>399</v>
+      </c>
+      <c r="P50" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="51" spans="1:16">
+      <c r="A51">
+        <v>0</v>
+      </c>
+      <c r="B51" t="s">
+        <v>100</v>
+      </c>
+      <c r="C51">
+        <v>0.02490508549204658</v>
+      </c>
+      <c r="D51">
+        <v>0.01320060715079308</v>
+      </c>
+      <c r="E51">
+        <v>0.1357249617576599</v>
+      </c>
+      <c r="F51">
+        <v>0.003000298980623484</v>
+      </c>
+      <c r="G51">
+        <v>0.003567822743207216</v>
+      </c>
+      <c r="H51">
+        <v>1.003427172582619</v>
+      </c>
+      <c r="I51">
+        <v>0.06555952123015193</v>
+      </c>
+      <c r="J51">
+        <v>0.09725998342037201</v>
+      </c>
+      <c r="K51">
+        <v>4.55316093862622E+18</v>
+      </c>
+      <c r="L51">
+        <v>7.768401622772217</v>
+      </c>
+      <c r="M51">
+        <v>5.566806316375732</v>
+      </c>
+      <c r="N51" t="s">
+        <v>340</v>
+      </c>
+      <c r="O51" t="s">
+        <v>400</v>
+      </c>
+      <c r="P51" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="52" spans="1:16">
+      <c r="A52">
+        <v>0</v>
+      </c>
+      <c r="B52" t="s">
+        <v>101</v>
+      </c>
+      <c r="C52">
+        <v>0.0001310654726840996</v>
+      </c>
+      <c r="D52">
+        <v>0.0002429722371743992</v>
+      </c>
+      <c r="E52">
+        <v>0.0006934861885383725</v>
+      </c>
+      <c r="F52">
+        <v>0.001213999232277274</v>
+      </c>
+      <c r="G52">
+        <v>0.001190320355817676</v>
+      </c>
+      <c r="H52">
+        <v>0.9993601116366884</v>
+      </c>
+      <c r="I52">
+        <v>0.04968981149406811</v>
+      </c>
+      <c r="J52">
+        <v>0.3503634929656982</v>
+      </c>
+      <c r="K52">
+        <v>1.216219186782837</v>
+      </c>
+      <c r="L52">
+        <v>0.03969261795282364</v>
+      </c>
+      <c r="M52">
+        <v>20.05352783203125</v>
+      </c>
+      <c r="N52" t="s">
+        <v>341</v>
+      </c>
+      <c r="O52" t="s">
+        <v>401</v>
+      </c>
+      <c r="P52" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="53" spans="1:16">
+      <c r="A53">
+        <v>0</v>
+      </c>
+      <c r="B53" t="s">
+        <v>102</v>
+      </c>
+      <c r="C53">
+        <v>0.0001562137327752975</v>
+      </c>
+      <c r="D53">
+        <v>0.0002900025283452123</v>
+      </c>
+      <c r="E53">
+        <v>0.0007726841140538454</v>
+      </c>
+      <c r="F53">
+        <v>0.00127503601834178</v>
+      </c>
+      <c r="G53">
+        <v>0.001231515198014677</v>
+      </c>
+      <c r="H53">
+        <v>0.9993001157562305</v>
+      </c>
+      <c r="I53">
+        <v>0.04979736190126383</v>
+      </c>
+      <c r="J53">
+        <v>0.3753183484077454</v>
+      </c>
+      <c r="K53">
+        <v>1.585763454437256</v>
+      </c>
+      <c r="L53">
+        <v>0.04422561824321747</v>
+      </c>
+      <c r="M53">
+        <v>21.48185348510742</v>
+      </c>
+      <c r="N53" t="s">
+        <v>342</v>
+      </c>
+      <c r="O53" t="s">
+        <v>402</v>
+      </c>
+      <c r="P53" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="54" spans="1:16">
+      <c r="A54">
+        <v>0</v>
+      </c>
+      <c r="B54" t="s">
+        <v>103</v>
+      </c>
+      <c r="C54">
+        <v>0.0001754297153654112</v>
+      </c>
+      <c r="D54">
+        <v>0.0003250934823881835</v>
+      </c>
+      <c r="E54">
+        <v>0.0008254284039139748</v>
+      </c>
+      <c r="F54">
+        <v>0.001324380515143275</v>
+      </c>
+      <c r="G54">
+        <v>0.001241332734934986</v>
+      </c>
+      <c r="H54">
+        <v>0.9992601700411193</v>
+      </c>
+      <c r="I54">
+        <v>0.04996897486439636</v>
+      </c>
+      <c r="J54">
+        <v>0.393848180770874</v>
+      </c>
+      <c r="K54">
+        <v>1.900262594223022</v>
+      </c>
+      <c r="L54">
+        <v>0.04724451154470444</v>
+      </c>
+      <c r="M54">
+        <v>22.54243278503418</v>
+      </c>
+      <c r="N54" t="s">
+        <v>343</v>
+      </c>
+      <c r="O54" t="s">
+        <v>403</v>
+      </c>
+      <c r="P54" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="55" spans="1:16">
+      <c r="A55">
+        <v>0</v>
+      </c>
+      <c r="B55" t="s">
+        <v>43</v>
+      </c>
+      <c r="C55">
+        <v>0.0002342180707273615</v>
+      </c>
+      <c r="D55">
+        <v>0.0004328677023295313</v>
+      </c>
+      <c r="E55">
+        <v>0.0009985072538256645</v>
+      </c>
+      <c r="F55">
+        <v>0.001458143000490963</v>
+      </c>
+      <c r="G55">
+        <v>0.001443744637072086</v>
+      </c>
+      <c r="H55">
+        <v>0.9992367906885358</v>
+      </c>
+      <c r="I55">
+        <v>0.05027968406054421</v>
+      </c>
+      <c r="J55">
+        <v>0.4335148334503174</v>
+      </c>
+      <c r="K55">
+        <v>3.127642154693604</v>
+      </c>
+      <c r="L55">
+        <v>0.05715091153979301</v>
+      </c>
+      <c r="M55">
+        <v>24.81280708312988</v>
+      </c>
+      <c r="N55" t="s">
+        <v>344</v>
+      </c>
+      <c r="O55" t="s">
+        <v>404</v>
+      </c>
+      <c r="P55" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="56" spans="1:16">
+      <c r="A56">
+        <v>0</v>
+      </c>
+      <c r="B56" t="s">
+        <v>104</v>
+      </c>
+      <c r="C56">
+        <v>0.0002905918363211231</v>
+      </c>
+      <c r="D56">
+        <v>0.000535577186383307</v>
+      </c>
+      <c r="E56">
+        <v>0.001182629959657788</v>
+      </c>
+      <c r="F56">
+        <v>0.001715286751277745</v>
+      </c>
+      <c r="G56">
+        <v>0.001796146854758263</v>
+      </c>
+      <c r="H56">
+        <v>1.000070086377417</v>
+      </c>
+      <c r="I56">
+        <v>0.04962869996169329</v>
+      </c>
+      <c r="J56">
+        <v>0.4528696238994598</v>
+      </c>
+      <c r="K56">
+        <v>4.778706550598145</v>
+      </c>
+      <c r="L56">
+        <v>0.06768942624330521</v>
+      </c>
+      <c r="M56">
+        <v>25.92060470581055</v>
+      </c>
+      <c r="N56" t="s">
+        <v>345</v>
+      </c>
+      <c r="O56" t="s">
+        <v>405</v>
+      </c>
+      <c r="P56" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="57" spans="1:16">
+      <c r="A57">
+        <v>0</v>
+      </c>
+      <c r="B57" t="s">
+        <v>105</v>
+      </c>
+      <c r="C57">
+        <v>0.0003426259323122716</v>
+      </c>
+      <c r="D57">
+        <v>0.0006306155119091272</v>
+      </c>
+      <c r="E57">
+        <v>0.001420232583768666</v>
+      </c>
+      <c r="F57">
+        <v>0.001900045434013009</v>
+      </c>
+      <c r="G57">
+        <v>0.002143960911780596</v>
+      </c>
+      <c r="H57">
+        <v>1.00081527757242</v>
+      </c>
+      <c r="I57">
+        <v>0.04902741836298091</v>
+      </c>
+      <c r="J57">
+        <v>0.4440227150917053</v>
+      </c>
+      <c r="K57">
+        <v>6.887274265289307</v>
+      </c>
+      <c r="L57">
+        <v>0.08128893375396729</v>
+      </c>
+      <c r="M57">
+        <v>25.41423988342285</v>
+      </c>
+      <c r="N57" t="s">
+        <v>346</v>
+      </c>
+      <c r="O57" t="s">
+        <v>406</v>
+      </c>
+      <c r="P57" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="58" spans="1:16">
+      <c r="A58">
+        <v>0</v>
+      </c>
+      <c r="B58" t="s">
+        <v>106</v>
+      </c>
+      <c r="C58">
+        <v>0.0004042995083488769</v>
+      </c>
+      <c r="D58">
+        <v>0.0007623520796187222</v>
+      </c>
+      <c r="E58">
+        <v>0.001960460096597672</v>
+      </c>
+      <c r="F58">
+        <v>0.002169066807255149</v>
+      </c>
+      <c r="G58">
+        <v>0.002599048428237438</v>
+      </c>
+      <c r="H58">
+        <v>1.001338849977017</v>
+      </c>
+      <c r="I58">
+        <v>0.04972432482901139</v>
+      </c>
+      <c r="J58">
+        <v>0.3888638615608215</v>
+      </c>
+      <c r="K58">
+        <v>11.13975429534912</v>
+      </c>
+      <c r="L58">
+        <v>0.1122095808386803</v>
+      </c>
+      <c r="M58">
+        <v>22.25714874267578</v>
+      </c>
+      <c r="N58" t="s">
+        <v>347</v>
+      </c>
+      <c r="O58" t="s">
+        <v>407</v>
+      </c>
+      <c r="P58" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="59" spans="1:16">
+      <c r="A59">
+        <v>0</v>
+      </c>
+      <c r="B59" t="s">
+        <v>107</v>
+      </c>
+      <c r="C59">
+        <v>0.0004467598487473802</v>
+      </c>
+      <c r="D59">
+        <v>0.000895905657671392</v>
+      </c>
+      <c r="E59">
+        <v>0.002677076263353229</v>
+      </c>
+      <c r="F59">
+        <v>0.002313330071046948</v>
+      </c>
+      <c r="G59">
+        <v>0.002888989867642522</v>
+      </c>
+      <c r="H59">
+        <v>1.001467736748441</v>
+      </c>
+      <c r="I59">
+        <v>0.05048215640946174</v>
+      </c>
+      <c r="J59">
+        <v>0.3346582353115082</v>
+      </c>
+      <c r="K59">
+        <v>17.79360008239746</v>
+      </c>
+      <c r="L59">
+        <v>0.1532260775566101</v>
+      </c>
+      <c r="M59">
+        <v>19.15461540222168</v>
+      </c>
+      <c r="N59" t="s">
+        <v>348</v>
+      </c>
+      <c r="O59" t="s">
+        <v>408</v>
+      </c>
+      <c r="P59" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="60" spans="1:16">
+      <c r="A60">
+        <v>0</v>
+      </c>
+      <c r="B60" t="s">
+        <v>108</v>
+      </c>
+      <c r="C60">
+        <v>0.000499542576613905</v>
+      </c>
+      <c r="D60">
+        <v>0.001144184032455087</v>
+      </c>
+      <c r="E60">
+        <v>0.004224067553877831</v>
+      </c>
+      <c r="F60">
+        <v>0.002482462907209992</v>
+      </c>
+      <c r="G60">
+        <v>0.003252698807045817</v>
+      </c>
+      <c r="H60">
+        <v>1.00169667473829</v>
+      </c>
+      <c r="I60">
+        <v>0.05710827073576265</v>
+      </c>
+      <c r="J60">
+        <v>0.270872563123703</v>
+      </c>
+      <c r="K60">
+        <v>41.3581428527832</v>
+      </c>
+      <c r="L60">
+        <v>0.2417702078819275</v>
+      </c>
+      <c r="M60">
+        <v>15.50375747680664</v>
+      </c>
+      <c r="N60" t="s">
+        <v>349</v>
+      </c>
+      <c r="O60" t="s">
+        <v>409</v>
+      </c>
+      <c r="P60" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="61" spans="1:16">
+      <c r="A61">
+        <v>0</v>
+      </c>
+      <c r="B61" t="s">
+        <v>109</v>
+      </c>
+      <c r="C61">
+        <v>0.0005358735532091459</v>
+      </c>
+      <c r="D61">
+        <v>0.001290365937165916</v>
+      </c>
+      <c r="E61">
+        <v>0.005600405856966972</v>
+      </c>
+      <c r="F61">
+        <v>0.002590182470157743</v>
+      </c>
+      <c r="G61">
+        <v>0.00358158815652132</v>
+      </c>
+      <c r="H61">
+        <v>1.002631578947368</v>
+      </c>
+      <c r="I61">
+        <v>0.06681109656002021</v>
+      </c>
+      <c r="J61">
+        <v>0.230405792593956</v>
+      </c>
+      <c r="K61">
+        <v>67.331298828125</v>
+      </c>
+      <c r="L61">
+        <v>0.3205468058586121</v>
+      </c>
+      <c r="M61">
+        <v>13.18758678436279</v>
+      </c>
+      <c r="N61" t="s">
+        <v>350</v>
+      </c>
+      <c r="O61" t="s">
+        <v>410</v>
+      </c>
+      <c r="P61" t="s">
+        <v>470</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="B1"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="2:2">
+      <c r="B1" t="s">
+        <v>471</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="B1"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="2:2">
+      <c r="B1" t="s">
+        <v>471</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="B1"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="2:2">
+      <c r="B1" t="s">
+        <v>471</v>
       </c>
     </row>
   </sheetData>

--- a/scripts/ffn/performance.xlsx
+++ b/scripts/ffn/performance.xlsx
@@ -8919,12 +8919,6556 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="B1"/>
+  <dimension ref="A1:B819"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="2:2">
+    <row r="1" spans="1:2">
       <c r="B1" t="s">
         <v>471</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>0.0004815417632926255</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3">
+        <v>-0.0004598749510478228</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4">
+        <v>2</v>
+      </c>
+      <c r="B4">
+        <v>0.0009129561367444694</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5">
+        <v>3</v>
+      </c>
+      <c r="B5">
+        <v>-0.0005853955517522991</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6">
+        <v>4</v>
+      </c>
+      <c r="B6">
+        <v>-0.0003387732722330838</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7">
+        <v>5</v>
+      </c>
+      <c r="B7">
+        <v>-0.0003248478751629591</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8">
+        <v>6</v>
+      </c>
+      <c r="B8">
+        <v>0.0001272060762858018</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9">
+        <v>7</v>
+      </c>
+      <c r="B9">
+        <v>0.0003380649432074279</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10">
+        <v>8</v>
+      </c>
+      <c r="B10">
+        <v>0.0005076384986750782</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11">
+        <v>9</v>
+      </c>
+      <c r="B11">
+        <v>0.0004664481093641371</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12">
+        <v>10</v>
+      </c>
+      <c r="B12">
+        <v>-0.0006087932852096856</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13">
+        <v>11</v>
+      </c>
+      <c r="B13">
+        <v>0.001499308040365577</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14">
+        <v>12</v>
+      </c>
+      <c r="B14">
+        <v>-0.002277498599141836</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="A15">
+        <v>13</v>
+      </c>
+      <c r="B15">
+        <v>-0.0009922926547005773</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16">
+        <v>14</v>
+      </c>
+      <c r="B16">
+        <v>0.0004983780672773719</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17">
+        <v>15</v>
+      </c>
+      <c r="B17">
+        <v>-0.0002391353045823053</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18">
+        <v>16</v>
+      </c>
+      <c r="B18">
+        <v>-0.0008623970788903534</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="A19">
+        <v>17</v>
+      </c>
+      <c r="B19">
+        <v>0.001023807097226381</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
+      <c r="A20">
+        <v>18</v>
+      </c>
+      <c r="B20">
+        <v>0.0004658246762119234</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
+      <c r="A21">
+        <v>19</v>
+      </c>
+      <c r="B21">
+        <v>0.0003860471188090742</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
+      <c r="A22">
+        <v>20</v>
+      </c>
+      <c r="B22">
+        <v>-0.0004176926740910858</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2">
+      <c r="A23">
+        <v>21</v>
+      </c>
+      <c r="B23">
+        <v>0.0006679535144940019</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
+      <c r="A24">
+        <v>22</v>
+      </c>
+      <c r="B24">
+        <v>0.000220796573557891</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
+      <c r="A25">
+        <v>23</v>
+      </c>
+      <c r="B25">
+        <v>0.0005109526100568473</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2">
+      <c r="A26">
+        <v>24</v>
+      </c>
+      <c r="B26">
+        <v>0.001342196366749704</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2">
+      <c r="A27">
+        <v>25</v>
+      </c>
+      <c r="B27">
+        <v>0.001176969730295241</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2">
+      <c r="A28">
+        <v>26</v>
+      </c>
+      <c r="B28">
+        <v>0.0001128494259319268</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2">
+      <c r="A29">
+        <v>27</v>
+      </c>
+      <c r="B29">
+        <v>-0.0003952961415052414</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2">
+      <c r="A30">
+        <v>28</v>
+      </c>
+      <c r="B30">
+        <v>-0.0003421083674766123</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2">
+      <c r="A31">
+        <v>29</v>
+      </c>
+      <c r="B31">
+        <v>-6.966976070543751E-05</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2">
+      <c r="A32">
+        <v>30</v>
+      </c>
+      <c r="B32">
+        <v>0.0004942692467011511</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2">
+      <c r="A33">
+        <v>31</v>
+      </c>
+      <c r="B33">
+        <v>0.0005572895752266049</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2">
+      <c r="A34">
+        <v>32</v>
+      </c>
+      <c r="B34">
+        <v>-9.473454701947048E-05</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2">
+      <c r="A35">
+        <v>33</v>
+      </c>
+      <c r="B35">
+        <v>0.0002414047921774909</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2">
+      <c r="A36">
+        <v>34</v>
+      </c>
+      <c r="B36">
+        <v>0.0006442965241149068</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2">
+      <c r="A37">
+        <v>35</v>
+      </c>
+      <c r="B37">
+        <v>3.966940857935697E-05</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2">
+      <c r="A38">
+        <v>36</v>
+      </c>
+      <c r="B38">
+        <v>0.0003960260073654354</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2">
+      <c r="A39">
+        <v>37</v>
+      </c>
+      <c r="B39">
+        <v>-0.0002909911272581667</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2">
+      <c r="A40">
+        <v>38</v>
+      </c>
+      <c r="B40">
+        <v>0.0006870554061606526</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2">
+      <c r="A41">
+        <v>39</v>
+      </c>
+      <c r="B41">
+        <v>0.0004187450977042317</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2">
+      <c r="A42">
+        <v>40</v>
+      </c>
+      <c r="B42">
+        <v>-5.010767836211016E-06</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2">
+      <c r="A43">
+        <v>41</v>
+      </c>
+      <c r="B43">
+        <v>0.0007542027160525322</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2">
+      <c r="A44">
+        <v>42</v>
+      </c>
+      <c r="B44">
+        <v>-0.0009821953717619181</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2">
+      <c r="A45">
+        <v>43</v>
+      </c>
+      <c r="B45">
+        <v>0.0008601841400377452</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2">
+      <c r="A46">
+        <v>44</v>
+      </c>
+      <c r="B46">
+        <v>0.0008551938808523118</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2">
+      <c r="A47">
+        <v>45</v>
+      </c>
+      <c r="B47">
+        <v>0.000122266574180685</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2">
+      <c r="A48">
+        <v>46</v>
+      </c>
+      <c r="B48">
+        <v>-0.0001134760386776179</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2">
+      <c r="A49">
+        <v>47</v>
+      </c>
+      <c r="B49">
+        <v>0.0005125039606355131</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2">
+      <c r="A50">
+        <v>48</v>
+      </c>
+      <c r="B50">
+        <v>0.0001080968795577064</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2">
+      <c r="A51">
+        <v>49</v>
+      </c>
+      <c r="B51">
+        <v>-5.035263893660158E-05</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2">
+      <c r="A52">
+        <v>50</v>
+      </c>
+      <c r="B52">
+        <v>0.001800431869924068</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2">
+      <c r="A53">
+        <v>51</v>
+      </c>
+      <c r="B53">
+        <v>-8.059765241341665E-05</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2">
+      <c r="A54">
+        <v>52</v>
+      </c>
+      <c r="B54">
+        <v>-0.0002397980715613812</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2">
+      <c r="A55">
+        <v>53</v>
+      </c>
+      <c r="B55">
+        <v>0.001049065380357206</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2">
+      <c r="A56">
+        <v>54</v>
+      </c>
+      <c r="B56">
+        <v>-0.0005824248655699193</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2">
+      <c r="A57">
+        <v>55</v>
+      </c>
+      <c r="B57">
+        <v>0.0006843007286079228</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2">
+      <c r="A58">
+        <v>56</v>
+      </c>
+      <c r="B58">
+        <v>-0.0006823926814831793</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2">
+      <c r="A59">
+        <v>57</v>
+      </c>
+      <c r="B59">
+        <v>5.972682265564799E-05</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2">
+      <c r="A60">
+        <v>58</v>
+      </c>
+      <c r="B60">
+        <v>0.0002847832220140845</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2">
+      <c r="A61">
+        <v>59</v>
+      </c>
+      <c r="B61">
+        <v>5.141249494045042E-05</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2">
+      <c r="A62">
+        <v>60</v>
+      </c>
+      <c r="B62">
+        <v>0.0001430880365660414</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2">
+      <c r="A63">
+        <v>61</v>
+      </c>
+      <c r="B63">
+        <v>-0.0004216849047224969</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2">
+      <c r="A64">
+        <v>62</v>
+      </c>
+      <c r="B64">
+        <v>0.0004916769685223699</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2">
+      <c r="A65">
+        <v>63</v>
+      </c>
+      <c r="B65">
+        <v>0.001570307649672031</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2">
+      <c r="A66">
+        <v>64</v>
+      </c>
+      <c r="B66">
+        <v>0.0004793698899447918</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2">
+      <c r="A67">
+        <v>65</v>
+      </c>
+      <c r="B67">
+        <v>0.0004150653257966042</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2">
+      <c r="A68">
+        <v>66</v>
+      </c>
+      <c r="B68">
+        <v>0.0003312237677164376</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2">
+      <c r="A69">
+        <v>67</v>
+      </c>
+      <c r="B69">
+        <v>0.0003258643264416605</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2">
+      <c r="A70">
+        <v>68</v>
+      </c>
+      <c r="B70">
+        <v>0.000593189150094986</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2">
+      <c r="A71">
+        <v>69</v>
+      </c>
+      <c r="B71">
+        <v>0.0003598900511860847</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2">
+      <c r="A72">
+        <v>70</v>
+      </c>
+      <c r="B72">
+        <v>-0.0005234242998994887</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2">
+      <c r="A73">
+        <v>71</v>
+      </c>
+      <c r="B73">
+        <v>-0.001548427506349981</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2">
+      <c r="A74">
+        <v>72</v>
+      </c>
+      <c r="B74">
+        <v>0.0007466234965249896</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2">
+      <c r="A75">
+        <v>73</v>
+      </c>
+      <c r="B75">
+        <v>0.0008498377283103764</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2">
+      <c r="A76">
+        <v>74</v>
+      </c>
+      <c r="B76">
+        <v>0.001446795184165239</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2">
+      <c r="A77">
+        <v>75</v>
+      </c>
+      <c r="B77">
+        <v>-0.001236826414242387</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2">
+      <c r="A78">
+        <v>76</v>
+      </c>
+      <c r="B78">
+        <v>0.003121918765828013</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2">
+      <c r="A79">
+        <v>77</v>
+      </c>
+      <c r="B79">
+        <v>0.0009387371246702969</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2">
+      <c r="A80">
+        <v>78</v>
+      </c>
+      <c r="B80">
+        <v>-5.615257032332011E-05</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2">
+      <c r="A81">
+        <v>79</v>
+      </c>
+      <c r="B81">
+        <v>0.0003380552225280553</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2">
+      <c r="A82">
+        <v>80</v>
+      </c>
+      <c r="B82">
+        <v>0.0003219686332158744</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2">
+      <c r="A83">
+        <v>81</v>
+      </c>
+      <c r="B83">
+        <v>0.0003044333425350487</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2">
+      <c r="A84">
+        <v>82</v>
+      </c>
+      <c r="B84">
+        <v>7.025830564089119E-05</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2">
+      <c r="A85">
+        <v>83</v>
+      </c>
+      <c r="B85">
+        <v>-0.0002661593607626855</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2">
+      <c r="A86">
+        <v>84</v>
+      </c>
+      <c r="B86">
+        <v>-0.0001202814164571464</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2">
+      <c r="A87">
+        <v>85</v>
+      </c>
+      <c r="B87">
+        <v>-0.0003536884905770421</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2">
+      <c r="A88">
+        <v>86</v>
+      </c>
+      <c r="B88">
+        <v>0.0001021427815430798</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2">
+      <c r="A89">
+        <v>87</v>
+      </c>
+      <c r="B89">
+        <v>-0.0004862530913669616</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2">
+      <c r="A90">
+        <v>88</v>
+      </c>
+      <c r="B90">
+        <v>0.0003261373494751751</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2">
+      <c r="A91">
+        <v>89</v>
+      </c>
+      <c r="B91">
+        <v>0.0002461868862155825</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2">
+      <c r="A92">
+        <v>90</v>
+      </c>
+      <c r="B92">
+        <v>4.183977216598578E-05</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2">
+      <c r="A93">
+        <v>91</v>
+      </c>
+      <c r="B93">
+        <v>-0.0003252324822824448</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2">
+      <c r="A94">
+        <v>92</v>
+      </c>
+      <c r="B94">
+        <v>0.0002544636954553425</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2">
+      <c r="A95">
+        <v>93</v>
+      </c>
+      <c r="B95">
+        <v>0.0008955897064879537</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2">
+      <c r="A96">
+        <v>94</v>
+      </c>
+      <c r="B96">
+        <v>-0.0002906006702687591</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2">
+      <c r="A97">
+        <v>95</v>
+      </c>
+      <c r="B97">
+        <v>0.0001912132574943826</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2">
+      <c r="A98">
+        <v>96</v>
+      </c>
+      <c r="B98">
+        <v>0.000262852234300226</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2">
+      <c r="A99">
+        <v>97</v>
+      </c>
+      <c r="B99">
+        <v>0.0001461170031689107</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2">
+      <c r="A100">
+        <v>98</v>
+      </c>
+      <c r="B100">
+        <v>6.007137926644646E-05</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2">
+      <c r="A101">
+        <v>99</v>
+      </c>
+      <c r="B101">
+        <v>-0.0002898257516790181</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2">
+      <c r="A102">
+        <v>100</v>
+      </c>
+      <c r="B102">
+        <v>3.136350642307661E-05</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2">
+      <c r="A103">
+        <v>101</v>
+      </c>
+      <c r="B103">
+        <v>-0.0001149837189586833</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2">
+      <c r="A104">
+        <v>102</v>
+      </c>
+      <c r="B104">
+        <v>0.0001517460477771237</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2">
+      <c r="A105">
+        <v>103</v>
+      </c>
+      <c r="B105">
+        <v>0.0004230262711644173</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2">
+      <c r="A106">
+        <v>104</v>
+      </c>
+      <c r="B106">
+        <v>0.0003314934438094497</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2">
+      <c r="A107">
+        <v>105</v>
+      </c>
+      <c r="B107">
+        <v>0.0008690845570527017</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2">
+      <c r="A108">
+        <v>106</v>
+      </c>
+      <c r="B108">
+        <v>0.001558320363983512</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2">
+      <c r="A109">
+        <v>107</v>
+      </c>
+      <c r="B109">
+        <v>-0.0001913356099976227</v>
+      </c>
+    </row>
+    <row r="110" spans="1:2">
+      <c r="A110">
+        <v>108</v>
+      </c>
+      <c r="B110">
+        <v>0.0006792999338358641</v>
+      </c>
+    </row>
+    <row r="111" spans="1:2">
+      <c r="A111">
+        <v>109</v>
+      </c>
+      <c r="B111">
+        <v>0.001201241742819548</v>
+      </c>
+    </row>
+    <row r="112" spans="1:2">
+      <c r="A112">
+        <v>110</v>
+      </c>
+      <c r="B112">
+        <v>0.0001111450110329315</v>
+      </c>
+    </row>
+    <row r="113" spans="1:2">
+      <c r="A113">
+        <v>111</v>
+      </c>
+      <c r="B113">
+        <v>-0.0002534570812713355</v>
+      </c>
+    </row>
+    <row r="114" spans="1:2">
+      <c r="A114">
+        <v>112</v>
+      </c>
+      <c r="B114">
+        <v>-2.762743679340929E-05</v>
+      </c>
+    </row>
+    <row r="115" spans="1:2">
+      <c r="A115">
+        <v>113</v>
+      </c>
+      <c r="B115">
+        <v>-6.779573595849797E-06</v>
+      </c>
+    </row>
+    <row r="116" spans="1:2">
+      <c r="A116">
+        <v>114</v>
+      </c>
+      <c r="B116">
+        <v>0.0002646924986038357</v>
+      </c>
+    </row>
+    <row r="117" spans="1:2">
+      <c r="A117">
+        <v>115</v>
+      </c>
+      <c r="B117">
+        <v>0.001575721660628915</v>
+      </c>
+    </row>
+    <row r="118" spans="1:2">
+      <c r="A118">
+        <v>116</v>
+      </c>
+      <c r="B118">
+        <v>-0.000544231035746634</v>
+      </c>
+    </row>
+    <row r="119" spans="1:2">
+      <c r="A119">
+        <v>117</v>
+      </c>
+      <c r="B119">
+        <v>0.001230990746989846</v>
+      </c>
+    </row>
+    <row r="120" spans="1:2">
+      <c r="A120">
+        <v>118</v>
+      </c>
+      <c r="B120">
+        <v>-0.0001574863708810881</v>
+      </c>
+    </row>
+    <row r="121" spans="1:2">
+      <c r="A121">
+        <v>119</v>
+      </c>
+      <c r="B121">
+        <v>-0.0002894357894547284</v>
+      </c>
+    </row>
+    <row r="122" spans="1:2">
+      <c r="A122">
+        <v>120</v>
+      </c>
+      <c r="B122">
+        <v>0.0004994977498427033</v>
+      </c>
+    </row>
+    <row r="123" spans="1:2">
+      <c r="A123">
+        <v>121</v>
+      </c>
+      <c r="B123">
+        <v>-0.0001839421747718006</v>
+      </c>
+    </row>
+    <row r="124" spans="1:2">
+      <c r="A124">
+        <v>122</v>
+      </c>
+      <c r="B124">
+        <v>0.0003701626555994153</v>
+      </c>
+    </row>
+    <row r="125" spans="1:2">
+      <c r="A125">
+        <v>123</v>
+      </c>
+      <c r="B125">
+        <v>0.000597109436057508</v>
+      </c>
+    </row>
+    <row r="126" spans="1:2">
+      <c r="A126">
+        <v>124</v>
+      </c>
+      <c r="B126">
+        <v>0.0003623641096055508</v>
+      </c>
+    </row>
+    <row r="127" spans="1:2">
+      <c r="A127">
+        <v>125</v>
+      </c>
+      <c r="B127">
+        <v>0.001692224876023829</v>
+      </c>
+    </row>
+    <row r="128" spans="1:2">
+      <c r="A128">
+        <v>126</v>
+      </c>
+      <c r="B128">
+        <v>3.394159284653142E-05</v>
+      </c>
+    </row>
+    <row r="129" spans="1:2">
+      <c r="A129">
+        <v>127</v>
+      </c>
+      <c r="B129">
+        <v>7.751525845378637E-05</v>
+      </c>
+    </row>
+    <row r="130" spans="1:2">
+      <c r="A130">
+        <v>128</v>
+      </c>
+      <c r="B130">
+        <v>0.0005227659712545574</v>
+      </c>
+    </row>
+    <row r="131" spans="1:2">
+      <c r="A131">
+        <v>129</v>
+      </c>
+      <c r="B131">
+        <v>0.001256181625649333</v>
+      </c>
+    </row>
+    <row r="132" spans="1:2">
+      <c r="A132">
+        <v>130</v>
+      </c>
+      <c r="B132">
+        <v>-0.0001141136672231369</v>
+      </c>
+    </row>
+    <row r="133" spans="1:2">
+      <c r="A133">
+        <v>131</v>
+      </c>
+      <c r="B133">
+        <v>-0.000232029051403515</v>
+      </c>
+    </row>
+    <row r="134" spans="1:2">
+      <c r="A134">
+        <v>132</v>
+      </c>
+      <c r="B134">
+        <v>0.0004438167088665068</v>
+      </c>
+    </row>
+    <row r="135" spans="1:2">
+      <c r="A135">
+        <v>133</v>
+      </c>
+      <c r="B135">
+        <v>-1.916560222525732E-06</v>
+      </c>
+    </row>
+    <row r="136" spans="1:2">
+      <c r="A136">
+        <v>134</v>
+      </c>
+      <c r="B136">
+        <v>0.0002425614366075024</v>
+      </c>
+    </row>
+    <row r="137" spans="1:2">
+      <c r="A137">
+        <v>135</v>
+      </c>
+      <c r="B137">
+        <v>0.0010159348603338</v>
+      </c>
+    </row>
+    <row r="138" spans="1:2">
+      <c r="A138">
+        <v>136</v>
+      </c>
+      <c r="B138">
+        <v>0.000182682168087922</v>
+      </c>
+    </row>
+    <row r="139" spans="1:2">
+      <c r="A139">
+        <v>137</v>
+      </c>
+      <c r="B139">
+        <v>-0.000244050461333245</v>
+      </c>
+    </row>
+    <row r="140" spans="1:2">
+      <c r="A140">
+        <v>138</v>
+      </c>
+      <c r="B140">
+        <v>0.000666416366584599</v>
+      </c>
+    </row>
+    <row r="141" spans="1:2">
+      <c r="A141">
+        <v>139</v>
+      </c>
+      <c r="B141">
+        <v>1.093416085495846E-05</v>
+      </c>
+    </row>
+    <row r="142" spans="1:2">
+      <c r="A142">
+        <v>140</v>
+      </c>
+      <c r="B142">
+        <v>-0.0005924905999563634</v>
+      </c>
+    </row>
+    <row r="143" spans="1:2">
+      <c r="A143">
+        <v>141</v>
+      </c>
+      <c r="B143">
+        <v>0.003703865921124816</v>
+      </c>
+    </row>
+    <row r="144" spans="1:2">
+      <c r="A144">
+        <v>142</v>
+      </c>
+      <c r="B144">
+        <v>0.001162500819191337</v>
+      </c>
+    </row>
+    <row r="145" spans="1:2">
+      <c r="A145">
+        <v>143</v>
+      </c>
+      <c r="B145">
+        <v>0.000351950729964301</v>
+      </c>
+    </row>
+    <row r="146" spans="1:2">
+      <c r="A146">
+        <v>144</v>
+      </c>
+      <c r="B146">
+        <v>0.0003880771982949227</v>
+      </c>
+    </row>
+    <row r="147" spans="1:2">
+      <c r="A147">
+        <v>145</v>
+      </c>
+      <c r="B147">
+        <v>-2.083189974655397E-05</v>
+      </c>
+    </row>
+    <row r="148" spans="1:2">
+      <c r="A148">
+        <v>146</v>
+      </c>
+      <c r="B148">
+        <v>0.0009466063929721713</v>
+      </c>
+    </row>
+    <row r="149" spans="1:2">
+      <c r="A149">
+        <v>147</v>
+      </c>
+      <c r="B149">
+        <v>0.0007062680087983608</v>
+      </c>
+    </row>
+    <row r="150" spans="1:2">
+      <c r="A150">
+        <v>148</v>
+      </c>
+      <c r="B150">
+        <v>0.0005109435878694057</v>
+      </c>
+    </row>
+    <row r="151" spans="1:2">
+      <c r="A151">
+        <v>149</v>
+      </c>
+      <c r="B151">
+        <v>0.0002678105374798179</v>
+      </c>
+    </row>
+    <row r="152" spans="1:2">
+      <c r="A152">
+        <v>150</v>
+      </c>
+      <c r="B152">
+        <v>4.238574183546007E-05</v>
+      </c>
+    </row>
+    <row r="153" spans="1:2">
+      <c r="A153">
+        <v>151</v>
+      </c>
+      <c r="B153">
+        <v>0.000616351724602282</v>
+      </c>
+    </row>
+    <row r="154" spans="1:2">
+      <c r="A154">
+        <v>152</v>
+      </c>
+      <c r="B154">
+        <v>-0.0004299857246223837</v>
+      </c>
+    </row>
+    <row r="155" spans="1:2">
+      <c r="A155">
+        <v>153</v>
+      </c>
+      <c r="B155">
+        <v>-0.001082814414985478</v>
+      </c>
+    </row>
+    <row r="156" spans="1:2">
+      <c r="A156">
+        <v>154</v>
+      </c>
+      <c r="B156">
+        <v>0.002117958385497332</v>
+      </c>
+    </row>
+    <row r="157" spans="1:2">
+      <c r="A157">
+        <v>155</v>
+      </c>
+      <c r="B157">
+        <v>0.0002358808123972267</v>
+      </c>
+    </row>
+    <row r="158" spans="1:2">
+      <c r="A158">
+        <v>156</v>
+      </c>
+      <c r="B158">
+        <v>-4.339242150308564E-05</v>
+      </c>
+    </row>
+    <row r="159" spans="1:2">
+      <c r="A159">
+        <v>157</v>
+      </c>
+      <c r="B159">
+        <v>0.0009470818331465125</v>
+      </c>
+    </row>
+    <row r="160" spans="1:2">
+      <c r="A160">
+        <v>158</v>
+      </c>
+      <c r="B160">
+        <v>0.0001799996680347249</v>
+      </c>
+    </row>
+    <row r="161" spans="1:2">
+      <c r="A161">
+        <v>159</v>
+      </c>
+      <c r="B161">
+        <v>9.777554078027606E-05</v>
+      </c>
+    </row>
+    <row r="162" spans="1:2">
+      <c r="A162">
+        <v>160</v>
+      </c>
+      <c r="B162">
+        <v>0.0001251674548257142</v>
+      </c>
+    </row>
+    <row r="163" spans="1:2">
+      <c r="A163">
+        <v>161</v>
+      </c>
+      <c r="B163">
+        <v>0.0002597104758024216</v>
+      </c>
+    </row>
+    <row r="164" spans="1:2">
+      <c r="A164">
+        <v>162</v>
+      </c>
+      <c r="B164">
+        <v>0.0005324883386492729</v>
+      </c>
+    </row>
+    <row r="165" spans="1:2">
+      <c r="A165">
+        <v>163</v>
+      </c>
+      <c r="B165">
+        <v>0.0007063840166665614</v>
+      </c>
+    </row>
+    <row r="166" spans="1:2">
+      <c r="A166">
+        <v>164</v>
+      </c>
+      <c r="B166">
+        <v>-6.040495645720512E-05</v>
+      </c>
+    </row>
+    <row r="167" spans="1:2">
+      <c r="A167">
+        <v>165</v>
+      </c>
+      <c r="B167">
+        <v>0.0008522094576619565</v>
+      </c>
+    </row>
+    <row r="168" spans="1:2">
+      <c r="A168">
+        <v>166</v>
+      </c>
+      <c r="B168">
+        <v>4.455183079699054E-05</v>
+      </c>
+    </row>
+    <row r="169" spans="1:2">
+      <c r="A169">
+        <v>167</v>
+      </c>
+      <c r="B169">
+        <v>0.002096807351335883</v>
+      </c>
+    </row>
+    <row r="170" spans="1:2">
+      <c r="A170">
+        <v>168</v>
+      </c>
+      <c r="B170">
+        <v>0.0003761691332329065</v>
+      </c>
+    </row>
+    <row r="171" spans="1:2">
+      <c r="A171">
+        <v>169</v>
+      </c>
+      <c r="B171">
+        <v>0.0001994573831325397</v>
+      </c>
+    </row>
+    <row r="172" spans="1:2">
+      <c r="A172">
+        <v>170</v>
+      </c>
+      <c r="B172">
+        <v>0.000196901397430338</v>
+      </c>
+    </row>
+    <row r="173" spans="1:2">
+      <c r="A173">
+        <v>171</v>
+      </c>
+      <c r="B173">
+        <v>0.0005015188362449408</v>
+      </c>
+    </row>
+    <row r="174" spans="1:2">
+      <c r="A174">
+        <v>172</v>
+      </c>
+      <c r="B174">
+        <v>0.0005633524269796908</v>
+      </c>
+    </row>
+    <row r="175" spans="1:2">
+      <c r="A175">
+        <v>173</v>
+      </c>
+      <c r="B175">
+        <v>0.0002760358329396695</v>
+      </c>
+    </row>
+    <row r="176" spans="1:2">
+      <c r="A176">
+        <v>174</v>
+      </c>
+      <c r="B176">
+        <v>0.0001888114638859406</v>
+      </c>
+    </row>
+    <row r="177" spans="1:2">
+      <c r="A177">
+        <v>175</v>
+      </c>
+      <c r="B177">
+        <v>0.0002449436578899622</v>
+      </c>
+    </row>
+    <row r="178" spans="1:2">
+      <c r="A178">
+        <v>176</v>
+      </c>
+      <c r="B178">
+        <v>7.925523823359981E-05</v>
+      </c>
+    </row>
+    <row r="179" spans="1:2">
+      <c r="A179">
+        <v>177</v>
+      </c>
+      <c r="B179">
+        <v>0.0002438420924590901</v>
+      </c>
+    </row>
+    <row r="180" spans="1:2">
+      <c r="A180">
+        <v>178</v>
+      </c>
+      <c r="B180">
+        <v>0.0005066008889116347</v>
+      </c>
+    </row>
+    <row r="181" spans="1:2">
+      <c r="A181">
+        <v>179</v>
+      </c>
+      <c r="B181">
+        <v>0.0002793702587950975</v>
+      </c>
+    </row>
+    <row r="182" spans="1:2">
+      <c r="A182">
+        <v>180</v>
+      </c>
+      <c r="B182">
+        <v>0.0004440765187609941</v>
+      </c>
+    </row>
+    <row r="183" spans="1:2">
+      <c r="A183">
+        <v>181</v>
+      </c>
+      <c r="B183">
+        <v>0.0002719096373766661</v>
+      </c>
+    </row>
+    <row r="184" spans="1:2">
+      <c r="A184">
+        <v>182</v>
+      </c>
+      <c r="B184">
+        <v>0.0002139512216672301</v>
+      </c>
+    </row>
+    <row r="185" spans="1:2">
+      <c r="A185">
+        <v>183</v>
+      </c>
+      <c r="B185">
+        <v>0.0001028434999170713</v>
+      </c>
+    </row>
+    <row r="186" spans="1:2">
+      <c r="A186">
+        <v>184</v>
+      </c>
+      <c r="B186">
+        <v>-4.122121481486829E-06</v>
+      </c>
+    </row>
+    <row r="187" spans="1:2">
+      <c r="A187">
+        <v>185</v>
+      </c>
+      <c r="B187">
+        <v>0.0001420389016857371</v>
+      </c>
+    </row>
+    <row r="188" spans="1:2">
+      <c r="A188">
+        <v>186</v>
+      </c>
+      <c r="B188">
+        <v>0.0004412654088810086</v>
+      </c>
+    </row>
+    <row r="189" spans="1:2">
+      <c r="A189">
+        <v>187</v>
+      </c>
+      <c r="B189">
+        <v>0.001297003822401166</v>
+      </c>
+    </row>
+    <row r="190" spans="1:2">
+      <c r="A190">
+        <v>188</v>
+      </c>
+      <c r="B190">
+        <v>0.0002929980109911412</v>
+      </c>
+    </row>
+    <row r="191" spans="1:2">
+      <c r="A191">
+        <v>189</v>
+      </c>
+      <c r="B191">
+        <v>0.0001110840967157856</v>
+      </c>
+    </row>
+    <row r="192" spans="1:2">
+      <c r="A192">
+        <v>190</v>
+      </c>
+      <c r="B192">
+        <v>0.0002434642228763551</v>
+      </c>
+    </row>
+    <row r="193" spans="1:2">
+      <c r="A193">
+        <v>191</v>
+      </c>
+      <c r="B193">
+        <v>0.0003279819793533534</v>
+      </c>
+    </row>
+    <row r="194" spans="1:2">
+      <c r="A194">
+        <v>192</v>
+      </c>
+      <c r="B194">
+        <v>0.001931836479343474</v>
+      </c>
+    </row>
+    <row r="195" spans="1:2">
+      <c r="A195">
+        <v>193</v>
+      </c>
+      <c r="B195">
+        <v>0.003781522624194622</v>
+      </c>
+    </row>
+    <row r="196" spans="1:2">
+      <c r="A196">
+        <v>194</v>
+      </c>
+      <c r="B196">
+        <v>0.001183611457236111</v>
+      </c>
+    </row>
+    <row r="197" spans="1:2">
+      <c r="A197">
+        <v>195</v>
+      </c>
+      <c r="B197">
+        <v>-0.0001101234811358154</v>
+      </c>
+    </row>
+    <row r="198" spans="1:2">
+      <c r="A198">
+        <v>196</v>
+      </c>
+      <c r="B198">
+        <v>0.0007046194514259696</v>
+      </c>
+    </row>
+    <row r="199" spans="1:2">
+      <c r="A199">
+        <v>197</v>
+      </c>
+      <c r="B199">
+        <v>1.52822831296362E-05</v>
+      </c>
+    </row>
+    <row r="200" spans="1:2">
+      <c r="A200">
+        <v>198</v>
+      </c>
+      <c r="B200">
+        <v>6.356064841384068E-05</v>
+      </c>
+    </row>
+    <row r="201" spans="1:2">
+      <c r="A201">
+        <v>199</v>
+      </c>
+      <c r="B201">
+        <v>0.0005129267810843885</v>
+      </c>
+    </row>
+    <row r="202" spans="1:2">
+      <c r="A202">
+        <v>200</v>
+      </c>
+      <c r="B202">
+        <v>1.684267408563755E-05</v>
+      </c>
+    </row>
+    <row r="203" spans="1:2">
+      <c r="A203">
+        <v>201</v>
+      </c>
+      <c r="B203">
+        <v>-3.648150232038461E-05</v>
+      </c>
+    </row>
+    <row r="204" spans="1:2">
+      <c r="A204">
+        <v>202</v>
+      </c>
+      <c r="B204">
+        <v>0.001150299794971943</v>
+      </c>
+    </row>
+    <row r="205" spans="1:2">
+      <c r="A205">
+        <v>203</v>
+      </c>
+      <c r="B205">
+        <v>0.0002159303694497794</v>
+      </c>
+    </row>
+    <row r="206" spans="1:2">
+      <c r="A206">
+        <v>204</v>
+      </c>
+      <c r="B206">
+        <v>0.0001131420794990845</v>
+      </c>
+    </row>
+    <row r="207" spans="1:2">
+      <c r="A207">
+        <v>205</v>
+      </c>
+      <c r="B207">
+        <v>0.0002821651287376881</v>
+      </c>
+    </row>
+    <row r="208" spans="1:2">
+      <c r="A208">
+        <v>206</v>
+      </c>
+      <c r="B208">
+        <v>-0.001468976028263569</v>
+      </c>
+    </row>
+    <row r="209" spans="1:2">
+      <c r="A209">
+        <v>207</v>
+      </c>
+      <c r="B209">
+        <v>0.001209229696542025</v>
+      </c>
+    </row>
+    <row r="210" spans="1:2">
+      <c r="A210">
+        <v>208</v>
+      </c>
+      <c r="B210">
+        <v>0.001283862045966089</v>
+      </c>
+    </row>
+    <row r="211" spans="1:2">
+      <c r="A211">
+        <v>209</v>
+      </c>
+      <c r="B211">
+        <v>0.0002125333703588694</v>
+      </c>
+    </row>
+    <row r="212" spans="1:2">
+      <c r="A212">
+        <v>210</v>
+      </c>
+      <c r="B212">
+        <v>-0.0001989788870560005</v>
+      </c>
+    </row>
+    <row r="213" spans="1:2">
+      <c r="A213">
+        <v>211</v>
+      </c>
+      <c r="B213">
+        <v>0.0004235624801367521</v>
+      </c>
+    </row>
+    <row r="214" spans="1:2">
+      <c r="A214">
+        <v>212</v>
+      </c>
+      <c r="B214">
+        <v>0.0001324651675531641</v>
+      </c>
+    </row>
+    <row r="215" spans="1:2">
+      <c r="A215">
+        <v>213</v>
+      </c>
+      <c r="B215">
+        <v>5.712114943889901E-05</v>
+      </c>
+    </row>
+    <row r="216" spans="1:2">
+      <c r="A216">
+        <v>214</v>
+      </c>
+      <c r="B216">
+        <v>-6.102506813476793E-05</v>
+      </c>
+    </row>
+    <row r="217" spans="1:2">
+      <c r="A217">
+        <v>215</v>
+      </c>
+      <c r="B217">
+        <v>0.0003334632201585919</v>
+      </c>
+    </row>
+    <row r="218" spans="1:2">
+      <c r="A218">
+        <v>216</v>
+      </c>
+      <c r="B218">
+        <v>0.0005424902192316949</v>
+      </c>
+    </row>
+    <row r="219" spans="1:2">
+      <c r="A219">
+        <v>217</v>
+      </c>
+      <c r="B219">
+        <v>0.0003779587568715215</v>
+      </c>
+    </row>
+    <row r="220" spans="1:2">
+      <c r="A220">
+        <v>218</v>
+      </c>
+      <c r="B220">
+        <v>0.0002136648399755359</v>
+      </c>
+    </row>
+    <row r="221" spans="1:2">
+      <c r="A221">
+        <v>219</v>
+      </c>
+      <c r="B221">
+        <v>-0.00226304680109024</v>
+      </c>
+    </row>
+    <row r="222" spans="1:2">
+      <c r="A222">
+        <v>220</v>
+      </c>
+      <c r="B222">
+        <v>0.0007078554481267929</v>
+      </c>
+    </row>
+    <row r="223" spans="1:2">
+      <c r="A223">
+        <v>221</v>
+      </c>
+      <c r="B223">
+        <v>0.0002780760987661779</v>
+      </c>
+    </row>
+    <row r="224" spans="1:2">
+      <c r="A224">
+        <v>222</v>
+      </c>
+      <c r="B224">
+        <v>0.0004915976314805448</v>
+      </c>
+    </row>
+    <row r="225" spans="1:2">
+      <c r="A225">
+        <v>223</v>
+      </c>
+      <c r="B225">
+        <v>0.0001896281319204718</v>
+      </c>
+    </row>
+    <row r="226" spans="1:2">
+      <c r="A226">
+        <v>224</v>
+      </c>
+      <c r="B226">
+        <v>0.0003779276739805937</v>
+      </c>
+    </row>
+    <row r="227" spans="1:2">
+      <c r="A227">
+        <v>225</v>
+      </c>
+      <c r="B227">
+        <v>7.345301128225401E-05</v>
+      </c>
+    </row>
+    <row r="228" spans="1:2">
+      <c r="A228">
+        <v>226</v>
+      </c>
+      <c r="B228">
+        <v>-5.10105601279065E-05</v>
+      </c>
+    </row>
+    <row r="229" spans="1:2">
+      <c r="A229">
+        <v>227</v>
+      </c>
+      <c r="B229">
+        <v>0.000433744047768414</v>
+      </c>
+    </row>
+    <row r="230" spans="1:2">
+      <c r="A230">
+        <v>228</v>
+      </c>
+      <c r="B230">
+        <v>0.000987716019153595</v>
+      </c>
+    </row>
+    <row r="231" spans="1:2">
+      <c r="A231">
+        <v>229</v>
+      </c>
+      <c r="B231">
+        <v>0.0004926710389554501</v>
+      </c>
+    </row>
+    <row r="232" spans="1:2">
+      <c r="A232">
+        <v>230</v>
+      </c>
+      <c r="B232">
+        <v>0.0002745164674706757</v>
+      </c>
+    </row>
+    <row r="233" spans="1:2">
+      <c r="A233">
+        <v>231</v>
+      </c>
+      <c r="B233">
+        <v>0.0004726333427242935</v>
+      </c>
+    </row>
+    <row r="234" spans="1:2">
+      <c r="A234">
+        <v>232</v>
+      </c>
+      <c r="B234">
+        <v>0.0001776812860043719</v>
+      </c>
+    </row>
+    <row r="235" spans="1:2">
+      <c r="A235">
+        <v>233</v>
+      </c>
+      <c r="B235">
+        <v>0.0005439265514723957</v>
+      </c>
+    </row>
+    <row r="236" spans="1:2">
+      <c r="A236">
+        <v>234</v>
+      </c>
+      <c r="B236">
+        <v>-0.0001671199715929106</v>
+      </c>
+    </row>
+    <row r="237" spans="1:2">
+      <c r="A237">
+        <v>235</v>
+      </c>
+      <c r="B237">
+        <v>0.0007018625037744641</v>
+      </c>
+    </row>
+    <row r="238" spans="1:2">
+      <c r="A238">
+        <v>236</v>
+      </c>
+      <c r="B238">
+        <v>-2.853412297554314E-05</v>
+      </c>
+    </row>
+    <row r="239" spans="1:2">
+      <c r="A239">
+        <v>237</v>
+      </c>
+      <c r="B239">
+        <v>-0.001046841847710311</v>
+      </c>
+    </row>
+    <row r="240" spans="1:2">
+      <c r="A240">
+        <v>238</v>
+      </c>
+      <c r="B240">
+        <v>1.074110514309723E-05</v>
+      </c>
+    </row>
+    <row r="241" spans="1:2">
+      <c r="A241">
+        <v>239</v>
+      </c>
+      <c r="B241">
+        <v>0.001242794911377132</v>
+      </c>
+    </row>
+    <row r="242" spans="1:2">
+      <c r="A242">
+        <v>240</v>
+      </c>
+      <c r="B242">
+        <v>0.0001141273896791972</v>
+      </c>
+    </row>
+    <row r="243" spans="1:2">
+      <c r="A243">
+        <v>241</v>
+      </c>
+      <c r="B243">
+        <v>-1.477033038099762E-05</v>
+      </c>
+    </row>
+    <row r="244" spans="1:2">
+      <c r="A244">
+        <v>242</v>
+      </c>
+      <c r="B244">
+        <v>0.0003138406027574092</v>
+      </c>
+    </row>
+    <row r="245" spans="1:2">
+      <c r="A245">
+        <v>243</v>
+      </c>
+      <c r="B245">
+        <v>-0.0002309030824108049</v>
+      </c>
+    </row>
+    <row r="246" spans="1:2">
+      <c r="A246">
+        <v>244</v>
+      </c>
+      <c r="B246">
+        <v>-4.798116788151674E-05</v>
+      </c>
+    </row>
+    <row r="247" spans="1:2">
+      <c r="A247">
+        <v>245</v>
+      </c>
+      <c r="B247">
+        <v>0.002987075829878449</v>
+      </c>
+    </row>
+    <row r="248" spans="1:2">
+      <c r="A248">
+        <v>246</v>
+      </c>
+      <c r="B248">
+        <v>0.0006325818249024451</v>
+      </c>
+    </row>
+    <row r="249" spans="1:2">
+      <c r="A249">
+        <v>247</v>
+      </c>
+      <c r="B249">
+        <v>-2.576147835497977E-06</v>
+      </c>
+    </row>
+    <row r="250" spans="1:2">
+      <c r="A250">
+        <v>248</v>
+      </c>
+      <c r="B250">
+        <v>0.0006332927150651813</v>
+      </c>
+    </row>
+    <row r="251" spans="1:2">
+      <c r="A251">
+        <v>249</v>
+      </c>
+      <c r="B251">
+        <v>8.993728260975331E-05</v>
+      </c>
+    </row>
+    <row r="252" spans="1:2">
+      <c r="A252">
+        <v>250</v>
+      </c>
+      <c r="B252">
+        <v>0.0002658800221979618</v>
+      </c>
+    </row>
+    <row r="253" spans="1:2">
+      <c r="A253">
+        <v>251</v>
+      </c>
+      <c r="B253">
+        <v>0.0003425620670896024</v>
+      </c>
+    </row>
+    <row r="254" spans="1:2">
+      <c r="A254">
+        <v>252</v>
+      </c>
+      <c r="B254">
+        <v>0.0001219049154315144</v>
+      </c>
+    </row>
+    <row r="255" spans="1:2">
+      <c r="A255">
+        <v>253</v>
+      </c>
+      <c r="B255">
+        <v>2.729090192588046E-05</v>
+      </c>
+    </row>
+    <row r="256" spans="1:2">
+      <c r="A256">
+        <v>254</v>
+      </c>
+      <c r="B256">
+        <v>-0.0001639605907257646</v>
+      </c>
+    </row>
+    <row r="257" spans="1:2">
+      <c r="A257">
+        <v>255</v>
+      </c>
+      <c r="B257">
+        <v>0.0002183870237786323</v>
+      </c>
+    </row>
+    <row r="258" spans="1:2">
+      <c r="A258">
+        <v>256</v>
+      </c>
+      <c r="B258">
+        <v>0.000394189526559785</v>
+      </c>
+    </row>
+    <row r="259" spans="1:2">
+      <c r="A259">
+        <v>257</v>
+      </c>
+      <c r="B259">
+        <v>9.578846947988495E-05</v>
+      </c>
+    </row>
+    <row r="260" spans="1:2">
+      <c r="A260">
+        <v>258</v>
+      </c>
+      <c r="B260">
+        <v>0.001713788253255188</v>
+      </c>
+    </row>
+    <row r="261" spans="1:2">
+      <c r="A261">
+        <v>259</v>
+      </c>
+      <c r="B261">
+        <v>-0.0004909922718070447</v>
+      </c>
+    </row>
+    <row r="262" spans="1:2">
+      <c r="A262">
+        <v>260</v>
+      </c>
+      <c r="B262">
+        <v>0.0001459932827856392</v>
+      </c>
+    </row>
+    <row r="263" spans="1:2">
+      <c r="A263">
+        <v>261</v>
+      </c>
+      <c r="B263">
+        <v>-0.0001031218271236867</v>
+      </c>
+    </row>
+    <row r="264" spans="1:2">
+      <c r="A264">
+        <v>262</v>
+      </c>
+      <c r="B264">
+        <v>-0.0001339240407105535</v>
+      </c>
+    </row>
+    <row r="265" spans="1:2">
+      <c r="A265">
+        <v>263</v>
+      </c>
+      <c r="B265">
+        <v>-2.178168142563663E-05</v>
+      </c>
+    </row>
+    <row r="266" spans="1:2">
+      <c r="A266">
+        <v>264</v>
+      </c>
+      <c r="B266">
+        <v>0.0002565169415902346</v>
+      </c>
+    </row>
+    <row r="267" spans="1:2">
+      <c r="A267">
+        <v>265</v>
+      </c>
+      <c r="B267">
+        <v>-2.133973066520412E-05</v>
+      </c>
+    </row>
+    <row r="268" spans="1:2">
+      <c r="A268">
+        <v>266</v>
+      </c>
+      <c r="B268">
+        <v>0.0001044119780999608</v>
+      </c>
+    </row>
+    <row r="269" spans="1:2">
+      <c r="A269">
+        <v>267</v>
+      </c>
+      <c r="B269">
+        <v>-9.932354441843927E-05</v>
+      </c>
+    </row>
+    <row r="270" spans="1:2">
+      <c r="A270">
+        <v>268</v>
+      </c>
+      <c r="B270">
+        <v>-1.993281148315873E-05</v>
+      </c>
+    </row>
+    <row r="271" spans="1:2">
+      <c r="A271">
+        <v>269</v>
+      </c>
+      <c r="B271">
+        <v>0.0002317917533218861</v>
+      </c>
+    </row>
+    <row r="272" spans="1:2">
+      <c r="A272">
+        <v>270</v>
+      </c>
+      <c r="B272">
+        <v>-0.0002261719928355888</v>
+      </c>
+    </row>
+    <row r="273" spans="1:2">
+      <c r="A273">
+        <v>271</v>
+      </c>
+      <c r="B273">
+        <v>0.001511999871581793</v>
+      </c>
+    </row>
+    <row r="274" spans="1:2">
+      <c r="A274">
+        <v>272</v>
+      </c>
+      <c r="B274">
+        <v>-0.0005010886816307902</v>
+      </c>
+    </row>
+    <row r="275" spans="1:2">
+      <c r="A275">
+        <v>273</v>
+      </c>
+      <c r="B275">
+        <v>8.603837341070175E-05</v>
+      </c>
+    </row>
+    <row r="276" spans="1:2">
+      <c r="A276">
+        <v>274</v>
+      </c>
+      <c r="B276">
+        <v>1.377069929731078E-05</v>
+      </c>
+    </row>
+    <row r="277" spans="1:2">
+      <c r="A277">
+        <v>275</v>
+      </c>
+      <c r="B277">
+        <v>-6.848461634945124E-05</v>
+      </c>
+    </row>
+    <row r="278" spans="1:2">
+      <c r="A278">
+        <v>276</v>
+      </c>
+      <c r="B278">
+        <v>-0.0001056546170730144</v>
+      </c>
+    </row>
+    <row r="279" spans="1:2">
+      <c r="A279">
+        <v>277</v>
+      </c>
+      <c r="B279">
+        <v>0.000110947948996909</v>
+      </c>
+    </row>
+    <row r="280" spans="1:2">
+      <c r="A280">
+        <v>278</v>
+      </c>
+      <c r="B280">
+        <v>5.957403118372895E-05</v>
+      </c>
+    </row>
+    <row r="281" spans="1:2">
+      <c r="A281">
+        <v>279</v>
+      </c>
+      <c r="B281">
+        <v>0.0003479839069768786</v>
+      </c>
+    </row>
+    <row r="282" spans="1:2">
+      <c r="A282">
+        <v>280</v>
+      </c>
+      <c r="B282">
+        <v>0.0002866846334654838</v>
+      </c>
+    </row>
+    <row r="283" spans="1:2">
+      <c r="A283">
+        <v>281</v>
+      </c>
+      <c r="B283">
+        <v>0.0003464261826593429</v>
+      </c>
+    </row>
+    <row r="284" spans="1:2">
+      <c r="A284">
+        <v>282</v>
+      </c>
+      <c r="B284">
+        <v>0.0002859951055143028</v>
+      </c>
+    </row>
+    <row r="285" spans="1:2">
+      <c r="A285">
+        <v>283</v>
+      </c>
+      <c r="B285">
+        <v>-0.0003730075259227306</v>
+      </c>
+    </row>
+    <row r="286" spans="1:2">
+      <c r="A286">
+        <v>284</v>
+      </c>
+      <c r="B286">
+        <v>0.0004767464124597609</v>
+      </c>
+    </row>
+    <row r="287" spans="1:2">
+      <c r="A287">
+        <v>285</v>
+      </c>
+      <c r="B287">
+        <v>0.0006282016984187067</v>
+      </c>
+    </row>
+    <row r="288" spans="1:2">
+      <c r="A288">
+        <v>286</v>
+      </c>
+      <c r="B288">
+        <v>0.0005377448396757245</v>
+      </c>
+    </row>
+    <row r="289" spans="1:2">
+      <c r="A289">
+        <v>287</v>
+      </c>
+      <c r="B289">
+        <v>0.0002368996647419408</v>
+      </c>
+    </row>
+    <row r="290" spans="1:2">
+      <c r="A290">
+        <v>288</v>
+      </c>
+      <c r="B290">
+        <v>5.984607923892327E-06</v>
+      </c>
+    </row>
+    <row r="291" spans="1:2">
+      <c r="A291">
+        <v>289</v>
+      </c>
+      <c r="B291">
+        <v>4.326596535975114E-05</v>
+      </c>
+    </row>
+    <row r="292" spans="1:2">
+      <c r="A292">
+        <v>290</v>
+      </c>
+      <c r="B292">
+        <v>0.0006173808942548931</v>
+      </c>
+    </row>
+    <row r="293" spans="1:2">
+      <c r="A293">
+        <v>291</v>
+      </c>
+      <c r="B293">
+        <v>0.0003945331845898181</v>
+      </c>
+    </row>
+    <row r="294" spans="1:2">
+      <c r="A294">
+        <v>292</v>
+      </c>
+      <c r="B294">
+        <v>-0.0001127939394791611</v>
+      </c>
+    </row>
+    <row r="295" spans="1:2">
+      <c r="A295">
+        <v>293</v>
+      </c>
+      <c r="B295">
+        <v>0.0006251591257750988</v>
+      </c>
+    </row>
+    <row r="296" spans="1:2">
+      <c r="A296">
+        <v>294</v>
+      </c>
+      <c r="B296">
+        <v>0.0002283178910147399</v>
+      </c>
+    </row>
+    <row r="297" spans="1:2">
+      <c r="A297">
+        <v>295</v>
+      </c>
+      <c r="B297">
+        <v>0.0004400592006277293</v>
+      </c>
+    </row>
+    <row r="298" spans="1:2">
+      <c r="A298">
+        <v>296</v>
+      </c>
+      <c r="B298">
+        <v>0.0004524073738139123</v>
+      </c>
+    </row>
+    <row r="299" spans="1:2">
+      <c r="A299">
+        <v>297</v>
+      </c>
+      <c r="B299">
+        <v>-0.001343788346275687</v>
+      </c>
+    </row>
+    <row r="300" spans="1:2">
+      <c r="A300">
+        <v>298</v>
+      </c>
+      <c r="B300">
+        <v>0.0005581569275818765</v>
+      </c>
+    </row>
+    <row r="301" spans="1:2">
+      <c r="A301">
+        <v>299</v>
+      </c>
+      <c r="B301">
+        <v>0.0004011929268017411</v>
+      </c>
+    </row>
+    <row r="302" spans="1:2">
+      <c r="A302">
+        <v>300</v>
+      </c>
+      <c r="B302">
+        <v>0.0001320632291026413</v>
+      </c>
+    </row>
+    <row r="303" spans="1:2">
+      <c r="A303">
+        <v>301</v>
+      </c>
+      <c r="B303">
+        <v>0.0004066505644004792</v>
+      </c>
+    </row>
+    <row r="304" spans="1:2">
+      <c r="A304">
+        <v>302</v>
+      </c>
+      <c r="B304">
+        <v>0.0004269640485290438</v>
+      </c>
+    </row>
+    <row r="305" spans="1:2">
+      <c r="A305">
+        <v>303</v>
+      </c>
+      <c r="B305">
+        <v>0.000327838963130489</v>
+      </c>
+    </row>
+    <row r="306" spans="1:2">
+      <c r="A306">
+        <v>304</v>
+      </c>
+      <c r="B306">
+        <v>0.0001959014189196751</v>
+      </c>
+    </row>
+    <row r="307" spans="1:2">
+      <c r="A307">
+        <v>305</v>
+      </c>
+      <c r="B307">
+        <v>0.0001682142465142533</v>
+      </c>
+    </row>
+    <row r="308" spans="1:2">
+      <c r="A308">
+        <v>306</v>
+      </c>
+      <c r="B308">
+        <v>-4.940950020682067E-06</v>
+      </c>
+    </row>
+    <row r="309" spans="1:2">
+      <c r="A309">
+        <v>307</v>
+      </c>
+      <c r="B309">
+        <v>0.0009751746547408402</v>
+      </c>
+    </row>
+    <row r="310" spans="1:2">
+      <c r="A310">
+        <v>308</v>
+      </c>
+      <c r="B310">
+        <v>4.67145764559973E-05</v>
+      </c>
+    </row>
+    <row r="311" spans="1:2">
+      <c r="A311">
+        <v>309</v>
+      </c>
+      <c r="B311">
+        <v>0.0006433392991311848</v>
+      </c>
+    </row>
+    <row r="312" spans="1:2">
+      <c r="A312">
+        <v>310</v>
+      </c>
+      <c r="B312">
+        <v>0.0004374375275801867</v>
+      </c>
+    </row>
+    <row r="313" spans="1:2">
+      <c r="A313">
+        <v>311</v>
+      </c>
+      <c r="B313">
+        <v>-0.0002777959452942014</v>
+      </c>
+    </row>
+    <row r="314" spans="1:2">
+      <c r="A314">
+        <v>312</v>
+      </c>
+      <c r="B314">
+        <v>0.001115654828026891</v>
+      </c>
+    </row>
+    <row r="315" spans="1:2">
+      <c r="A315">
+        <v>313</v>
+      </c>
+      <c r="B315">
+        <v>0.0009377653477713466</v>
+      </c>
+    </row>
+    <row r="316" spans="1:2">
+      <c r="A316">
+        <v>314</v>
+      </c>
+      <c r="B316">
+        <v>0.0006120230536907911</v>
+      </c>
+    </row>
+    <row r="317" spans="1:2">
+      <c r="A317">
+        <v>315</v>
+      </c>
+      <c r="B317">
+        <v>0.000308130809571594</v>
+      </c>
+    </row>
+    <row r="318" spans="1:2">
+      <c r="A318">
+        <v>316</v>
+      </c>
+      <c r="B318">
+        <v>0.0002091880014631897</v>
+      </c>
+    </row>
+    <row r="319" spans="1:2">
+      <c r="A319">
+        <v>317</v>
+      </c>
+      <c r="B319">
+        <v>0.0001057980189216323</v>
+      </c>
+    </row>
+    <row r="320" spans="1:2">
+      <c r="A320">
+        <v>318</v>
+      </c>
+      <c r="B320">
+        <v>-9.356777445646003E-05</v>
+      </c>
+    </row>
+    <row r="321" spans="1:2">
+      <c r="A321">
+        <v>319</v>
+      </c>
+      <c r="B321">
+        <v>0.0006448518252000213</v>
+      </c>
+    </row>
+    <row r="322" spans="1:2">
+      <c r="A322">
+        <v>320</v>
+      </c>
+      <c r="B322">
+        <v>0.0002663233899511397</v>
+      </c>
+    </row>
+    <row r="323" spans="1:2">
+      <c r="A323">
+        <v>321</v>
+      </c>
+      <c r="B323">
+        <v>-0.0001579431263962761</v>
+      </c>
+    </row>
+    <row r="324" spans="1:2">
+      <c r="A324">
+        <v>322</v>
+      </c>
+      <c r="B324">
+        <v>-0.0007247102912515402</v>
+      </c>
+    </row>
+    <row r="325" spans="1:2">
+      <c r="A325">
+        <v>323</v>
+      </c>
+      <c r="B325">
+        <v>-0.001401519868522882</v>
+      </c>
+    </row>
+    <row r="326" spans="1:2">
+      <c r="A326">
+        <v>324</v>
+      </c>
+      <c r="B326">
+        <v>0.0007894466980360448</v>
+      </c>
+    </row>
+    <row r="327" spans="1:2">
+      <c r="A327">
+        <v>325</v>
+      </c>
+      <c r="B327">
+        <v>0.0009357060771435499</v>
+      </c>
+    </row>
+    <row r="328" spans="1:2">
+      <c r="A328">
+        <v>326</v>
+      </c>
+      <c r="B328">
+        <v>0.0001344560005236417</v>
+      </c>
+    </row>
+    <row r="329" spans="1:2">
+      <c r="A329">
+        <v>327</v>
+      </c>
+      <c r="B329">
+        <v>2.852737816283479E-05</v>
+      </c>
+    </row>
+    <row r="330" spans="1:2">
+      <c r="A330">
+        <v>328</v>
+      </c>
+      <c r="B330">
+        <v>-4.264039944246178E-06</v>
+      </c>
+    </row>
+    <row r="331" spans="1:2">
+      <c r="A331">
+        <v>329</v>
+      </c>
+      <c r="B331">
+        <v>8.430376328760758E-05</v>
+      </c>
+    </row>
+    <row r="332" spans="1:2">
+      <c r="A332">
+        <v>330</v>
+      </c>
+      <c r="B332">
+        <v>0.00108390545938164</v>
+      </c>
+    </row>
+    <row r="333" spans="1:2">
+      <c r="A333">
+        <v>331</v>
+      </c>
+      <c r="B333">
+        <v>0.001351718092337251</v>
+      </c>
+    </row>
+    <row r="334" spans="1:2">
+      <c r="A334">
+        <v>332</v>
+      </c>
+      <c r="B334">
+        <v>0.0008075276855379343</v>
+      </c>
+    </row>
+    <row r="335" spans="1:2">
+      <c r="A335">
+        <v>333</v>
+      </c>
+      <c r="B335">
+        <v>0.0007722576847299933</v>
+      </c>
+    </row>
+    <row r="336" spans="1:2">
+      <c r="A336">
+        <v>334</v>
+      </c>
+      <c r="B336">
+        <v>0.0004240831767674536</v>
+      </c>
+    </row>
+    <row r="337" spans="1:2">
+      <c r="A337">
+        <v>335</v>
+      </c>
+      <c r="B337">
+        <v>0.00183778372593224</v>
+      </c>
+    </row>
+    <row r="338" spans="1:2">
+      <c r="A338">
+        <v>336</v>
+      </c>
+      <c r="B338">
+        <v>0.000651421258226037</v>
+      </c>
+    </row>
+    <row r="339" spans="1:2">
+      <c r="A339">
+        <v>337</v>
+      </c>
+      <c r="B339">
+        <v>0.000482002564240247</v>
+      </c>
+    </row>
+    <row r="340" spans="1:2">
+      <c r="A340">
+        <v>338</v>
+      </c>
+      <c r="B340">
+        <v>0.0003675694752018899</v>
+      </c>
+    </row>
+    <row r="341" spans="1:2">
+      <c r="A341">
+        <v>339</v>
+      </c>
+      <c r="B341">
+        <v>-0.0002443745033815503</v>
+      </c>
+    </row>
+    <row r="342" spans="1:2">
+      <c r="A342">
+        <v>340</v>
+      </c>
+      <c r="B342">
+        <v>0.0006593075231648982</v>
+      </c>
+    </row>
+    <row r="343" spans="1:2">
+      <c r="A343">
+        <v>341</v>
+      </c>
+      <c r="B343">
+        <v>0.0001657711109146476</v>
+      </c>
+    </row>
+    <row r="344" spans="1:2">
+      <c r="A344">
+        <v>342</v>
+      </c>
+      <c r="B344">
+        <v>0.000506871729157865</v>
+      </c>
+    </row>
+    <row r="345" spans="1:2">
+      <c r="A345">
+        <v>343</v>
+      </c>
+      <c r="B345">
+        <v>0.0007956725894473493</v>
+      </c>
+    </row>
+    <row r="346" spans="1:2">
+      <c r="A346">
+        <v>344</v>
+      </c>
+      <c r="B346">
+        <v>5.587415216723457E-05</v>
+      </c>
+    </row>
+    <row r="347" spans="1:2">
+      <c r="A347">
+        <v>345</v>
+      </c>
+      <c r="B347">
+        <v>0.000477262627100572</v>
+      </c>
+    </row>
+    <row r="348" spans="1:2">
+      <c r="A348">
+        <v>346</v>
+      </c>
+      <c r="B348">
+        <v>0.0002732764405664057</v>
+      </c>
+    </row>
+    <row r="349" spans="1:2">
+      <c r="A349">
+        <v>347</v>
+      </c>
+      <c r="B349">
+        <v>0.0004294592654332519</v>
+      </c>
+    </row>
+    <row r="350" spans="1:2">
+      <c r="A350">
+        <v>348</v>
+      </c>
+      <c r="B350">
+        <v>0.0005053862114436924</v>
+      </c>
+    </row>
+    <row r="351" spans="1:2">
+      <c r="A351">
+        <v>349</v>
+      </c>
+      <c r="B351">
+        <v>0.0008809632854536176</v>
+      </c>
+    </row>
+    <row r="352" spans="1:2">
+      <c r="A352">
+        <v>350</v>
+      </c>
+      <c r="B352">
+        <v>0.001459600520320237</v>
+      </c>
+    </row>
+    <row r="353" spans="1:2">
+      <c r="A353">
+        <v>351</v>
+      </c>
+      <c r="B353">
+        <v>0.0007431940757669508</v>
+      </c>
+    </row>
+    <row r="354" spans="1:2">
+      <c r="A354">
+        <v>352</v>
+      </c>
+      <c r="B354">
+        <v>0.0005565113970078528</v>
+      </c>
+    </row>
+    <row r="355" spans="1:2">
+      <c r="A355">
+        <v>353</v>
+      </c>
+      <c r="B355">
+        <v>0.0010343516478315</v>
+      </c>
+    </row>
+    <row r="356" spans="1:2">
+      <c r="A356">
+        <v>354</v>
+      </c>
+      <c r="B356">
+        <v>0.001167074427939951</v>
+      </c>
+    </row>
+    <row r="357" spans="1:2">
+      <c r="A357">
+        <v>355</v>
+      </c>
+      <c r="B357">
+        <v>0.0004084185929968953</v>
+      </c>
+    </row>
+    <row r="358" spans="1:2">
+      <c r="A358">
+        <v>356</v>
+      </c>
+      <c r="B358">
+        <v>0.0003586417296901345</v>
+      </c>
+    </row>
+    <row r="359" spans="1:2">
+      <c r="A359">
+        <v>357</v>
+      </c>
+      <c r="B359">
+        <v>4.042761793243699E-05</v>
+      </c>
+    </row>
+    <row r="360" spans="1:2">
+      <c r="A360">
+        <v>358</v>
+      </c>
+      <c r="B360">
+        <v>0.0005940087721683085</v>
+      </c>
+    </row>
+    <row r="361" spans="1:2">
+      <c r="A361">
+        <v>359</v>
+      </c>
+      <c r="B361">
+        <v>-0.000410056411055848</v>
+      </c>
+    </row>
+    <row r="362" spans="1:2">
+      <c r="A362">
+        <v>360</v>
+      </c>
+      <c r="B362">
+        <v>0.0002480586408637464</v>
+      </c>
+    </row>
+    <row r="363" spans="1:2">
+      <c r="A363">
+        <v>361</v>
+      </c>
+      <c r="B363">
+        <v>0.002260405803099275</v>
+      </c>
+    </row>
+    <row r="364" spans="1:2">
+      <c r="A364">
+        <v>362</v>
+      </c>
+      <c r="B364">
+        <v>-0.000304028857499361</v>
+      </c>
+    </row>
+    <row r="365" spans="1:2">
+      <c r="A365">
+        <v>363</v>
+      </c>
+      <c r="B365">
+        <v>-0.001293172361329198</v>
+      </c>
+    </row>
+    <row r="366" spans="1:2">
+      <c r="A366">
+        <v>364</v>
+      </c>
+      <c r="B366">
+        <v>-3.950590325985104E-05</v>
+      </c>
+    </row>
+    <row r="367" spans="1:2">
+      <c r="A367">
+        <v>365</v>
+      </c>
+      <c r="B367">
+        <v>0.0009943521581590176</v>
+      </c>
+    </row>
+    <row r="368" spans="1:2">
+      <c r="A368">
+        <v>366</v>
+      </c>
+      <c r="B368">
+        <v>0.0002544804301578552</v>
+      </c>
+    </row>
+    <row r="369" spans="1:2">
+      <c r="A369">
+        <v>367</v>
+      </c>
+      <c r="B369">
+        <v>0.001128105097450316</v>
+      </c>
+    </row>
+    <row r="370" spans="1:2">
+      <c r="A370">
+        <v>368</v>
+      </c>
+      <c r="B370">
+        <v>-0.0001004246296361089</v>
+      </c>
+    </row>
+    <row r="371" spans="1:2">
+      <c r="A371">
+        <v>369</v>
+      </c>
+      <c r="B371">
+        <v>0.0001732168166199699</v>
+      </c>
+    </row>
+    <row r="372" spans="1:2">
+      <c r="A372">
+        <v>370</v>
+      </c>
+      <c r="B372">
+        <v>0.0001080418660421856</v>
+      </c>
+    </row>
+    <row r="373" spans="1:2">
+      <c r="A373">
+        <v>371</v>
+      </c>
+      <c r="B373">
+        <v>0.0005561182042583823</v>
+      </c>
+    </row>
+    <row r="374" spans="1:2">
+      <c r="A374">
+        <v>372</v>
+      </c>
+      <c r="B374">
+        <v>0.0006192083237692714</v>
+      </c>
+    </row>
+    <row r="375" spans="1:2">
+      <c r="A375">
+        <v>373</v>
+      </c>
+      <c r="B375">
+        <v>-7.826695946278051E-05</v>
+      </c>
+    </row>
+    <row r="376" spans="1:2">
+      <c r="A376">
+        <v>374</v>
+      </c>
+      <c r="B376">
+        <v>0.0007677334942854941</v>
+      </c>
+    </row>
+    <row r="377" spans="1:2">
+      <c r="A377">
+        <v>375</v>
+      </c>
+      <c r="B377">
+        <v>0.002977220341563225</v>
+      </c>
+    </row>
+    <row r="378" spans="1:2">
+      <c r="A378">
+        <v>376</v>
+      </c>
+      <c r="B378">
+        <v>0.0006340303225442767</v>
+      </c>
+    </row>
+    <row r="379" spans="1:2">
+      <c r="A379">
+        <v>377</v>
+      </c>
+      <c r="B379">
+        <v>0.0005427250871434808</v>
+      </c>
+    </row>
+    <row r="380" spans="1:2">
+      <c r="A380">
+        <v>378</v>
+      </c>
+      <c r="B380">
+        <v>0.0001133806144935079</v>
+      </c>
+    </row>
+    <row r="381" spans="1:2">
+      <c r="A381">
+        <v>379</v>
+      </c>
+      <c r="B381">
+        <v>0.0001053472005878575</v>
+      </c>
+    </row>
+    <row r="382" spans="1:2">
+      <c r="A382">
+        <v>380</v>
+      </c>
+      <c r="B382">
+        <v>0.0006297369254752994</v>
+      </c>
+    </row>
+    <row r="383" spans="1:2">
+      <c r="A383">
+        <v>381</v>
+      </c>
+      <c r="B383">
+        <v>0.0001759618171490729</v>
+      </c>
+    </row>
+    <row r="384" spans="1:2">
+      <c r="A384">
+        <v>382</v>
+      </c>
+      <c r="B384">
+        <v>0.0008458023075945675</v>
+      </c>
+    </row>
+    <row r="385" spans="1:2">
+      <c r="A385">
+        <v>383</v>
+      </c>
+      <c r="B385">
+        <v>5.240714745013975E-05</v>
+      </c>
+    </row>
+    <row r="386" spans="1:2">
+      <c r="A386">
+        <v>384</v>
+      </c>
+      <c r="B386">
+        <v>-0.0001126380302594043</v>
+      </c>
+    </row>
+    <row r="387" spans="1:2">
+      <c r="A387">
+        <v>385</v>
+      </c>
+      <c r="B387">
+        <v>0.001416656654328108</v>
+      </c>
+    </row>
+    <row r="388" spans="1:2">
+      <c r="A388">
+        <v>386</v>
+      </c>
+      <c r="B388">
+        <v>0.002213250147178769</v>
+      </c>
+    </row>
+    <row r="389" spans="1:2">
+      <c r="A389">
+        <v>387</v>
+      </c>
+      <c r="B389">
+        <v>0.001604067394509912</v>
+      </c>
+    </row>
+    <row r="390" spans="1:2">
+      <c r="A390">
+        <v>388</v>
+      </c>
+      <c r="B390">
+        <v>0.001105138566344976</v>
+      </c>
+    </row>
+    <row r="391" spans="1:2">
+      <c r="A391">
+        <v>389</v>
+      </c>
+      <c r="B391">
+        <v>0.000310479401377961</v>
+      </c>
+    </row>
+    <row r="392" spans="1:2">
+      <c r="A392">
+        <v>390</v>
+      </c>
+      <c r="B392">
+        <v>0.0005544443265534937</v>
+      </c>
+    </row>
+    <row r="393" spans="1:2">
+      <c r="A393">
+        <v>391</v>
+      </c>
+      <c r="B393">
+        <v>0.001021033502183855</v>
+      </c>
+    </row>
+    <row r="394" spans="1:2">
+      <c r="A394">
+        <v>392</v>
+      </c>
+      <c r="B394">
+        <v>0.001384525210596621</v>
+      </c>
+    </row>
+    <row r="395" spans="1:2">
+      <c r="A395">
+        <v>393</v>
+      </c>
+      <c r="B395">
+        <v>0.0005336538306437433</v>
+      </c>
+    </row>
+    <row r="396" spans="1:2">
+      <c r="A396">
+        <v>394</v>
+      </c>
+      <c r="B396">
+        <v>-5.472619523061439E-05</v>
+      </c>
+    </row>
+    <row r="397" spans="1:2">
+      <c r="A397">
+        <v>395</v>
+      </c>
+      <c r="B397">
+        <v>0.0001234294904861599</v>
+      </c>
+    </row>
+    <row r="398" spans="1:2">
+      <c r="A398">
+        <v>396</v>
+      </c>
+      <c r="B398">
+        <v>0.0001905983663164079</v>
+      </c>
+    </row>
+    <row r="399" spans="1:2">
+      <c r="A399">
+        <v>397</v>
+      </c>
+      <c r="B399">
+        <v>0.0001822333579184487</v>
+      </c>
+    </row>
+    <row r="400" spans="1:2">
+      <c r="A400">
+        <v>398</v>
+      </c>
+      <c r="B400">
+        <v>-0.0002172904933104292</v>
+      </c>
+    </row>
+    <row r="401" spans="1:2">
+      <c r="A401">
+        <v>399</v>
+      </c>
+      <c r="B401">
+        <v>0.0001569887681398541</v>
+      </c>
+    </row>
+    <row r="402" spans="1:2">
+      <c r="A402">
+        <v>400</v>
+      </c>
+      <c r="B402">
+        <v>0.0002762794902082533</v>
+      </c>
+    </row>
+    <row r="403" spans="1:2">
+      <c r="A403">
+        <v>401</v>
+      </c>
+      <c r="B403">
+        <v>-0.000283489323919639</v>
+      </c>
+    </row>
+    <row r="404" spans="1:2">
+      <c r="A404">
+        <v>402</v>
+      </c>
+      <c r="B404">
+        <v>0.0007201605476438999</v>
+      </c>
+    </row>
+    <row r="405" spans="1:2">
+      <c r="A405">
+        <v>403</v>
+      </c>
+      <c r="B405">
+        <v>0.0008473593043163419</v>
+      </c>
+    </row>
+    <row r="406" spans="1:2">
+      <c r="A406">
+        <v>404</v>
+      </c>
+      <c r="B406">
+        <v>-0.0001196946977870539</v>
+      </c>
+    </row>
+    <row r="407" spans="1:2">
+      <c r="A407">
+        <v>405</v>
+      </c>
+      <c r="B407">
+        <v>0.002421272220090032</v>
+      </c>
+    </row>
+    <row r="408" spans="1:2">
+      <c r="A408">
+        <v>406</v>
+      </c>
+      <c r="B408">
+        <v>1.774691918399185E-05</v>
+      </c>
+    </row>
+    <row r="409" spans="1:2">
+      <c r="A409">
+        <v>407</v>
+      </c>
+      <c r="B409">
+        <v>-0.0001392224803566933</v>
+      </c>
+    </row>
+    <row r="410" spans="1:2">
+      <c r="A410">
+        <v>408</v>
+      </c>
+      <c r="B410">
+        <v>0.000388707936508581</v>
+      </c>
+    </row>
+    <row r="411" spans="1:2">
+      <c r="A411">
+        <v>409</v>
+      </c>
+      <c r="B411">
+        <v>3.755950456252322E-05</v>
+      </c>
+    </row>
+    <row r="412" spans="1:2">
+      <c r="A412">
+        <v>410</v>
+      </c>
+      <c r="B412">
+        <v>-0.0008445468847639859</v>
+      </c>
+    </row>
+    <row r="413" spans="1:2">
+      <c r="A413">
+        <v>411</v>
+      </c>
+      <c r="B413">
+        <v>-6.356100493576378E-05</v>
+      </c>
+    </row>
+    <row r="414" spans="1:2">
+      <c r="A414">
+        <v>412</v>
+      </c>
+      <c r="B414">
+        <v>0.0009831172646954656</v>
+      </c>
+    </row>
+    <row r="415" spans="1:2">
+      <c r="A415">
+        <v>413</v>
+      </c>
+      <c r="B415">
+        <v>0.001440946361981332</v>
+      </c>
+    </row>
+    <row r="416" spans="1:2">
+      <c r="A416">
+        <v>414</v>
+      </c>
+      <c r="B416">
+        <v>0.0005268175737001002</v>
+      </c>
+    </row>
+    <row r="417" spans="1:2">
+      <c r="A417">
+        <v>415</v>
+      </c>
+      <c r="B417">
+        <v>0.0004593521589413285</v>
+      </c>
+    </row>
+    <row r="418" spans="1:2">
+      <c r="A418">
+        <v>416</v>
+      </c>
+      <c r="B418">
+        <v>0.0001624977303436026</v>
+      </c>
+    </row>
+    <row r="419" spans="1:2">
+      <c r="A419">
+        <v>417</v>
+      </c>
+      <c r="B419">
+        <v>0.000772815546952188</v>
+      </c>
+    </row>
+    <row r="420" spans="1:2">
+      <c r="A420">
+        <v>418</v>
+      </c>
+      <c r="B420">
+        <v>0.0005383758689276874</v>
+      </c>
+    </row>
+    <row r="421" spans="1:2">
+      <c r="A421">
+        <v>419</v>
+      </c>
+      <c r="B421">
+        <v>0.0006674602045677602</v>
+      </c>
+    </row>
+    <row r="422" spans="1:2">
+      <c r="A422">
+        <v>420</v>
+      </c>
+      <c r="B422">
+        <v>0.001462823478505015</v>
+      </c>
+    </row>
+    <row r="423" spans="1:2">
+      <c r="A423">
+        <v>421</v>
+      </c>
+      <c r="B423">
+        <v>-0.0001260346471099183</v>
+      </c>
+    </row>
+    <row r="424" spans="1:2">
+      <c r="A424">
+        <v>422</v>
+      </c>
+      <c r="B424">
+        <v>0.0008738577016629279</v>
+      </c>
+    </row>
+    <row r="425" spans="1:2">
+      <c r="A425">
+        <v>423</v>
+      </c>
+      <c r="B425">
+        <v>0.0003118785389233381</v>
+      </c>
+    </row>
+    <row r="426" spans="1:2">
+      <c r="A426">
+        <v>424</v>
+      </c>
+      <c r="B426">
+        <v>0.001622326206415892</v>
+      </c>
+    </row>
+    <row r="427" spans="1:2">
+      <c r="A427">
+        <v>425</v>
+      </c>
+      <c r="B427">
+        <v>-0.000485116004711017</v>
+      </c>
+    </row>
+    <row r="428" spans="1:2">
+      <c r="A428">
+        <v>426</v>
+      </c>
+      <c r="B428">
+        <v>0.001573941321112216</v>
+      </c>
+    </row>
+    <row r="429" spans="1:2">
+      <c r="A429">
+        <v>427</v>
+      </c>
+      <c r="B429">
+        <v>0.0004834815044887364</v>
+      </c>
+    </row>
+    <row r="430" spans="1:2">
+      <c r="A430">
+        <v>428</v>
+      </c>
+      <c r="B430">
+        <v>0.00109927321318537</v>
+      </c>
+    </row>
+    <row r="431" spans="1:2">
+      <c r="A431">
+        <v>429</v>
+      </c>
+      <c r="B431">
+        <v>1.238298864336684E-05</v>
+      </c>
+    </row>
+    <row r="432" spans="1:2">
+      <c r="A432">
+        <v>430</v>
+      </c>
+      <c r="B432">
+        <v>0.0003059174632653594</v>
+      </c>
+    </row>
+    <row r="433" spans="1:2">
+      <c r="A433">
+        <v>431</v>
+      </c>
+      <c r="B433">
+        <v>0.0003208001726306975</v>
+      </c>
+    </row>
+    <row r="434" spans="1:2">
+      <c r="A434">
+        <v>432</v>
+      </c>
+      <c r="B434">
+        <v>0.001528487075120211</v>
+      </c>
+    </row>
+    <row r="435" spans="1:2">
+      <c r="A435">
+        <v>433</v>
+      </c>
+      <c r="B435">
+        <v>0.0004424829385243356</v>
+      </c>
+    </row>
+    <row r="436" spans="1:2">
+      <c r="A436">
+        <v>434</v>
+      </c>
+      <c r="B436">
+        <v>0.0005644828779622912</v>
+      </c>
+    </row>
+    <row r="437" spans="1:2">
+      <c r="A437">
+        <v>435</v>
+      </c>
+      <c r="B437">
+        <v>0.0006731018074788153</v>
+      </c>
+    </row>
+    <row r="438" spans="1:2">
+      <c r="A438">
+        <v>436</v>
+      </c>
+      <c r="B438">
+        <v>0.002367333741858602</v>
+      </c>
+    </row>
+    <row r="439" spans="1:2">
+      <c r="A439">
+        <v>437</v>
+      </c>
+      <c r="B439">
+        <v>-4.139933298574761E-05</v>
+      </c>
+    </row>
+    <row r="440" spans="1:2">
+      <c r="A440">
+        <v>438</v>
+      </c>
+      <c r="B440">
+        <v>0.0006922250031493604</v>
+      </c>
+    </row>
+    <row r="441" spans="1:2">
+      <c r="A441">
+        <v>439</v>
+      </c>
+      <c r="B441">
+        <v>0.003042785450816154</v>
+      </c>
+    </row>
+    <row r="442" spans="1:2">
+      <c r="A442">
+        <v>440</v>
+      </c>
+      <c r="B442">
+        <v>0.0002343940577702597</v>
+      </c>
+    </row>
+    <row r="443" spans="1:2">
+      <c r="A443">
+        <v>441</v>
+      </c>
+      <c r="B443">
+        <v>0.000507061427924782</v>
+      </c>
+    </row>
+    <row r="444" spans="1:2">
+      <c r="A444">
+        <v>442</v>
+      </c>
+      <c r="B444">
+        <v>0.0003535360156092793</v>
+      </c>
+    </row>
+    <row r="445" spans="1:2">
+      <c r="A445">
+        <v>443</v>
+      </c>
+      <c r="B445">
+        <v>0.0006294851773418486</v>
+      </c>
+    </row>
+    <row r="446" spans="1:2">
+      <c r="A446">
+        <v>444</v>
+      </c>
+      <c r="B446">
+        <v>1.366587366646854E-05</v>
+      </c>
+    </row>
+    <row r="447" spans="1:2">
+      <c r="A447">
+        <v>445</v>
+      </c>
+      <c r="B447">
+        <v>0.0002433118643239141</v>
+      </c>
+    </row>
+    <row r="448" spans="1:2">
+      <c r="A448">
+        <v>446</v>
+      </c>
+      <c r="B448">
+        <v>0.0002782566007226706</v>
+      </c>
+    </row>
+    <row r="449" spans="1:2">
+      <c r="A449">
+        <v>447</v>
+      </c>
+      <c r="B449">
+        <v>0.000598591286689043</v>
+      </c>
+    </row>
+    <row r="450" spans="1:2">
+      <c r="A450">
+        <v>448</v>
+      </c>
+      <c r="B450">
+        <v>6.682961975457147E-05</v>
+      </c>
+    </row>
+    <row r="451" spans="1:2">
+      <c r="A451">
+        <v>449</v>
+      </c>
+      <c r="B451">
+        <v>0.0002906114677898586</v>
+      </c>
+    </row>
+    <row r="452" spans="1:2">
+      <c r="A452">
+        <v>450</v>
+      </c>
+      <c r="B452">
+        <v>-8.992293442133814E-05</v>
+      </c>
+    </row>
+    <row r="453" spans="1:2">
+      <c r="A453">
+        <v>451</v>
+      </c>
+      <c r="B453">
+        <v>0.0005212051328271627</v>
+      </c>
+    </row>
+    <row r="454" spans="1:2">
+      <c r="A454">
+        <v>452</v>
+      </c>
+      <c r="B454">
+        <v>-0.001085172174498439</v>
+      </c>
+    </row>
+    <row r="455" spans="1:2">
+      <c r="A455">
+        <v>453</v>
+      </c>
+      <c r="B455">
+        <v>-0.0007166227442212403</v>
+      </c>
+    </row>
+    <row r="456" spans="1:2">
+      <c r="A456">
+        <v>454</v>
+      </c>
+      <c r="B456">
+        <v>0.001144844805821776</v>
+      </c>
+    </row>
+    <row r="457" spans="1:2">
+      <c r="A457">
+        <v>455</v>
+      </c>
+      <c r="B457">
+        <v>0.0003341804258525372</v>
+      </c>
+    </row>
+    <row r="458" spans="1:2">
+      <c r="A458">
+        <v>456</v>
+      </c>
+      <c r="B458">
+        <v>0.0006495827692560852</v>
+      </c>
+    </row>
+    <row r="459" spans="1:2">
+      <c r="A459">
+        <v>457</v>
+      </c>
+      <c r="B459">
+        <v>0.0008591059013269842</v>
+      </c>
+    </row>
+    <row r="460" spans="1:2">
+      <c r="A460">
+        <v>458</v>
+      </c>
+      <c r="B460">
+        <v>0.0002342466032132506</v>
+      </c>
+    </row>
+    <row r="461" spans="1:2">
+      <c r="A461">
+        <v>459</v>
+      </c>
+      <c r="B461">
+        <v>0.001040282775647938</v>
+      </c>
+    </row>
+    <row r="462" spans="1:2">
+      <c r="A462">
+        <v>460</v>
+      </c>
+      <c r="B462">
+        <v>0.0004850112891290337</v>
+      </c>
+    </row>
+    <row r="463" spans="1:2">
+      <c r="A463">
+        <v>461</v>
+      </c>
+      <c r="B463">
+        <v>0.001311097061261535</v>
+      </c>
+    </row>
+    <row r="464" spans="1:2">
+      <c r="A464">
+        <v>462</v>
+      </c>
+      <c r="B464">
+        <v>0.0002514703082852066</v>
+      </c>
+    </row>
+    <row r="465" spans="1:2">
+      <c r="A465">
+        <v>463</v>
+      </c>
+      <c r="B465">
+        <v>-0.0004732999950647354</v>
+      </c>
+    </row>
+    <row r="466" spans="1:2">
+      <c r="A466">
+        <v>464</v>
+      </c>
+      <c r="B466">
+        <v>0.001313172397203743</v>
+      </c>
+    </row>
+    <row r="467" spans="1:2">
+      <c r="A467">
+        <v>465</v>
+      </c>
+      <c r="B467">
+        <v>0.0005996175459586084</v>
+      </c>
+    </row>
+    <row r="468" spans="1:2">
+      <c r="A468">
+        <v>466</v>
+      </c>
+      <c r="B468">
+        <v>0.001153098302893341</v>
+      </c>
+    </row>
+    <row r="469" spans="1:2">
+      <c r="A469">
+        <v>467</v>
+      </c>
+      <c r="B469">
+        <v>0.0005051629268564284</v>
+      </c>
+    </row>
+    <row r="470" spans="1:2">
+      <c r="A470">
+        <v>468</v>
+      </c>
+      <c r="B470">
+        <v>0.001178519218228757</v>
+      </c>
+    </row>
+    <row r="471" spans="1:2">
+      <c r="A471">
+        <v>469</v>
+      </c>
+      <c r="B471">
+        <v>0.0004127495631109923</v>
+      </c>
+    </row>
+    <row r="472" spans="1:2">
+      <c r="A472">
+        <v>470</v>
+      </c>
+      <c r="B472">
+        <v>0.0001385746145388111</v>
+      </c>
+    </row>
+    <row r="473" spans="1:2">
+      <c r="A473">
+        <v>471</v>
+      </c>
+      <c r="B473">
+        <v>0.0001381659239996225</v>
+      </c>
+    </row>
+    <row r="474" spans="1:2">
+      <c r="A474">
+        <v>472</v>
+      </c>
+      <c r="B474">
+        <v>0.0002846099087037146</v>
+      </c>
+    </row>
+    <row r="475" spans="1:2">
+      <c r="A475">
+        <v>473</v>
+      </c>
+      <c r="B475">
+        <v>0.0002293189463671297</v>
+      </c>
+    </row>
+    <row r="476" spans="1:2">
+      <c r="A476">
+        <v>474</v>
+      </c>
+      <c r="B476">
+        <v>8.821813389658928E-05</v>
+      </c>
+    </row>
+    <row r="477" spans="1:2">
+      <c r="A477">
+        <v>475</v>
+      </c>
+      <c r="B477">
+        <v>0.0003514140262268484</v>
+      </c>
+    </row>
+    <row r="478" spans="1:2">
+      <c r="A478">
+        <v>476</v>
+      </c>
+      <c r="B478">
+        <v>0.0002405453706160188</v>
+      </c>
+    </row>
+    <row r="479" spans="1:2">
+      <c r="A479">
+        <v>477</v>
+      </c>
+      <c r="B479">
+        <v>0.0003723122645169497</v>
+      </c>
+    </row>
+    <row r="480" spans="1:2">
+      <c r="A480">
+        <v>478</v>
+      </c>
+      <c r="B480">
+        <v>0.005331993103027344</v>
+      </c>
+    </row>
+    <row r="481" spans="1:2">
+      <c r="A481">
+        <v>479</v>
+      </c>
+      <c r="B481">
+        <v>0.001000454765744507</v>
+      </c>
+    </row>
+    <row r="482" spans="1:2">
+      <c r="A482">
+        <v>480</v>
+      </c>
+      <c r="B482">
+        <v>-3.83377555408515E-05</v>
+      </c>
+    </row>
+    <row r="483" spans="1:2">
+      <c r="A483">
+        <v>481</v>
+      </c>
+      <c r="B483">
+        <v>0.0004970234003849328</v>
+      </c>
+    </row>
+    <row r="484" spans="1:2">
+      <c r="A484">
+        <v>482</v>
+      </c>
+      <c r="B484">
+        <v>-0.000246168696321547</v>
+      </c>
+    </row>
+    <row r="485" spans="1:2">
+      <c r="A485">
+        <v>483</v>
+      </c>
+      <c r="B485">
+        <v>0.0003908965736627579</v>
+      </c>
+    </row>
+    <row r="486" spans="1:2">
+      <c r="A486">
+        <v>484</v>
+      </c>
+      <c r="B486">
+        <v>-0.0003100378380622715</v>
+      </c>
+    </row>
+    <row r="487" spans="1:2">
+      <c r="A487">
+        <v>485</v>
+      </c>
+      <c r="B487">
+        <v>0.0003863079473376274</v>
+      </c>
+    </row>
+    <row r="488" spans="1:2">
+      <c r="A488">
+        <v>486</v>
+      </c>
+      <c r="B488">
+        <v>-4.425249426276423E-05</v>
+      </c>
+    </row>
+    <row r="489" spans="1:2">
+      <c r="A489">
+        <v>487</v>
+      </c>
+      <c r="B489">
+        <v>0.001220726175233722</v>
+      </c>
+    </row>
+    <row r="490" spans="1:2">
+      <c r="A490">
+        <v>488</v>
+      </c>
+      <c r="B490">
+        <v>0.0003916675050277263</v>
+      </c>
+    </row>
+    <row r="491" spans="1:2">
+      <c r="A491">
+        <v>489</v>
+      </c>
+      <c r="B491">
+        <v>7.898145850049332E-05</v>
+      </c>
+    </row>
+    <row r="492" spans="1:2">
+      <c r="A492">
+        <v>490</v>
+      </c>
+      <c r="B492">
+        <v>0.0004307542403694242</v>
+      </c>
+    </row>
+    <row r="493" spans="1:2">
+      <c r="A493">
+        <v>491</v>
+      </c>
+      <c r="B493">
+        <v>0.000281122192973271</v>
+      </c>
+    </row>
+    <row r="494" spans="1:2">
+      <c r="A494">
+        <v>492</v>
+      </c>
+      <c r="B494">
+        <v>0.0003654591273516417</v>
+      </c>
+    </row>
+    <row r="495" spans="1:2">
+      <c r="A495">
+        <v>493</v>
+      </c>
+      <c r="B495">
+        <v>0.0007032253197394311</v>
+      </c>
+    </row>
+    <row r="496" spans="1:2">
+      <c r="A496">
+        <v>494</v>
+      </c>
+      <c r="B496">
+        <v>0.0002376820339122787</v>
+      </c>
+    </row>
+    <row r="497" spans="1:2">
+      <c r="A497">
+        <v>495</v>
+      </c>
+      <c r="B497">
+        <v>0.0006685854750685394</v>
+      </c>
+    </row>
+    <row r="498" spans="1:2">
+      <c r="A498">
+        <v>496</v>
+      </c>
+      <c r="B498">
+        <v>0.0003002072335220873</v>
+      </c>
+    </row>
+    <row r="499" spans="1:2">
+      <c r="A499">
+        <v>497</v>
+      </c>
+      <c r="B499">
+        <v>0.0002180816954933107</v>
+      </c>
+    </row>
+    <row r="500" spans="1:2">
+      <c r="A500">
+        <v>498</v>
+      </c>
+      <c r="B500">
+        <v>0.0002235619613202289</v>
+      </c>
+    </row>
+    <row r="501" spans="1:2">
+      <c r="A501">
+        <v>499</v>
+      </c>
+      <c r="B501">
+        <v>0.000583956076297909</v>
+      </c>
+    </row>
+    <row r="502" spans="1:2">
+      <c r="A502">
+        <v>500</v>
+      </c>
+      <c r="B502">
+        <v>0.0005296258605085313</v>
+      </c>
+    </row>
+    <row r="503" spans="1:2">
+      <c r="A503">
+        <v>501</v>
+      </c>
+      <c r="B503">
+        <v>0.0008583487942814827</v>
+      </c>
+    </row>
+    <row r="504" spans="1:2">
+      <c r="A504">
+        <v>502</v>
+      </c>
+      <c r="B504">
+        <v>0.001683444948866963</v>
+      </c>
+    </row>
+    <row r="505" spans="1:2">
+      <c r="A505">
+        <v>503</v>
+      </c>
+      <c r="B505">
+        <v>0.0009379963157698512</v>
+      </c>
+    </row>
+    <row r="506" spans="1:2">
+      <c r="A506">
+        <v>504</v>
+      </c>
+      <c r="B506">
+        <v>-0.0002152186934836209</v>
+      </c>
+    </row>
+    <row r="507" spans="1:2">
+      <c r="A507">
+        <v>505</v>
+      </c>
+      <c r="B507">
+        <v>0.001517877681180835</v>
+      </c>
+    </row>
+    <row r="508" spans="1:2">
+      <c r="A508">
+        <v>506</v>
+      </c>
+      <c r="B508">
+        <v>0.0007167369476519525</v>
+      </c>
+    </row>
+    <row r="509" spans="1:2">
+      <c r="A509">
+        <v>507</v>
+      </c>
+      <c r="B509">
+        <v>3.322571137687191E-05</v>
+      </c>
+    </row>
+    <row r="510" spans="1:2">
+      <c r="A510">
+        <v>508</v>
+      </c>
+      <c r="B510">
+        <v>0.000738203467335552</v>
+      </c>
+    </row>
+    <row r="511" spans="1:2">
+      <c r="A511">
+        <v>509</v>
+      </c>
+      <c r="B511">
+        <v>9.555563883623108E-05</v>
+      </c>
+    </row>
+    <row r="512" spans="1:2">
+      <c r="A512">
+        <v>510</v>
+      </c>
+      <c r="B512">
+        <v>0.0003182942164130509</v>
+      </c>
+    </row>
+    <row r="513" spans="1:2">
+      <c r="A513">
+        <v>511</v>
+      </c>
+      <c r="B513">
+        <v>0.0005708030657842755</v>
+      </c>
+    </row>
+    <row r="514" spans="1:2">
+      <c r="A514">
+        <v>512</v>
+      </c>
+      <c r="B514">
+        <v>0.0002677426091395319</v>
+      </c>
+    </row>
+    <row r="515" spans="1:2">
+      <c r="A515">
+        <v>513</v>
+      </c>
+      <c r="B515">
+        <v>-6.703562394250184E-05</v>
+      </c>
+    </row>
+    <row r="516" spans="1:2">
+      <c r="A516">
+        <v>514</v>
+      </c>
+      <c r="B516">
+        <v>1.690324825176504E-05</v>
+      </c>
+    </row>
+    <row r="517" spans="1:2">
+      <c r="A517">
+        <v>515</v>
+      </c>
+      <c r="B517">
+        <v>-0.0001775195996742696</v>
+      </c>
+    </row>
+    <row r="518" spans="1:2">
+      <c r="A518">
+        <v>516</v>
+      </c>
+      <c r="B518">
+        <v>0.001154330908320844</v>
+      </c>
+    </row>
+    <row r="519" spans="1:2">
+      <c r="A519">
+        <v>517</v>
+      </c>
+      <c r="B519">
+        <v>0.0009370679617859423</v>
+      </c>
+    </row>
+    <row r="520" spans="1:2">
+      <c r="A520">
+        <v>518</v>
+      </c>
+      <c r="B520">
+        <v>0.0001232029753737152</v>
+      </c>
+    </row>
+    <row r="521" spans="1:2">
+      <c r="A521">
+        <v>519</v>
+      </c>
+      <c r="B521">
+        <v>9.805514855543151E-05</v>
+      </c>
+    </row>
+    <row r="522" spans="1:2">
+      <c r="A522">
+        <v>520</v>
+      </c>
+      <c r="B522">
+        <v>0.0003721285902429372</v>
+      </c>
+    </row>
+    <row r="523" spans="1:2">
+      <c r="A523">
+        <v>521</v>
+      </c>
+      <c r="B523">
+        <v>0.00040250743040815</v>
+      </c>
+    </row>
+    <row r="524" spans="1:2">
+      <c r="A524">
+        <v>522</v>
+      </c>
+      <c r="B524">
+        <v>0.0008329458069056273</v>
+      </c>
+    </row>
+    <row r="525" spans="1:2">
+      <c r="A525">
+        <v>523</v>
+      </c>
+      <c r="B525">
+        <v>0.001454211655072868</v>
+      </c>
+    </row>
+    <row r="526" spans="1:2">
+      <c r="A526">
+        <v>524</v>
+      </c>
+      <c r="B526">
+        <v>-0.0002847023715730757</v>
+      </c>
+    </row>
+    <row r="527" spans="1:2">
+      <c r="A527">
+        <v>525</v>
+      </c>
+      <c r="B527">
+        <v>0.001735010999254882</v>
+      </c>
+    </row>
+    <row r="528" spans="1:2">
+      <c r="A528">
+        <v>526</v>
+      </c>
+      <c r="B528">
+        <v>-2.315648453077301E-05</v>
+      </c>
+    </row>
+    <row r="529" spans="1:2">
+      <c r="A529">
+        <v>527</v>
+      </c>
+      <c r="B529">
+        <v>8.498858733219095E-06</v>
+      </c>
+    </row>
+    <row r="530" spans="1:2">
+      <c r="A530">
+        <v>528</v>
+      </c>
+      <c r="B530">
+        <v>0.0006683444371446967</v>
+      </c>
+    </row>
+    <row r="531" spans="1:2">
+      <c r="A531">
+        <v>529</v>
+      </c>
+      <c r="B531">
+        <v>0.0008314038859680295</v>
+      </c>
+    </row>
+    <row r="532" spans="1:2">
+      <c r="A532">
+        <v>530</v>
+      </c>
+      <c r="B532">
+        <v>0.0004849796823691577</v>
+      </c>
+    </row>
+    <row r="533" spans="1:2">
+      <c r="A533">
+        <v>531</v>
+      </c>
+      <c r="B533">
+        <v>6.714239862048998E-05</v>
+      </c>
+    </row>
+    <row r="534" spans="1:2">
+      <c r="A534">
+        <v>532</v>
+      </c>
+      <c r="B534">
+        <v>0.0007221280829980969</v>
+      </c>
+    </row>
+    <row r="535" spans="1:2">
+      <c r="A535">
+        <v>533</v>
+      </c>
+      <c r="B535">
+        <v>0.0007496175239793956</v>
+      </c>
+    </row>
+    <row r="536" spans="1:2">
+      <c r="A536">
+        <v>534</v>
+      </c>
+      <c r="B536">
+        <v>1.391181922372198E-05</v>
+      </c>
+    </row>
+    <row r="537" spans="1:2">
+      <c r="A537">
+        <v>535</v>
+      </c>
+      <c r="B537">
+        <v>0.00139531260356307</v>
+      </c>
+    </row>
+    <row r="538" spans="1:2">
+      <c r="A538">
+        <v>536</v>
+      </c>
+      <c r="B538">
+        <v>-0.0001275212853215635</v>
+      </c>
+    </row>
+    <row r="539" spans="1:2">
+      <c r="A539">
+        <v>537</v>
+      </c>
+      <c r="B539">
+        <v>0.00312460376881063</v>
+      </c>
+    </row>
+    <row r="540" spans="1:2">
+      <c r="A540">
+        <v>538</v>
+      </c>
+      <c r="B540">
+        <v>-0.0002850805758498609</v>
+      </c>
+    </row>
+    <row r="541" spans="1:2">
+      <c r="A541">
+        <v>539</v>
+      </c>
+      <c r="B541">
+        <v>-0.0004495898901950568</v>
+      </c>
+    </row>
+    <row r="542" spans="1:2">
+      <c r="A542">
+        <v>540</v>
+      </c>
+      <c r="B542">
+        <v>0.0004742041055578738</v>
+      </c>
+    </row>
+    <row r="543" spans="1:2">
+      <c r="A543">
+        <v>541</v>
+      </c>
+      <c r="B543">
+        <v>0.0003679785877466202</v>
+      </c>
+    </row>
+    <row r="544" spans="1:2">
+      <c r="A544">
+        <v>542</v>
+      </c>
+      <c r="B544">
+        <v>-0.0002065556764137</v>
+      </c>
+    </row>
+    <row r="545" spans="1:2">
+      <c r="A545">
+        <v>543</v>
+      </c>
+      <c r="B545">
+        <v>0.0001464615779696032</v>
+      </c>
+    </row>
+    <row r="546" spans="1:2">
+      <c r="A546">
+        <v>544</v>
+      </c>
+      <c r="B546">
+        <v>0.0006575318984687328</v>
+      </c>
+    </row>
+    <row r="547" spans="1:2">
+      <c r="A547">
+        <v>545</v>
+      </c>
+      <c r="B547">
+        <v>8.514062938047573E-05</v>
+      </c>
+    </row>
+    <row r="548" spans="1:2">
+      <c r="A548">
+        <v>546</v>
+      </c>
+      <c r="B548">
+        <v>0.0008456280920654535</v>
+      </c>
+    </row>
+    <row r="549" spans="1:2">
+      <c r="A549">
+        <v>547</v>
+      </c>
+      <c r="B549">
+        <v>0.0008701843325980008</v>
+      </c>
+    </row>
+    <row r="550" spans="1:2">
+      <c r="A550">
+        <v>548</v>
+      </c>
+      <c r="B550">
+        <v>-0.0004950409638695419</v>
+      </c>
+    </row>
+    <row r="551" spans="1:2">
+      <c r="A551">
+        <v>549</v>
+      </c>
+      <c r="B551">
+        <v>0.0005901469849050045</v>
+      </c>
+    </row>
+    <row r="552" spans="1:2">
+      <c r="A552">
+        <v>550</v>
+      </c>
+      <c r="B552">
+        <v>0.001768043963238597</v>
+      </c>
+    </row>
+    <row r="553" spans="1:2">
+      <c r="A553">
+        <v>551</v>
+      </c>
+      <c r="B553">
+        <v>0.000573315832298249</v>
+      </c>
+    </row>
+    <row r="554" spans="1:2">
+      <c r="A554">
+        <v>552</v>
+      </c>
+      <c r="B554">
+        <v>0.0001453689183108509</v>
+      </c>
+    </row>
+    <row r="555" spans="1:2">
+      <c r="A555">
+        <v>553</v>
+      </c>
+      <c r="B555">
+        <v>0.0008374580647796392</v>
+      </c>
+    </row>
+    <row r="556" spans="1:2">
+      <c r="A556">
+        <v>554</v>
+      </c>
+      <c r="B556">
+        <v>0.0008989938069134951</v>
+      </c>
+    </row>
+    <row r="557" spans="1:2">
+      <c r="A557">
+        <v>555</v>
+      </c>
+      <c r="B557">
+        <v>0.000285944202914834</v>
+      </c>
+    </row>
+    <row r="558" spans="1:2">
+      <c r="A558">
+        <v>556</v>
+      </c>
+      <c r="B558">
+        <v>-0.0007191572804003954</v>
+      </c>
+    </row>
+    <row r="559" spans="1:2">
+      <c r="A559">
+        <v>557</v>
+      </c>
+      <c r="B559">
+        <v>0.001301288837566972</v>
+      </c>
+    </row>
+    <row r="560" spans="1:2">
+      <c r="A560">
+        <v>558</v>
+      </c>
+      <c r="B560">
+        <v>-0.0003074668347835541</v>
+      </c>
+    </row>
+    <row r="561" spans="1:2">
+      <c r="A561">
+        <v>559</v>
+      </c>
+      <c r="B561">
+        <v>0.001698402222245932</v>
+      </c>
+    </row>
+    <row r="562" spans="1:2">
+      <c r="A562">
+        <v>560</v>
+      </c>
+      <c r="B562">
+        <v>0.00100798113271594</v>
+      </c>
+    </row>
+    <row r="563" spans="1:2">
+      <c r="A563">
+        <v>561</v>
+      </c>
+      <c r="B563">
+        <v>-0.0002029298048000783</v>
+      </c>
+    </row>
+    <row r="564" spans="1:2">
+      <c r="A564">
+        <v>562</v>
+      </c>
+      <c r="B564">
+        <v>0.0001130435048253275</v>
+      </c>
+    </row>
+    <row r="565" spans="1:2">
+      <c r="A565">
+        <v>563</v>
+      </c>
+      <c r="B565">
+        <v>-0.005442069843411446</v>
+      </c>
+    </row>
+    <row r="566" spans="1:2">
+      <c r="A566">
+        <v>564</v>
+      </c>
+      <c r="B566">
+        <v>0.001368932309560478</v>
+      </c>
+    </row>
+    <row r="567" spans="1:2">
+      <c r="A567">
+        <v>565</v>
+      </c>
+      <c r="B567">
+        <v>-0.0006262211827561259</v>
+      </c>
+    </row>
+    <row r="568" spans="1:2">
+      <c r="A568">
+        <v>566</v>
+      </c>
+      <c r="B568">
+        <v>0.000294350873446092</v>
+      </c>
+    </row>
+    <row r="569" spans="1:2">
+      <c r="A569">
+        <v>567</v>
+      </c>
+      <c r="B569">
+        <v>-0.0001199266334879212</v>
+      </c>
+    </row>
+    <row r="570" spans="1:2">
+      <c r="A570">
+        <v>568</v>
+      </c>
+      <c r="B570">
+        <v>0.001485669403336942</v>
+      </c>
+    </row>
+    <row r="571" spans="1:2">
+      <c r="A571">
+        <v>569</v>
+      </c>
+      <c r="B571">
+        <v>-0.001058412599377334</v>
+      </c>
+    </row>
+    <row r="572" spans="1:2">
+      <c r="A572">
+        <v>570</v>
+      </c>
+      <c r="B572">
+        <v>0.000435432477388531</v>
+      </c>
+    </row>
+    <row r="573" spans="1:2">
+      <c r="A573">
+        <v>571</v>
+      </c>
+      <c r="B573">
+        <v>0.0002918242826126516</v>
+      </c>
+    </row>
+    <row r="574" spans="1:2">
+      <c r="A574">
+        <v>572</v>
+      </c>
+      <c r="B574">
+        <v>0.001374167390167713</v>
+      </c>
+    </row>
+    <row r="575" spans="1:2">
+      <c r="A575">
+        <v>573</v>
+      </c>
+      <c r="B575">
+        <v>0.00253179227001965</v>
+      </c>
+    </row>
+    <row r="576" spans="1:2">
+      <c r="A576">
+        <v>574</v>
+      </c>
+      <c r="B576">
+        <v>-0.0005740743363276124</v>
+      </c>
+    </row>
+    <row r="577" spans="1:2">
+      <c r="A577">
+        <v>575</v>
+      </c>
+      <c r="B577">
+        <v>-0.0005714260623790324</v>
+      </c>
+    </row>
+    <row r="578" spans="1:2">
+      <c r="A578">
+        <v>576</v>
+      </c>
+      <c r="B578">
+        <v>0.004864498041570187</v>
+      </c>
+    </row>
+    <row r="579" spans="1:2">
+      <c r="A579">
+        <v>577</v>
+      </c>
+      <c r="B579">
+        <v>8.559079287806526E-05</v>
+      </c>
+    </row>
+    <row r="580" spans="1:2">
+      <c r="A580">
+        <v>578</v>
+      </c>
+      <c r="B580">
+        <v>0.000141690339660272</v>
+      </c>
+    </row>
+    <row r="581" spans="1:2">
+      <c r="A581">
+        <v>579</v>
+      </c>
+      <c r="B581">
+        <v>0.001147028291597962</v>
+      </c>
+    </row>
+    <row r="582" spans="1:2">
+      <c r="A582">
+        <v>580</v>
+      </c>
+      <c r="B582">
+        <v>0.001410468597896397</v>
+      </c>
+    </row>
+    <row r="583" spans="1:2">
+      <c r="A583">
+        <v>581</v>
+      </c>
+      <c r="B583">
+        <v>8.062677807174623E-05</v>
+      </c>
+    </row>
+    <row r="584" spans="1:2">
+      <c r="A584">
+        <v>582</v>
+      </c>
+      <c r="B584">
+        <v>0.0006970590329729021</v>
+      </c>
+    </row>
+    <row r="585" spans="1:2">
+      <c r="A585">
+        <v>583</v>
+      </c>
+      <c r="B585">
+        <v>0.0001817995798774064</v>
+      </c>
+    </row>
+    <row r="586" spans="1:2">
+      <c r="A586">
+        <v>584</v>
+      </c>
+      <c r="B586">
+        <v>0.000275031867204234</v>
+      </c>
+    </row>
+    <row r="587" spans="1:2">
+      <c r="A587">
+        <v>585</v>
+      </c>
+      <c r="B587">
+        <v>-7.639276736881584E-05</v>
+      </c>
+    </row>
+    <row r="588" spans="1:2">
+      <c r="A588">
+        <v>586</v>
+      </c>
+      <c r="B588">
+        <v>-0.001017139293253422</v>
+      </c>
+    </row>
+    <row r="589" spans="1:2">
+      <c r="A589">
+        <v>587</v>
+      </c>
+      <c r="B589">
+        <v>0.0002081862767226994</v>
+      </c>
+    </row>
+    <row r="590" spans="1:2">
+      <c r="A590">
+        <v>588</v>
+      </c>
+      <c r="B590">
+        <v>-4.751590313389897E-05</v>
+      </c>
+    </row>
+    <row r="591" spans="1:2">
+      <c r="A591">
+        <v>589</v>
+      </c>
+      <c r="B591">
+        <v>0.001279939897358418</v>
+      </c>
+    </row>
+    <row r="592" spans="1:2">
+      <c r="A592">
+        <v>590</v>
+      </c>
+      <c r="B592">
+        <v>0.001307632890529931</v>
+      </c>
+    </row>
+    <row r="593" spans="1:2">
+      <c r="A593">
+        <v>591</v>
+      </c>
+      <c r="B593">
+        <v>0.001444921130314469</v>
+      </c>
+    </row>
+    <row r="594" spans="1:2">
+      <c r="A594">
+        <v>592</v>
+      </c>
+      <c r="B594">
+        <v>-0.0002900921099353582</v>
+      </c>
+    </row>
+    <row r="595" spans="1:2">
+      <c r="A595">
+        <v>593</v>
+      </c>
+      <c r="B595">
+        <v>0.0005144187598489225</v>
+      </c>
+    </row>
+    <row r="596" spans="1:2">
+      <c r="A596">
+        <v>594</v>
+      </c>
+      <c r="B596">
+        <v>0.0005162157467566431</v>
+      </c>
+    </row>
+    <row r="597" spans="1:2">
+      <c r="A597">
+        <v>595</v>
+      </c>
+      <c r="B597">
+        <v>0.001048717764206231</v>
+      </c>
+    </row>
+    <row r="598" spans="1:2">
+      <c r="A598">
+        <v>596</v>
+      </c>
+      <c r="B598">
+        <v>8.501352567691356E-05</v>
+      </c>
+    </row>
+    <row r="599" spans="1:2">
+      <c r="A599">
+        <v>597</v>
+      </c>
+      <c r="B599">
+        <v>-1.444403187633725E-05</v>
+      </c>
+    </row>
+    <row r="600" spans="1:2">
+      <c r="A600">
+        <v>598</v>
+      </c>
+      <c r="B600">
+        <v>-0.000576685881242156</v>
+      </c>
+    </row>
+    <row r="601" spans="1:2">
+      <c r="A601">
+        <v>599</v>
+      </c>
+      <c r="B601">
+        <v>0.001103336340747774</v>
+      </c>
+    </row>
+    <row r="602" spans="1:2">
+      <c r="A602">
+        <v>600</v>
+      </c>
+      <c r="B602">
+        <v>0.003329530823975801</v>
+      </c>
+    </row>
+    <row r="603" spans="1:2">
+      <c r="A603">
+        <v>601</v>
+      </c>
+      <c r="B603">
+        <v>0.00184142030775547</v>
+      </c>
+    </row>
+    <row r="604" spans="1:2">
+      <c r="A604">
+        <v>602</v>
+      </c>
+      <c r="B604">
+        <v>0.009499764069914818</v>
+      </c>
+    </row>
+    <row r="605" spans="1:2">
+      <c r="A605">
+        <v>603</v>
+      </c>
+      <c r="B605">
+        <v>0.001680969027802348</v>
+      </c>
+    </row>
+    <row r="606" spans="1:2">
+      <c r="A606">
+        <v>604</v>
+      </c>
+      <c r="B606">
+        <v>-0.0002787421690300107</v>
+      </c>
+    </row>
+    <row r="607" spans="1:2">
+      <c r="A607">
+        <v>605</v>
+      </c>
+      <c r="B607">
+        <v>0.001567860250361264</v>
+      </c>
+    </row>
+    <row r="608" spans="1:2">
+      <c r="A608">
+        <v>606</v>
+      </c>
+      <c r="B608">
+        <v>0.002588883507996798</v>
+      </c>
+    </row>
+    <row r="609" spans="1:2">
+      <c r="A609">
+        <v>607</v>
+      </c>
+      <c r="B609">
+        <v>0.000370103633031249</v>
+      </c>
+    </row>
+    <row r="610" spans="1:2">
+      <c r="A610">
+        <v>608</v>
+      </c>
+      <c r="B610">
+        <v>0.0001782774634193629</v>
+      </c>
+    </row>
+    <row r="611" spans="1:2">
+      <c r="A611">
+        <v>609</v>
+      </c>
+      <c r="B611">
+        <v>0.000329597620293498</v>
+      </c>
+    </row>
+    <row r="612" spans="1:2">
+      <c r="A612">
+        <v>610</v>
+      </c>
+      <c r="B612">
+        <v>0.0001470012939535081</v>
+      </c>
+    </row>
+    <row r="613" spans="1:2">
+      <c r="A613">
+        <v>611</v>
+      </c>
+      <c r="B613">
+        <v>0.00023698563745711</v>
+      </c>
+    </row>
+    <row r="614" spans="1:2">
+      <c r="A614">
+        <v>612</v>
+      </c>
+      <c r="B614">
+        <v>7.689459016546607E-05</v>
+      </c>
+    </row>
+    <row r="615" spans="1:2">
+      <c r="A615">
+        <v>613</v>
+      </c>
+      <c r="B615">
+        <v>0.00057232502149418</v>
+      </c>
+    </row>
+    <row r="616" spans="1:2">
+      <c r="A616">
+        <v>614</v>
+      </c>
+      <c r="B616">
+        <v>-0.0005440577515400946</v>
+      </c>
+    </row>
+    <row r="617" spans="1:2">
+      <c r="A617">
+        <v>615</v>
+      </c>
+      <c r="B617">
+        <v>0.001497440855018795</v>
+      </c>
+    </row>
+    <row r="618" spans="1:2">
+      <c r="A618">
+        <v>616</v>
+      </c>
+      <c r="B618">
+        <v>0.001029432751238346</v>
+      </c>
+    </row>
+    <row r="619" spans="1:2">
+      <c r="A619">
+        <v>617</v>
+      </c>
+      <c r="B619">
+        <v>-0.0006863708840683103</v>
+      </c>
+    </row>
+    <row r="620" spans="1:2">
+      <c r="A620">
+        <v>618</v>
+      </c>
+      <c r="B620">
+        <v>0.0001293718814849854</v>
+      </c>
+    </row>
+    <row r="621" spans="1:2">
+      <c r="A621">
+        <v>619</v>
+      </c>
+      <c r="B621">
+        <v>0.002437665592879057</v>
+      </c>
+    </row>
+    <row r="622" spans="1:2">
+      <c r="A622">
+        <v>620</v>
+      </c>
+      <c r="B622">
+        <v>0.0009072919492609799</v>
+      </c>
+    </row>
+    <row r="623" spans="1:2">
+      <c r="A623">
+        <v>621</v>
+      </c>
+      <c r="B623">
+        <v>0.001073152525350451</v>
+      </c>
+    </row>
+    <row r="624" spans="1:2">
+      <c r="A624">
+        <v>622</v>
+      </c>
+      <c r="B624">
+        <v>-0.0007775355479680002</v>
+      </c>
+    </row>
+    <row r="625" spans="1:2">
+      <c r="A625">
+        <v>623</v>
+      </c>
+      <c r="B625">
+        <v>0.0001084276809706353</v>
+      </c>
+    </row>
+    <row r="626" spans="1:2">
+      <c r="A626">
+        <v>624</v>
+      </c>
+      <c r="B626">
+        <v>-0.0006869306089356542</v>
+      </c>
+    </row>
+    <row r="627" spans="1:2">
+      <c r="A627">
+        <v>625</v>
+      </c>
+      <c r="B627">
+        <v>0.0002192104584537446</v>
+      </c>
+    </row>
+    <row r="628" spans="1:2">
+      <c r="A628">
+        <v>626</v>
+      </c>
+      <c r="B628">
+        <v>0.0001297484268434346</v>
+      </c>
+    </row>
+    <row r="629" spans="1:2">
+      <c r="A629">
+        <v>627</v>
+      </c>
+      <c r="B629">
+        <v>-7.640432158950716E-05</v>
+      </c>
+    </row>
+    <row r="630" spans="1:2">
+      <c r="A630">
+        <v>628</v>
+      </c>
+      <c r="B630">
+        <v>0.000879159546457231</v>
+      </c>
+    </row>
+    <row r="631" spans="1:2">
+      <c r="A631">
+        <v>629</v>
+      </c>
+      <c r="B631">
+        <v>0.0006102912011556327</v>
+      </c>
+    </row>
+    <row r="632" spans="1:2">
+      <c r="A632">
+        <v>630</v>
+      </c>
+      <c r="B632">
+        <v>0.001131690107285976</v>
+      </c>
+    </row>
+    <row r="633" spans="1:2">
+      <c r="A633">
+        <v>631</v>
+      </c>
+      <c r="B633">
+        <v>4.951163282385096E-05</v>
+      </c>
+    </row>
+    <row r="634" spans="1:2">
+      <c r="A634">
+        <v>632</v>
+      </c>
+      <c r="B634">
+        <v>0.0009758814703673124</v>
+      </c>
+    </row>
+    <row r="635" spans="1:2">
+      <c r="A635">
+        <v>633</v>
+      </c>
+      <c r="B635">
+        <v>0.001268028281629086</v>
+      </c>
+    </row>
+    <row r="636" spans="1:2">
+      <c r="A636">
+        <v>634</v>
+      </c>
+      <c r="B636">
+        <v>-9.935590060194954E-05</v>
+      </c>
+    </row>
+    <row r="637" spans="1:2">
+      <c r="A637">
+        <v>635</v>
+      </c>
+      <c r="B637">
+        <v>0.0005132440128363669</v>
+      </c>
+    </row>
+    <row r="638" spans="1:2">
+      <c r="A638">
+        <v>636</v>
+      </c>
+      <c r="B638">
+        <v>0.0004002895730081946</v>
+      </c>
+    </row>
+    <row r="639" spans="1:2">
+      <c r="A639">
+        <v>637</v>
+      </c>
+      <c r="B639">
+        <v>0.0002711192064452916</v>
+      </c>
+    </row>
+    <row r="640" spans="1:2">
+      <c r="A640">
+        <v>638</v>
+      </c>
+      <c r="B640">
+        <v>0.001252418267540634</v>
+      </c>
+    </row>
+    <row r="641" spans="1:2">
+      <c r="A641">
+        <v>639</v>
+      </c>
+      <c r="B641">
+        <v>0.0003398546250537038</v>
+      </c>
+    </row>
+    <row r="642" spans="1:2">
+      <c r="A642">
+        <v>640</v>
+      </c>
+      <c r="B642">
+        <v>-3.464008841547184E-05</v>
+      </c>
+    </row>
+    <row r="643" spans="1:2">
+      <c r="A643">
+        <v>641</v>
+      </c>
+      <c r="B643">
+        <v>0.003455472411587834</v>
+      </c>
+    </row>
+    <row r="644" spans="1:2">
+      <c r="A644">
+        <v>642</v>
+      </c>
+      <c r="B644">
+        <v>0.0006783065036870539</v>
+      </c>
+    </row>
+    <row r="645" spans="1:2">
+      <c r="A645">
+        <v>643</v>
+      </c>
+      <c r="B645">
+        <v>0.0009381551644764841</v>
+      </c>
+    </row>
+    <row r="646" spans="1:2">
+      <c r="A646">
+        <v>644</v>
+      </c>
+      <c r="B646">
+        <v>0.0006880787550471723</v>
+      </c>
+    </row>
+    <row r="647" spans="1:2">
+      <c r="A647">
+        <v>645</v>
+      </c>
+      <c r="B647">
+        <v>0.0001887123653432354</v>
+      </c>
+    </row>
+    <row r="648" spans="1:2">
+      <c r="A648">
+        <v>646</v>
+      </c>
+      <c r="B648">
+        <v>-0.002530101453885436</v>
+      </c>
+    </row>
+    <row r="649" spans="1:2">
+      <c r="A649">
+        <v>647</v>
+      </c>
+      <c r="B649">
+        <v>0.0008523249998688698</v>
+      </c>
+    </row>
+    <row r="650" spans="1:2">
+      <c r="A650">
+        <v>648</v>
+      </c>
+      <c r="B650">
+        <v>0.001512665534391999</v>
+      </c>
+    </row>
+    <row r="651" spans="1:2">
+      <c r="A651">
+        <v>649</v>
+      </c>
+      <c r="B651">
+        <v>0.0001579410309204832</v>
+      </c>
+    </row>
+    <row r="652" spans="1:2">
+      <c r="A652">
+        <v>650</v>
+      </c>
+      <c r="B652">
+        <v>0.001123405061662197</v>
+      </c>
+    </row>
+    <row r="653" spans="1:2">
+      <c r="A653">
+        <v>651</v>
+      </c>
+      <c r="B653">
+        <v>0.0004639540566131473</v>
+      </c>
+    </row>
+    <row r="654" spans="1:2">
+      <c r="A654">
+        <v>652</v>
+      </c>
+      <c r="B654">
+        <v>-0.003930356353521347</v>
+      </c>
+    </row>
+    <row r="655" spans="1:2">
+      <c r="A655">
+        <v>653</v>
+      </c>
+      <c r="B655">
+        <v>0.001160353305749595</v>
+      </c>
+    </row>
+    <row r="656" spans="1:2">
+      <c r="A656">
+        <v>654</v>
+      </c>
+      <c r="B656">
+        <v>-0.00192597636487335</v>
+      </c>
+    </row>
+    <row r="657" spans="1:2">
+      <c r="A657">
+        <v>655</v>
+      </c>
+      <c r="B657">
+        <v>9.053827670868486E-05</v>
+      </c>
+    </row>
+    <row r="658" spans="1:2">
+      <c r="A658">
+        <v>656</v>
+      </c>
+      <c r="B658">
+        <v>0.000565701921004802</v>
+      </c>
+    </row>
+    <row r="659" spans="1:2">
+      <c r="A659">
+        <v>657</v>
+      </c>
+      <c r="B659">
+        <v>0.0002399900549789891</v>
+      </c>
+    </row>
+    <row r="660" spans="1:2">
+      <c r="A660">
+        <v>658</v>
+      </c>
+      <c r="B660">
+        <v>-4.387800800031982E-05</v>
+      </c>
+    </row>
+    <row r="661" spans="1:2">
+      <c r="A661">
+        <v>659</v>
+      </c>
+      <c r="B661">
+        <v>0.002911712741479278</v>
+      </c>
+    </row>
+    <row r="662" spans="1:2">
+      <c r="A662">
+        <v>660</v>
+      </c>
+      <c r="B662">
+        <v>0.001058394322171807</v>
+      </c>
+    </row>
+    <row r="663" spans="1:2">
+      <c r="A663">
+        <v>661</v>
+      </c>
+      <c r="B663">
+        <v>0.0001854808797361329</v>
+      </c>
+    </row>
+    <row r="664" spans="1:2">
+      <c r="A664">
+        <v>662</v>
+      </c>
+      <c r="B664">
+        <v>0.0003331652260385454</v>
+      </c>
+    </row>
+    <row r="665" spans="1:2">
+      <c r="A665">
+        <v>663</v>
+      </c>
+      <c r="B665">
+        <v>0.001973963342607021</v>
+      </c>
+    </row>
+    <row r="666" spans="1:2">
+      <c r="A666">
+        <v>664</v>
+      </c>
+      <c r="B666">
+        <v>0.001337346038781106</v>
+      </c>
+    </row>
+    <row r="667" spans="1:2">
+      <c r="A667">
+        <v>665</v>
+      </c>
+      <c r="B667">
+        <v>-0.001118901534937322</v>
+      </c>
+    </row>
+    <row r="668" spans="1:2">
+      <c r="A668">
+        <v>666</v>
+      </c>
+      <c r="B668">
+        <v>0.002677414566278458</v>
+      </c>
+    </row>
+    <row r="669" spans="1:2">
+      <c r="A669">
+        <v>667</v>
+      </c>
+      <c r="B669">
+        <v>-0.005202314350754023</v>
+      </c>
+    </row>
+    <row r="670" spans="1:2">
+      <c r="A670">
+        <v>668</v>
+      </c>
+      <c r="B670">
+        <v>0.0008276760345324874</v>
+      </c>
+    </row>
+    <row r="671" spans="1:2">
+      <c r="A671">
+        <v>669</v>
+      </c>
+      <c r="B671">
+        <v>0.0003765318251680583</v>
+      </c>
+    </row>
+    <row r="672" spans="1:2">
+      <c r="A672">
+        <v>670</v>
+      </c>
+      <c r="B672">
+        <v>3.585045851650648E-05</v>
+      </c>
+    </row>
+    <row r="673" spans="1:2">
+      <c r="A673">
+        <v>671</v>
+      </c>
+      <c r="B673">
+        <v>-0.0001727939525153488</v>
+      </c>
+    </row>
+    <row r="674" spans="1:2">
+      <c r="A674">
+        <v>672</v>
+      </c>
+      <c r="B674">
+        <v>0.0003349558392073959</v>
+      </c>
+    </row>
+    <row r="675" spans="1:2">
+      <c r="A675">
+        <v>673</v>
+      </c>
+      <c r="B675">
+        <v>-0.0001993236364796758</v>
+      </c>
+    </row>
+    <row r="676" spans="1:2">
+      <c r="A676">
+        <v>674</v>
+      </c>
+      <c r="B676">
+        <v>0.0004844742943532765</v>
+      </c>
+    </row>
+    <row r="677" spans="1:2">
+      <c r="A677">
+        <v>675</v>
+      </c>
+      <c r="B677">
+        <v>0.0005887377774342895</v>
+      </c>
+    </row>
+    <row r="678" spans="1:2">
+      <c r="A678">
+        <v>676</v>
+      </c>
+      <c r="B678">
+        <v>0.0005382319795899093</v>
+      </c>
+    </row>
+    <row r="679" spans="1:2">
+      <c r="A679">
+        <v>677</v>
+      </c>
+      <c r="B679">
+        <v>0.0005141239380463958</v>
+      </c>
+    </row>
+    <row r="680" spans="1:2">
+      <c r="A680">
+        <v>678</v>
+      </c>
+      <c r="B680">
+        <v>0.0001778857113095</v>
+      </c>
+    </row>
+    <row r="681" spans="1:2">
+      <c r="A681">
+        <v>679</v>
+      </c>
+      <c r="B681">
+        <v>-0.0003162332868669182</v>
+      </c>
+    </row>
+    <row r="682" spans="1:2">
+      <c r="A682">
+        <v>680</v>
+      </c>
+      <c r="B682">
+        <v>0.006397354882210493</v>
+      </c>
+    </row>
+    <row r="683" spans="1:2">
+      <c r="A683">
+        <v>681</v>
+      </c>
+      <c r="B683">
+        <v>-0.0001736166304908693</v>
+      </c>
+    </row>
+    <row r="684" spans="1:2">
+      <c r="A684">
+        <v>682</v>
+      </c>
+      <c r="B684">
+        <v>-0.00165425322484225</v>
+      </c>
+    </row>
+    <row r="685" spans="1:2">
+      <c r="A685">
+        <v>683</v>
+      </c>
+      <c r="B685">
+        <v>0.0002214100386481732</v>
+      </c>
+    </row>
+    <row r="686" spans="1:2">
+      <c r="A686">
+        <v>684</v>
+      </c>
+      <c r="B686">
+        <v>0.0005563009181059897</v>
+      </c>
+    </row>
+    <row r="687" spans="1:2">
+      <c r="A687">
+        <v>685</v>
+      </c>
+      <c r="B687">
+        <v>0.0005138186388649046</v>
+      </c>
+    </row>
+    <row r="688" spans="1:2">
+      <c r="A688">
+        <v>686</v>
+      </c>
+      <c r="B688">
+        <v>3.869881766149774E-05</v>
+      </c>
+    </row>
+    <row r="689" spans="1:2">
+      <c r="A689">
+        <v>687</v>
+      </c>
+      <c r="B689">
+        <v>0.0003819718258455396</v>
+      </c>
+    </row>
+    <row r="690" spans="1:2">
+      <c r="A690">
+        <v>688</v>
+      </c>
+      <c r="B690">
+        <v>-0.0004762447206303477</v>
+      </c>
+    </row>
+    <row r="691" spans="1:2">
+      <c r="A691">
+        <v>689</v>
+      </c>
+      <c r="B691">
+        <v>0.001328605692833662</v>
+      </c>
+    </row>
+    <row r="692" spans="1:2">
+      <c r="A692">
+        <v>690</v>
+      </c>
+      <c r="B692">
+        <v>-0.0002202121249865741</v>
+      </c>
+    </row>
+    <row r="693" spans="1:2">
+      <c r="A693">
+        <v>691</v>
+      </c>
+      <c r="B693">
+        <v>-0.0005035562207922339</v>
+      </c>
+    </row>
+    <row r="694" spans="1:2">
+      <c r="A694">
+        <v>692</v>
+      </c>
+      <c r="B694">
+        <v>0.0003193212614860386</v>
+      </c>
+    </row>
+    <row r="695" spans="1:2">
+      <c r="A695">
+        <v>693</v>
+      </c>
+      <c r="B695">
+        <v>0.001367994584143162</v>
+      </c>
+    </row>
+    <row r="696" spans="1:2">
+      <c r="A696">
+        <v>694</v>
+      </c>
+      <c r="B696">
+        <v>0.0005081151030026376</v>
+      </c>
+    </row>
+    <row r="697" spans="1:2">
+      <c r="A697">
+        <v>695</v>
+      </c>
+      <c r="B697">
+        <v>0.0001344572519883513</v>
+      </c>
+    </row>
+    <row r="698" spans="1:2">
+      <c r="A698">
+        <v>696</v>
+      </c>
+      <c r="B698">
+        <v>0.0008903219131752849</v>
+      </c>
+    </row>
+    <row r="699" spans="1:2">
+      <c r="A699">
+        <v>697</v>
+      </c>
+      <c r="B699">
+        <v>8.252861334767658E-06</v>
+      </c>
+    </row>
+    <row r="700" spans="1:2">
+      <c r="A700">
+        <v>698</v>
+      </c>
+      <c r="B700">
+        <v>4.672328213928267E-05</v>
+      </c>
+    </row>
+    <row r="701" spans="1:2">
+      <c r="A701">
+        <v>699</v>
+      </c>
+      <c r="B701">
+        <v>-1.048478952725418E-05</v>
+      </c>
+    </row>
+    <row r="702" spans="1:2">
+      <c r="A702">
+        <v>700</v>
+      </c>
+      <c r="B702">
+        <v>-0.0003167029935866594</v>
+      </c>
+    </row>
+    <row r="703" spans="1:2">
+      <c r="A703">
+        <v>701</v>
+      </c>
+      <c r="B703">
+        <v>0.001731422613374889</v>
+      </c>
+    </row>
+    <row r="704" spans="1:2">
+      <c r="A704">
+        <v>702</v>
+      </c>
+      <c r="B704">
+        <v>0.0002998347335960716</v>
+      </c>
+    </row>
+    <row r="705" spans="1:2">
+      <c r="A705">
+        <v>703</v>
+      </c>
+      <c r="B705">
+        <v>0.0004042810469400138</v>
+      </c>
+    </row>
+    <row r="706" spans="1:2">
+      <c r="A706">
+        <v>704</v>
+      </c>
+      <c r="B706">
+        <v>0.0008796961046755314</v>
+      </c>
+    </row>
+    <row r="707" spans="1:2">
+      <c r="A707">
+        <v>705</v>
+      </c>
+      <c r="B707">
+        <v>0.0004881573840975761</v>
+      </c>
+    </row>
+    <row r="708" spans="1:2">
+      <c r="A708">
+        <v>706</v>
+      </c>
+      <c r="B708">
+        <v>0.008127272129058838</v>
+      </c>
+    </row>
+    <row r="709" spans="1:2">
+      <c r="A709">
+        <v>707</v>
+      </c>
+      <c r="B709">
+        <v>-0.0008713071583770216</v>
+      </c>
+    </row>
+    <row r="710" spans="1:2">
+      <c r="A710">
+        <v>708</v>
+      </c>
+      <c r="B710">
+        <v>0.0007091262959875166</v>
+      </c>
+    </row>
+    <row r="711" spans="1:2">
+      <c r="A711">
+        <v>709</v>
+      </c>
+      <c r="B711">
+        <v>0.0002758963091764599</v>
+      </c>
+    </row>
+    <row r="712" spans="1:2">
+      <c r="A712">
+        <v>710</v>
+      </c>
+      <c r="B712">
+        <v>-0.0004783423210028559</v>
+      </c>
+    </row>
+    <row r="713" spans="1:2">
+      <c r="A713">
+        <v>711</v>
+      </c>
+      <c r="B713">
+        <v>0.0004106494889128953</v>
+      </c>
+    </row>
+    <row r="714" spans="1:2">
+      <c r="A714">
+        <v>712</v>
+      </c>
+      <c r="B714">
+        <v>0.000155558082042262</v>
+      </c>
+    </row>
+    <row r="715" spans="1:2">
+      <c r="A715">
+        <v>713</v>
+      </c>
+      <c r="B715">
+        <v>0.0003416051331441849</v>
+      </c>
+    </row>
+    <row r="716" spans="1:2">
+      <c r="A716">
+        <v>714</v>
+      </c>
+      <c r="B716">
+        <v>0.0001120372544392012</v>
+      </c>
+    </row>
+    <row r="717" spans="1:2">
+      <c r="A717">
+        <v>715</v>
+      </c>
+      <c r="B717">
+        <v>0.001449096365831792</v>
+      </c>
+    </row>
+    <row r="718" spans="1:2">
+      <c r="A718">
+        <v>716</v>
+      </c>
+      <c r="B718">
+        <v>0.0005626749480143189</v>
+      </c>
+    </row>
+    <row r="719" spans="1:2">
+      <c r="A719">
+        <v>717</v>
+      </c>
+      <c r="B719">
+        <v>0.0004102842940483242</v>
+      </c>
+    </row>
+    <row r="720" spans="1:2">
+      <c r="A720">
+        <v>718</v>
+      </c>
+      <c r="B720">
+        <v>-0.0001601712574483827</v>
+      </c>
+    </row>
+    <row r="721" spans="1:2">
+      <c r="A721">
+        <v>719</v>
+      </c>
+      <c r="B721">
+        <v>-0.0007850348483771086</v>
+      </c>
+    </row>
+    <row r="722" spans="1:2">
+      <c r="A722">
+        <v>720</v>
+      </c>
+      <c r="B722">
+        <v>0.0002589222276583314</v>
+      </c>
+    </row>
+    <row r="723" spans="1:2">
+      <c r="A723">
+        <v>721</v>
+      </c>
+      <c r="B723">
+        <v>6.185498205013573E-05</v>
+      </c>
+    </row>
+    <row r="724" spans="1:2">
+      <c r="A724">
+        <v>722</v>
+      </c>
+      <c r="B724">
+        <v>0.0004788141523022205</v>
+      </c>
+    </row>
+    <row r="725" spans="1:2">
+      <c r="A725">
+        <v>723</v>
+      </c>
+      <c r="B725">
+        <v>0.0007161910180002451</v>
+      </c>
+    </row>
+    <row r="726" spans="1:2">
+      <c r="A726">
+        <v>724</v>
+      </c>
+      <c r="B726">
+        <v>-0.0005789923015981913</v>
+      </c>
+    </row>
+    <row r="727" spans="1:2">
+      <c r="A727">
+        <v>725</v>
+      </c>
+      <c r="B727">
+        <v>0.0004457332252059132</v>
+      </c>
+    </row>
+    <row r="728" spans="1:2">
+      <c r="A728">
+        <v>726</v>
+      </c>
+      <c r="B728">
+        <v>0.0006755781942047179</v>
+      </c>
+    </row>
+    <row r="729" spans="1:2">
+      <c r="A729">
+        <v>727</v>
+      </c>
+      <c r="B729">
+        <v>0.0006336515070870519</v>
+      </c>
+    </row>
+    <row r="730" spans="1:2">
+      <c r="A730">
+        <v>728</v>
+      </c>
+      <c r="B730">
+        <v>-0.0004157888470217586</v>
+      </c>
+    </row>
+    <row r="731" spans="1:2">
+      <c r="A731">
+        <v>729</v>
+      </c>
+      <c r="B731">
+        <v>0.0006360524566844106</v>
+      </c>
+    </row>
+    <row r="732" spans="1:2">
+      <c r="A732">
+        <v>730</v>
+      </c>
+      <c r="B732">
+        <v>0.0003497913712635636</v>
+      </c>
+    </row>
+    <row r="733" spans="1:2">
+      <c r="A733">
+        <v>731</v>
+      </c>
+      <c r="B733">
+        <v>-0.0009190698037855327</v>
+      </c>
+    </row>
+    <row r="734" spans="1:2">
+      <c r="A734">
+        <v>732</v>
+      </c>
+      <c r="B734">
+        <v>0.005396689288318157</v>
+      </c>
+    </row>
+    <row r="735" spans="1:2">
+      <c r="A735">
+        <v>733</v>
+      </c>
+      <c r="B735">
+        <v>0.001042067422531545</v>
+      </c>
+    </row>
+    <row r="736" spans="1:2">
+      <c r="A736">
+        <v>734</v>
+      </c>
+      <c r="B736">
+        <v>0.0004465492384042591</v>
+      </c>
+    </row>
+    <row r="737" spans="1:2">
+      <c r="A737">
+        <v>735</v>
+      </c>
+      <c r="B737">
+        <v>0.0002546531322877854</v>
+      </c>
+    </row>
+    <row r="738" spans="1:2">
+      <c r="A738">
+        <v>736</v>
+      </c>
+      <c r="B738">
+        <v>0.0004787501238752156</v>
+      </c>
+    </row>
+    <row r="739" spans="1:2">
+      <c r="A739">
+        <v>737</v>
+      </c>
+      <c r="B739">
+        <v>0.0004099043435417116</v>
+      </c>
+    </row>
+    <row r="740" spans="1:2">
+      <c r="A740">
+        <v>738</v>
+      </c>
+      <c r="B740">
+        <v>0.0001873549917945638</v>
+      </c>
+    </row>
+    <row r="741" spans="1:2">
+      <c r="A741">
+        <v>739</v>
+      </c>
+      <c r="B741">
+        <v>6.706552085233852E-05</v>
+      </c>
+    </row>
+    <row r="742" spans="1:2">
+      <c r="A742">
+        <v>740</v>
+      </c>
+      <c r="B742">
+        <v>0.0001394146529491991</v>
+      </c>
+    </row>
+    <row r="743" spans="1:2">
+      <c r="A743">
+        <v>741</v>
+      </c>
+      <c r="B743">
+        <v>0.000378535216441378</v>
+      </c>
+    </row>
+    <row r="744" spans="1:2">
+      <c r="A744">
+        <v>742</v>
+      </c>
+      <c r="B744">
+        <v>-4.798272493644617E-05</v>
+      </c>
+    </row>
+    <row r="745" spans="1:2">
+      <c r="A745">
+        <v>743</v>
+      </c>
+      <c r="B745">
+        <v>0.0004436638264451176</v>
+      </c>
+    </row>
+    <row r="746" spans="1:2">
+      <c r="A746">
+        <v>744</v>
+      </c>
+      <c r="B746">
+        <v>-0.0006064538029022515</v>
+      </c>
+    </row>
+    <row r="747" spans="1:2">
+      <c r="A747">
+        <v>745</v>
+      </c>
+      <c r="B747">
+        <v>0.007964048534631729</v>
+      </c>
+    </row>
+    <row r="748" spans="1:2">
+      <c r="A748">
+        <v>746</v>
+      </c>
+      <c r="B748">
+        <v>0.002045190427452326</v>
+      </c>
+    </row>
+    <row r="749" spans="1:2">
+      <c r="A749">
+        <v>747</v>
+      </c>
+      <c r="B749">
+        <v>0.001587316510267556</v>
+      </c>
+    </row>
+    <row r="750" spans="1:2">
+      <c r="A750">
+        <v>748</v>
+      </c>
+      <c r="B750">
+        <v>0.0003175395540893078</v>
+      </c>
+    </row>
+    <row r="751" spans="1:2">
+      <c r="A751">
+        <v>749</v>
+      </c>
+      <c r="B751">
+        <v>0.0004896526224911213</v>
+      </c>
+    </row>
+    <row r="752" spans="1:2">
+      <c r="A752">
+        <v>750</v>
+      </c>
+      <c r="B752">
+        <v>-0.0002827024145517498</v>
+      </c>
+    </row>
+    <row r="753" spans="1:2">
+      <c r="A753">
+        <v>751</v>
+      </c>
+      <c r="B753">
+        <v>0.0002697983873076737</v>
+      </c>
+    </row>
+    <row r="754" spans="1:2">
+      <c r="A754">
+        <v>752</v>
+      </c>
+      <c r="B754">
+        <v>0.0008087814785540104</v>
+      </c>
+    </row>
+    <row r="755" spans="1:2">
+      <c r="A755">
+        <v>753</v>
+      </c>
+      <c r="B755">
+        <v>0.0004160943790338933</v>
+      </c>
+    </row>
+    <row r="756" spans="1:2">
+      <c r="A756">
+        <v>754</v>
+      </c>
+      <c r="B756">
+        <v>0.0004578630905598402</v>
+      </c>
+    </row>
+    <row r="757" spans="1:2">
+      <c r="A757">
+        <v>755</v>
+      </c>
+      <c r="B757">
+        <v>0.0008014918421395123</v>
+      </c>
+    </row>
+    <row r="758" spans="1:2">
+      <c r="A758">
+        <v>756</v>
+      </c>
+      <c r="B758">
+        <v>0.0001150750176748261</v>
+      </c>
+    </row>
+    <row r="759" spans="1:2">
+      <c r="A759">
+        <v>757</v>
+      </c>
+      <c r="B759">
+        <v>0.0001829007378546521</v>
+      </c>
+    </row>
+    <row r="760" spans="1:2">
+      <c r="A760">
+        <v>758</v>
+      </c>
+      <c r="B760">
+        <v>-0.002344731241464615</v>
+      </c>
+    </row>
+    <row r="761" spans="1:2">
+      <c r="A761">
+        <v>759</v>
+      </c>
+      <c r="B761">
+        <v>0.0001471686700824648</v>
+      </c>
+    </row>
+    <row r="762" spans="1:2">
+      <c r="A762">
+        <v>760</v>
+      </c>
+      <c r="B762">
+        <v>0.0001131644821725786</v>
+      </c>
+    </row>
+    <row r="763" spans="1:2">
+      <c r="A763">
+        <v>761</v>
+      </c>
+      <c r="B763">
+        <v>8.985090244095773E-05</v>
+      </c>
+    </row>
+    <row r="764" spans="1:2">
+      <c r="A764">
+        <v>762</v>
+      </c>
+      <c r="B764">
+        <v>0.0003165377420373261</v>
+      </c>
+    </row>
+    <row r="765" spans="1:2">
+      <c r="A765">
+        <v>763</v>
+      </c>
+      <c r="B765">
+        <v>-8.365938992938027E-05</v>
+      </c>
+    </row>
+    <row r="766" spans="1:2">
+      <c r="A766">
+        <v>764</v>
+      </c>
+      <c r="B766">
+        <v>0.000766935758292675</v>
+      </c>
+    </row>
+    <row r="767" spans="1:2">
+      <c r="A767">
+        <v>765</v>
+      </c>
+      <c r="B767">
+        <v>0.002450131811201572</v>
+      </c>
+    </row>
+    <row r="768" spans="1:2">
+      <c r="A768">
+        <v>766</v>
+      </c>
+      <c r="B768">
+        <v>0.0005775162717327476</v>
+      </c>
+    </row>
+    <row r="769" spans="1:2">
+      <c r="A769">
+        <v>767</v>
+      </c>
+      <c r="B769">
+        <v>9.940879863279406E-06</v>
+      </c>
+    </row>
+    <row r="770" spans="1:2">
+      <c r="A770">
+        <v>768</v>
+      </c>
+      <c r="B770">
+        <v>0.0002030744508374482</v>
+      </c>
+    </row>
+    <row r="771" spans="1:2">
+      <c r="A771">
+        <v>769</v>
+      </c>
+      <c r="B771">
+        <v>0.0006078184233047068</v>
+      </c>
+    </row>
+    <row r="772" spans="1:2">
+      <c r="A772">
+        <v>770</v>
+      </c>
+      <c r="B772">
+        <v>-6.73333925078623E-05</v>
+      </c>
+    </row>
+    <row r="773" spans="1:2">
+      <c r="A773">
+        <v>771</v>
+      </c>
+      <c r="B773">
+        <v>-3.972864215029404E-05</v>
+      </c>
+    </row>
+    <row r="774" spans="1:2">
+      <c r="A774">
+        <v>772</v>
+      </c>
+      <c r="B774">
+        <v>0.00043891990208067</v>
+      </c>
+    </row>
+    <row r="775" spans="1:2">
+      <c r="A775">
+        <v>773</v>
+      </c>
+      <c r="B775">
+        <v>0.001489381655119359</v>
+      </c>
+    </row>
+    <row r="776" spans="1:2">
+      <c r="A776">
+        <v>774</v>
+      </c>
+      <c r="B776">
+        <v>0.00182435498572886</v>
+      </c>
+    </row>
+    <row r="777" spans="1:2">
+      <c r="A777">
+        <v>775</v>
+      </c>
+      <c r="B777">
+        <v>-7.669412298128009E-05</v>
+      </c>
+    </row>
+    <row r="778" spans="1:2">
+      <c r="A778">
+        <v>776</v>
+      </c>
+      <c r="B778">
+        <v>0.0002615029807202518</v>
+      </c>
+    </row>
+    <row r="779" spans="1:2">
+      <c r="A779">
+        <v>777</v>
+      </c>
+      <c r="B779">
+        <v>-4.97626606374979E-05</v>
+      </c>
+    </row>
+    <row r="780" spans="1:2">
+      <c r="A780">
+        <v>778</v>
+      </c>
+      <c r="B780">
+        <v>0.00185290933586657</v>
+      </c>
+    </row>
+    <row r="781" spans="1:2">
+      <c r="A781">
+        <v>779</v>
+      </c>
+      <c r="B781">
+        <v>0.0004762585449498147</v>
+      </c>
+    </row>
+    <row r="782" spans="1:2">
+      <c r="A782">
+        <v>780</v>
+      </c>
+      <c r="B782">
+        <v>0.0003106302756350487</v>
+      </c>
+    </row>
+    <row r="783" spans="1:2">
+      <c r="A783">
+        <v>781</v>
+      </c>
+      <c r="B783">
+        <v>0.001285449834540486</v>
+      </c>
+    </row>
+    <row r="784" spans="1:2">
+      <c r="A784">
+        <v>782</v>
+      </c>
+      <c r="B784">
+        <v>0.0005252578412182629</v>
+      </c>
+    </row>
+    <row r="785" spans="1:2">
+      <c r="A785">
+        <v>783</v>
+      </c>
+      <c r="B785">
+        <v>-0.0003539106401149184</v>
+      </c>
+    </row>
+    <row r="786" spans="1:2">
+      <c r="A786">
+        <v>784</v>
+      </c>
+      <c r="B786">
+        <v>-1.739378240017686E-05</v>
+      </c>
+    </row>
+    <row r="787" spans="1:2">
+      <c r="A787">
+        <v>785</v>
+      </c>
+      <c r="B787">
+        <v>0.0003082233015447855</v>
+      </c>
+    </row>
+    <row r="788" spans="1:2">
+      <c r="A788">
+        <v>786</v>
+      </c>
+      <c r="B788">
+        <v>0.0002286024391651154</v>
+      </c>
+    </row>
+    <row r="789" spans="1:2">
+      <c r="A789">
+        <v>787</v>
+      </c>
+      <c r="B789">
+        <v>-0.0001004840596579015</v>
+      </c>
+    </row>
+    <row r="790" spans="1:2">
+      <c r="A790">
+        <v>788</v>
+      </c>
+      <c r="B790">
+        <v>0.000294853380182758</v>
+      </c>
+    </row>
+    <row r="791" spans="1:2">
+      <c r="A791">
+        <v>789</v>
+      </c>
+      <c r="B791">
+        <v>0.0004955249605700374</v>
+      </c>
+    </row>
+    <row r="792" spans="1:2">
+      <c r="A792">
+        <v>790</v>
+      </c>
+      <c r="B792">
+        <v>0.0005100845592096448</v>
+      </c>
+    </row>
+    <row r="793" spans="1:2">
+      <c r="A793">
+        <v>791</v>
+      </c>
+      <c r="B793">
+        <v>0.003353020641952753</v>
+      </c>
+    </row>
+    <row r="794" spans="1:2">
+      <c r="A794">
+        <v>792</v>
+      </c>
+      <c r="B794">
+        <v>0.000243568210862577</v>
+      </c>
+    </row>
+    <row r="795" spans="1:2">
+      <c r="A795">
+        <v>793</v>
+      </c>
+      <c r="B795">
+        <v>0.0005736121674999595</v>
+      </c>
+    </row>
+    <row r="796" spans="1:2">
+      <c r="A796">
+        <v>794</v>
+      </c>
+      <c r="B796">
+        <v>-8.542981231585145E-05</v>
+      </c>
+    </row>
+    <row r="797" spans="1:2">
+      <c r="A797">
+        <v>795</v>
+      </c>
+      <c r="B797">
+        <v>0.000386059662560001</v>
+      </c>
+    </row>
+    <row r="798" spans="1:2">
+      <c r="A798">
+        <v>796</v>
+      </c>
+      <c r="B798">
+        <v>-0.0005837914068251848</v>
+      </c>
+    </row>
+    <row r="799" spans="1:2">
+      <c r="A799">
+        <v>797</v>
+      </c>
+      <c r="B799">
+        <v>-0.0002801654627546668</v>
+      </c>
+    </row>
+    <row r="800" spans="1:2">
+      <c r="A800">
+        <v>798</v>
+      </c>
+      <c r="B800">
+        <v>-0.0001959386863745749</v>
+      </c>
+    </row>
+    <row r="801" spans="1:2">
+      <c r="A801">
+        <v>799</v>
+      </c>
+      <c r="B801">
+        <v>0.0005483924178406596</v>
+      </c>
+    </row>
+    <row r="802" spans="1:2">
+      <c r="A802">
+        <v>800</v>
+      </c>
+      <c r="B802">
+        <v>6.364880391629413E-05</v>
+      </c>
+    </row>
+    <row r="803" spans="1:2">
+      <c r="A803">
+        <v>801</v>
+      </c>
+      <c r="B803">
+        <v>-0.000282329332549125</v>
+      </c>
+    </row>
+    <row r="804" spans="1:2">
+      <c r="A804">
+        <v>802</v>
+      </c>
+      <c r="B804">
+        <v>-0.0002256331354146823</v>
+      </c>
+    </row>
+    <row r="805" spans="1:2">
+      <c r="A805">
+        <v>803</v>
+      </c>
+      <c r="B805">
+        <v>0.000374195515178144</v>
+      </c>
+    </row>
+    <row r="806" spans="1:2">
+      <c r="A806">
+        <v>804</v>
+      </c>
+      <c r="B806">
+        <v>0.001537215895950794</v>
+      </c>
+    </row>
+    <row r="807" spans="1:2">
+      <c r="A807">
+        <v>805</v>
+      </c>
+      <c r="B807">
+        <v>-0.0003546459192875773</v>
+      </c>
+    </row>
+    <row r="808" spans="1:2">
+      <c r="A808">
+        <v>806</v>
+      </c>
+      <c r="B808">
+        <v>0.001257080934010446</v>
+      </c>
+    </row>
+    <row r="809" spans="1:2">
+      <c r="A809">
+        <v>807</v>
+      </c>
+      <c r="B809">
+        <v>0.0007067355909384787</v>
+      </c>
+    </row>
+    <row r="810" spans="1:2">
+      <c r="A810">
+        <v>808</v>
+      </c>
+      <c r="B810">
+        <v>0.0003407333279028535</v>
+      </c>
+    </row>
+    <row r="811" spans="1:2">
+      <c r="A811">
+        <v>809</v>
+      </c>
+      <c r="B811">
+        <v>0.0001847506937338039</v>
+      </c>
+    </row>
+    <row r="812" spans="1:2">
+      <c r="A812">
+        <v>810</v>
+      </c>
+      <c r="B812">
+        <v>0.001349415630102158</v>
+      </c>
+    </row>
+    <row r="813" spans="1:2">
+      <c r="A813">
+        <v>811</v>
+      </c>
+      <c r="B813">
+        <v>0.0009209719719365239</v>
+      </c>
+    </row>
+    <row r="814" spans="1:2">
+      <c r="A814">
+        <v>812</v>
+      </c>
+      <c r="B814">
+        <v>0.0003439904248807579</v>
+      </c>
+    </row>
+    <row r="815" spans="1:2">
+      <c r="A815">
+        <v>813</v>
+      </c>
+      <c r="B815">
+        <v>0.001203151186928153</v>
+      </c>
+    </row>
+    <row r="816" spans="1:2">
+      <c r="A816">
+        <v>814</v>
+      </c>
+      <c r="B816">
+        <v>0.0009180641500279307</v>
+      </c>
+    </row>
+    <row r="817" spans="1:2">
+      <c r="A817">
+        <v>815</v>
+      </c>
+      <c r="B817">
+        <v>0.0004788969818037003</v>
+      </c>
+    </row>
+    <row r="818" spans="1:2">
+      <c r="A818">
+        <v>816</v>
+      </c>
+      <c r="B818">
+        <v>-0.0003072546969633549</v>
+      </c>
+    </row>
+    <row r="819" spans="1:2">
+      <c r="A819">
+        <v>817</v>
+      </c>
+      <c r="B819">
+        <v>0.001966553507372737</v>
       </c>
     </row>
   </sheetData>
@@ -8934,12 +15478,508 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="B1"/>
+  <dimension ref="A1:B63"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="2:2">
+    <row r="1" spans="1:2">
       <c r="B1" t="s">
         <v>471</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>-0.0002672076225280762</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3">
+        <v>0.003784656524658203</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4">
+        <v>2</v>
+      </c>
+      <c r="B4">
+        <v>0.001981019973754883</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5">
+        <v>3</v>
+      </c>
+      <c r="B5">
+        <v>0.00420534610748291</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6">
+        <v>4</v>
+      </c>
+      <c r="B6">
+        <v>0.00288856029510498</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7">
+        <v>5</v>
+      </c>
+      <c r="B7">
+        <v>0.005827903747558594</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8">
+        <v>6</v>
+      </c>
+      <c r="B8">
+        <v>0.000468134880065918</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9">
+        <v>7</v>
+      </c>
+      <c r="B9">
+        <v>0.001396298408508301</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10">
+        <v>8</v>
+      </c>
+      <c r="B10">
+        <v>0.005578875541687012</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11">
+        <v>9</v>
+      </c>
+      <c r="B11">
+        <v>0.006026148796081543</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12">
+        <v>10</v>
+      </c>
+      <c r="B12">
+        <v>0.006254911422729492</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13">
+        <v>11</v>
+      </c>
+      <c r="B13">
+        <v>0.004657387733459473</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14">
+        <v>12</v>
+      </c>
+      <c r="B14">
+        <v>0.006129860877990723</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="A15">
+        <v>13</v>
+      </c>
+      <c r="B15">
+        <v>0.004003524780273438</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16">
+        <v>14</v>
+      </c>
+      <c r="B16">
+        <v>0.01010525226593018</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17">
+        <v>15</v>
+      </c>
+      <c r="B17">
+        <v>0.00266873836517334</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18">
+        <v>16</v>
+      </c>
+      <c r="B18">
+        <v>0.001759529113769531</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="A19">
+        <v>17</v>
+      </c>
+      <c r="B19">
+        <v>0.004752755165100098</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
+      <c r="A20">
+        <v>18</v>
+      </c>
+      <c r="B20">
+        <v>0.004470229148864746</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
+      <c r="A21">
+        <v>19</v>
+      </c>
+      <c r="B21">
+        <v>0.00324857234954834</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
+      <c r="A22">
+        <v>20</v>
+      </c>
+      <c r="B22">
+        <v>0.001123428344726562</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2">
+      <c r="A23">
+        <v>21</v>
+      </c>
+      <c r="B23">
+        <v>0.002096891403198242</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
+      <c r="A24">
+        <v>22</v>
+      </c>
+      <c r="B24">
+        <v>0.002684831619262695</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
+      <c r="A25">
+        <v>23</v>
+      </c>
+      <c r="B25">
+        <v>0.003885030746459961</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2">
+      <c r="A26">
+        <v>24</v>
+      </c>
+      <c r="B26">
+        <v>0.002611637115478516</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2">
+      <c r="A27">
+        <v>25</v>
+      </c>
+      <c r="B27">
+        <v>0.008621692657470703</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2">
+      <c r="A28">
+        <v>26</v>
+      </c>
+      <c r="B28">
+        <v>0.006350278854370117</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2">
+      <c r="A29">
+        <v>27</v>
+      </c>
+      <c r="B29">
+        <v>0.005412817001342773</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2">
+      <c r="A30">
+        <v>28</v>
+      </c>
+      <c r="B30">
+        <v>0.008019685745239258</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2">
+      <c r="A31">
+        <v>29</v>
+      </c>
+      <c r="B31">
+        <v>0.009037137031555176</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2">
+      <c r="A32">
+        <v>30</v>
+      </c>
+      <c r="B32">
+        <v>0.004596233367919922</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2">
+      <c r="A33">
+        <v>31</v>
+      </c>
+      <c r="B33">
+        <v>0.005968093872070312</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2">
+      <c r="A34">
+        <v>32</v>
+      </c>
+      <c r="B34">
+        <v>0.00899207592010498</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2">
+      <c r="A35">
+        <v>33</v>
+      </c>
+      <c r="B35">
+        <v>0.01069736480712891</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2">
+      <c r="A36">
+        <v>34</v>
+      </c>
+      <c r="B36">
+        <v>0.002249240875244141</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2">
+      <c r="A37">
+        <v>35</v>
+      </c>
+      <c r="B37">
+        <v>0.008292913436889648</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2">
+      <c r="A38">
+        <v>36</v>
+      </c>
+      <c r="B38">
+        <v>0.009760022163391113</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2">
+      <c r="A39">
+        <v>37</v>
+      </c>
+      <c r="B39">
+        <v>0.004152774810791016</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2">
+      <c r="A40">
+        <v>38</v>
+      </c>
+      <c r="B40">
+        <v>0.008290648460388184</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2">
+      <c r="A41">
+        <v>39</v>
+      </c>
+      <c r="B41">
+        <v>0.004115581512451172</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2">
+      <c r="A42">
+        <v>40</v>
+      </c>
+      <c r="B42">
+        <v>0.007293462753295898</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2">
+      <c r="A43">
+        <v>41</v>
+      </c>
+      <c r="B43">
+        <v>0.00595700740814209</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2">
+      <c r="A44">
+        <v>42</v>
+      </c>
+      <c r="B44">
+        <v>0.00661170482635498</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2">
+      <c r="A45">
+        <v>43</v>
+      </c>
+      <c r="B45">
+        <v>-0.0007734894752502441</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2">
+      <c r="A46">
+        <v>44</v>
+      </c>
+      <c r="B46">
+        <v>0.01169383525848389</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2">
+      <c r="A47">
+        <v>45</v>
+      </c>
+      <c r="B47">
+        <v>0.004967331886291504</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2">
+      <c r="A48">
+        <v>46</v>
+      </c>
+      <c r="B48">
+        <v>0.02195990085601807</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2">
+      <c r="A49">
+        <v>47</v>
+      </c>
+      <c r="B49">
+        <v>0.006072759628295898</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2">
+      <c r="A50">
+        <v>48</v>
+      </c>
+      <c r="B50">
+        <v>0.005325078964233398</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2">
+      <c r="A51">
+        <v>49</v>
+      </c>
+      <c r="B51">
+        <v>0.007787942886352539</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2">
+      <c r="A52">
+        <v>50</v>
+      </c>
+      <c r="B52">
+        <v>0.002218723297119141</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2">
+      <c r="A53">
+        <v>51</v>
+      </c>
+      <c r="B53">
+        <v>0.001924037933349609</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2">
+      <c r="A54">
+        <v>52</v>
+      </c>
+      <c r="B54">
+        <v>0.006719350814819336</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2">
+      <c r="A55">
+        <v>53</v>
+      </c>
+      <c r="B55">
+        <v>0.005294322967529297</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2">
+      <c r="A56">
+        <v>54</v>
+      </c>
+      <c r="B56">
+        <v>0.01087856292724609</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2">
+      <c r="A57">
+        <v>55</v>
+      </c>
+      <c r="B57">
+        <v>0.004174590110778809</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2">
+      <c r="A58">
+        <v>56</v>
+      </c>
+      <c r="B58">
+        <v>0.008089780807495117</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2">
+      <c r="A59">
+        <v>57</v>
+      </c>
+      <c r="B59">
+        <v>0.01384258270263672</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2">
+      <c r="A60">
+        <v>58</v>
+      </c>
+      <c r="B60">
+        <v>0.003589868545532227</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2">
+      <c r="A61">
+        <v>59</v>
+      </c>
+      <c r="B61">
+        <v>0.006949901580810547</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2">
+      <c r="A62">
+        <v>60</v>
+      </c>
+      <c r="B62">
+        <v>0.00710141658782959</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2">
+      <c r="A63">
+        <v>61</v>
+      </c>
+      <c r="B63">
+        <v>0.001474499702453613</v>
       </c>
     </row>
   </sheetData>
@@ -8949,12 +15989,108 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="B1"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="2:2">
+    <row r="1" spans="1:2">
       <c r="B1" t="s">
         <v>471</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>0.01264965534210205</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3">
+        <v>0.0194321870803833</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4">
+        <v>2</v>
+      </c>
+      <c r="B4">
+        <v>0.03153049945831299</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5">
+        <v>3</v>
+      </c>
+      <c r="B5">
+        <v>0.01701128482818604</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6">
+        <v>4</v>
+      </c>
+      <c r="B6">
+        <v>0.01246142387390137</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7">
+        <v>5</v>
+      </c>
+      <c r="B7">
+        <v>0.03800177574157715</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8">
+        <v>6</v>
+      </c>
+      <c r="B8">
+        <v>0.03290426731109619</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9">
+        <v>7</v>
+      </c>
+      <c r="B9">
+        <v>0.03508114814758301</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10">
+        <v>8</v>
+      </c>
+      <c r="B10">
+        <v>0.03112292289733887</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11">
+        <v>9</v>
+      </c>
+      <c r="B11">
+        <v>0.04686594009399414</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12">
+        <v>10</v>
+      </c>
+      <c r="B12">
+        <v>0.02730178833007812</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13">
+        <v>11</v>
+      </c>
+      <c r="B13">
+        <v>0.03715336322784424</v>
       </c>
     </row>
   </sheetData>
